--- a/Patterns_findings.xlsx
+++ b/Patterns_findings.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universitaetstgallen-my.sharepoint.com/personal/marco_franceschetti_unisg_ch/Documents/Dokumente/Papers/ICPM2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2804" documentId="8_{974D3D4C-716F-4351-96AB-0AD63E80B230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C840D05A-DCAF-4C8D-AF43-2DD768CFE473}"/>
+  <xr:revisionPtr revIDLastSave="2834" documentId="8_{974D3D4C-716F-4351-96AB-0AD63E80B230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01524B55-D281-4208-9980-0EB70903A76B}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pattern Definitions &amp; Examples " sheetId="2" r:id="rId1"/>
-    <sheet name="EventLog Analysis Results" sheetId="1" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
-    <sheet name="_order(tbd)" sheetId="3" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="5" r:id="rId2"/>
+    <sheet name="EventLog Analysis Results" sheetId="1" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
+    <sheet name="_order(tbd)" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <fileRecoveryPr repairLoad="1"/>
@@ -44,7 +45,6 @@
   <authors>
     <author>tc={C3AB106E-67B6-47D3-89A2-BB8CB97FB91E}</author>
     <author>tc={E7877EEB-2D85-2341-994E-2C28A5849E9A}</author>
-    <author>tc={51C16D9B-76D6-4433-8632-5524C850DF46}</author>
     <author>tc={AAFD993C-A04A-4B76-B167-304144E7A171}</author>
     <author>tc={AB77BB8E-CA5C-42B0-A57D-8714CA3C2751}</author>
     <author>tc={21D50800-A3E3-4ADA-A6A0-28A745989724}</author>
@@ -111,17 +111,7 @@
     Interesting is Attribute-change matrix creation</t>
       </text>
     </comment>
-    <comment ref="E12" authorId="2" shapeId="0" xr:uid="{51C16D9B-76D6-4433-8632-5524C850DF46}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    @Franceschetti, Marco, somehow I don‘t manage to find this pattern in the merimo notebook. I can see that log attributes are „silently“ dropped, but what about the case level candidates? 
-Reply:
-    Yes, log attributes are dropped, but the case level are listed - it‘s the last output before the log view</t>
-      </text>
-    </comment>
-    <comment ref="E13" authorId="3" shapeId="0" xr:uid="{AAFD993C-A04A-4B76-B167-304144E7A171}">
+    <comment ref="E12" authorId="2" shapeId="0" xr:uid="{AAFD993C-A04A-4B76-B167-304144E7A171}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -135,7 +125,7 @@
     I would then also rename the above one for consistency, yes</t>
       </text>
     </comment>
-    <comment ref="K13" authorId="4" shapeId="0" xr:uid="{AB77BB8E-CA5C-42B0-A57D-8714CA3C2751}">
+    <comment ref="K12" authorId="3" shapeId="0" xr:uid="{AB77BB8E-CA5C-42B0-A57D-8714CA3C2751}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -145,7 +135,7 @@
     I removed this part. </t>
       </text>
     </comment>
-    <comment ref="H14" authorId="5" shapeId="0" xr:uid="{21D50800-A3E3-4ADA-A6A0-28A745989724}">
+    <comment ref="H13" authorId="4" shapeId="0" xr:uid="{21D50800-A3E3-4ADA-A6A0-28A745989724}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -154,7 +144,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="K14" authorId="6" shapeId="0" xr:uid="{691C73A0-D1D8-4D1C-9516-40DEC9F03857}">
+    <comment ref="K13" authorId="5" shapeId="0" xr:uid="{691C73A0-D1D8-4D1C-9516-40DEC9F03857}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -162,7 +152,7 @@
     The examples are nice but the BPIC 2019 description is not ideal. I like the RTFM version where you mention the case log as a way to reduce complexity</t>
       </text>
     </comment>
-    <comment ref="E15" authorId="7" shapeId="0" xr:uid="{C0E32D3B-8652-4173-9E35-41CCF37B4A96}">
+    <comment ref="E14" authorId="6" shapeId="0" xr:uid="{C0E32D3B-8652-4173-9E35-41CCF37B4A96}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -170,7 +160,7 @@
     Add modification to clean duplicate events?</t>
       </text>
     </comment>
-    <comment ref="C16" authorId="8" shapeId="0" xr:uid="{55AAB93E-8EC8-422F-AD91-C085FDF4DFDE}">
+    <comment ref="C15" authorId="7" shapeId="0" xr:uid="{55AAB93E-8EC8-422F-AD91-C085FDF4DFDE}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -180,7 +170,7 @@
     Could these two also fit into category „derived information“? </t>
       </text>
     </comment>
-    <comment ref="E16" authorId="9" shapeId="0" xr:uid="{0EB0EBAB-D5EC-4BC0-B6C7-9206BBE5A796}">
+    <comment ref="E15" authorId="8" shapeId="0" xr:uid="{0EB0EBAB-D5EC-4BC0-B6C7-9206BBE5A796}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -190,7 +180,7 @@
     I agree - column comes from the case log I think</t>
       </text>
     </comment>
-    <comment ref="F16" authorId="10" shapeId="0" xr:uid="{A000C18D-3B8A-4F63-9C6D-0C0CA7A4AF57}">
+    <comment ref="F15" authorId="9" shapeId="0" xr:uid="{A000C18D-3B8A-4F63-9C6D-0C0CA7A4AF57}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -204,7 +194,7 @@
     Sounds good to me now ☺️ </t>
       </text>
     </comment>
-    <comment ref="G16" authorId="11" shapeId="0" xr:uid="{61996517-5406-467F-B19F-0EC4060EB4D1}">
+    <comment ref="G15" authorId="10" shapeId="0" xr:uid="{61996517-5406-467F-B19F-0EC4060EB4D1}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -213,7 +203,7 @@
 Also the output might need adaption?</t>
       </text>
     </comment>
-    <comment ref="I16" authorId="12" shapeId="0" xr:uid="{3B0E8F38-2BB9-44DB-9C56-20D49FF9C5DC}">
+    <comment ref="I15" authorId="11" shapeId="0" xr:uid="{3B0E8F38-2BB9-44DB-9C56-20D49FF9C5DC}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -226,7 +216,7 @@
     Made a new proposal without the visualization part. </t>
       </text>
     </comment>
-    <comment ref="J16" authorId="13" shapeId="0" xr:uid="{F06D0834-1DA6-4DF8-AC23-58B5855D9707}">
+    <comment ref="J15" authorId="12" shapeId="0" xr:uid="{F06D0834-1DA6-4DF8-AC23-58B5855D9707}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -240,7 +230,7 @@
     This is now merged</t>
       </text>
     </comment>
-    <comment ref="K16" authorId="14" shapeId="0" xr:uid="{3666C166-7054-4EB3-9256-735FC5E46074}">
+    <comment ref="K15" authorId="13" shapeId="0" xr:uid="{3666C166-7054-4EB3-9256-735FC5E46074}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -262,7 +252,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="E17" authorId="15" shapeId="0" xr:uid="{57EA069E-1ECD-4C4F-9FF9-1F90B9ACDD9A}">
+    <comment ref="E16" authorId="14" shapeId="0" xr:uid="{57EA069E-1ECD-4C4F-9FF9-1F90B9ACDD9A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -270,7 +260,7 @@
     We mention in the paper / excel sheet that this is realized manually</t>
       </text>
     </comment>
-    <comment ref="D18" authorId="16" shapeId="0" xr:uid="{89338788-C0B7-457D-AA08-57875DE8D18A}">
+    <comment ref="D17" authorId="15" shapeId="0" xr:uid="{89338788-C0B7-457D-AA08-57875DE8D18A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -278,7 +268,7 @@
     One-to-one is a special case of that an attribute is already a derivate (enrichment) of the remainder (which is hard to detect but this is linked to consistency - for example totalPaymentAmount is computed from paymentAmount) - on the other hand 1:1 also generalizes to 1:0 n:m etc. which is easy to compute and what would make sense as a general pattern IMO</t>
       </text>
     </comment>
-    <comment ref="E18" authorId="17" shapeId="0" xr:uid="{0AEA5C55-82A5-4211-BF25-3CF0E2A3C6B2}">
+    <comment ref="E17" authorId="16" shapeId="0" xr:uid="{0AEA5C55-82A5-4211-BF25-3CF0E2A3C6B2}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -288,7 +278,7 @@
     To be aligned in the notebook</t>
       </text>
     </comment>
-    <comment ref="D19" authorId="18" shapeId="0" xr:uid="{EDEE3FC7-D0FA-45B3-B479-7A1207682CB9}">
+    <comment ref="D18" authorId="17" shapeId="0" xr:uid="{EDEE3FC7-D0FA-45B3-B479-7A1207682CB9}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -296,7 +286,7 @@
     Constant and 1:1 columns are to instances/sub-patterns of redundant (uninformative).</t>
       </text>
     </comment>
-    <comment ref="E19" authorId="19" shapeId="0" xr:uid="{5D37468B-09E9-4FFE-8546-6A2341A391B3}">
+    <comment ref="E18" authorId="18" shapeId="0" xr:uid="{5D37468B-09E9-4FFE-8546-6A2341A391B3}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -304,7 +294,7 @@
     Made attribute removal more general</t>
       </text>
     </comment>
-    <comment ref="G19" authorId="20" shapeId="0" xr:uid="{774CE146-74B0-4753-BFE6-B91819DA1C44}">
+    <comment ref="G18" authorId="19" shapeId="0" xr:uid="{774CE146-74B0-4753-BFE6-B91819DA1C44}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -314,7 +304,7 @@
     Agree - removed that part</t>
       </text>
     </comment>
-    <comment ref="I20" authorId="21" shapeId="0" xr:uid="{1E16C301-C9B2-44D6-841D-1D2B584940B2}">
+    <comment ref="I19" authorId="20" shapeId="0" xr:uid="{1E16C301-C9B2-44D6-841D-1D2B584940B2}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -326,7 +316,7 @@
     Just feels a bit obsolete at the moment.</t>
       </text>
     </comment>
-    <comment ref="J20" authorId="22" shapeId="0" xr:uid="{69312987-A4DF-458B-A66C-282A91B5A63F}">
+    <comment ref="J19" authorId="21" shapeId="0" xr:uid="{69312987-A4DF-458B-A66C-282A91B5A63F}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -335,7 +325,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="K20" authorId="23" shapeId="0" xr:uid="{106DA730-0355-41A1-8F55-3D4B7287BE45}">
+    <comment ref="K19" authorId="22" shapeId="0" xr:uid="{106DA730-0355-41A1-8F55-3D4B7287BE45}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -343,7 +333,7 @@
     Woudnt I want to get the different dismissal codes listed that can appear?</t>
       </text>
     </comment>
-    <comment ref="E21" authorId="24" shapeId="0" xr:uid="{0B51E013-4F9D-430D-841B-19FC9B143976}">
+    <comment ref="E20" authorId="23" shapeId="0" xr:uid="{0B51E013-4F9D-430D-841B-19FC9B143976}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -351,7 +341,7 @@
     Maybe Case-Level Attribute Consistency Validation. </t>
       </text>
     </comment>
-    <comment ref="F21" authorId="25" shapeId="0" xr:uid="{B7FEC47E-54DE-4364-812D-DBAF5731EB4E}">
+    <comment ref="F20" authorId="24" shapeId="0" xr:uid="{B7FEC47E-54DE-4364-812D-DBAF5731EB4E}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -364,7 +354,7 @@
     Reformulated for clarity</t>
       </text>
     </comment>
-    <comment ref="K21" authorId="26" shapeId="0" xr:uid="{83EE44CD-8856-416F-8B24-6F1BE24AEF2E}">
+    <comment ref="K20" authorId="25" shapeId="0" xr:uid="{83EE44CD-8856-416F-8B24-6F1BE24AEF2E}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -374,7 +364,7 @@
     After restructuring, I think these two examples are better</t>
       </text>
     </comment>
-    <comment ref="E22" authorId="27" shapeId="0" xr:uid="{A8AB18DA-CD05-4130-B2CA-B3872BDEA80A}">
+    <comment ref="E21" authorId="26" shapeId="0" xr:uid="{A8AB18DA-CD05-4130-B2CA-B3872BDEA80A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -382,7 +372,7 @@
     This is nice, but not entirely clear how you compute this. This is tightly related to scatter plots, which should be mentioned here as well.</t>
       </text>
     </comment>
-    <comment ref="F22" authorId="28" shapeId="0" xr:uid="{402584D8-B375-4D51-8684-F15FA5F4BBF5}">
+    <comment ref="F21" authorId="27" shapeId="0" xr:uid="{402584D8-B375-4D51-8684-F15FA5F4BBF5}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -396,7 +386,7 @@
     Statistical dependence. I checked for consistent terminology and I think that now it should be clear. Please let me know if this is still not sufficiently clear</t>
       </text>
     </comment>
-    <comment ref="C24" authorId="29" shapeId="0" xr:uid="{01DF6923-E607-4C1B-BF78-59F3BAA10DA4}">
+    <comment ref="C23" authorId="28" shapeId="0" xr:uid="{01DF6923-E607-4C1B-BF78-59F3BAA10DA4}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -406,7 +396,7 @@
     Could these two also fit into category „derived information“? </t>
       </text>
     </comment>
-    <comment ref="E24" authorId="30" shapeId="0" xr:uid="{915AD55F-BFE8-403C-822B-591C77261636}">
+    <comment ref="E23" authorId="29" shapeId="0" xr:uid="{915AD55F-BFE8-403C-822B-591C77261636}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -416,7 +406,7 @@
     Sounds good to me! </t>
       </text>
     </comment>
-    <comment ref="C25" authorId="31" shapeId="0" xr:uid="{F581D420-4F66-47B0-93C4-676F91999735}">
+    <comment ref="C24" authorId="30" shapeId="0" xr:uid="{F581D420-4F66-47B0-93C4-676F91999735}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -426,7 +416,7 @@
     Could these two also fit into category „derived information“? </t>
       </text>
     </comment>
-    <comment ref="E25" authorId="32" shapeId="0" xr:uid="{3976CB8A-A166-4144-8235-28E0ECAF53B4}">
+    <comment ref="E24" authorId="31" shapeId="0" xr:uid="{3976CB8A-A166-4144-8235-28E0ECAF53B4}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -434,7 +424,7 @@
     Detection of the Suriadi „Collateral events“ pattern - but more in general as we drop the assumption on the event timestamps they have (they are close in time in the imperfection pattern, here we assume only coexistence) --&gt; “Collateral Events Candidates”</t>
       </text>
     </comment>
-    <comment ref="H25" authorId="33" shapeId="0" xr:uid="{6D97DA2C-FCDE-4741-9559-009793170C1B}">
+    <comment ref="H24" authorId="32" shapeId="0" xr:uid="{6D97DA2C-FCDE-4741-9559-009793170C1B}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -444,7 +434,7 @@
     Abstracted to "similarity score/threshold" in both to avoid bringing technical details in</t>
       </text>
     </comment>
-    <comment ref="B26" authorId="34" shapeId="0" xr:uid="{D1815610-93D3-469C-8CC6-34FF18A30241}">
+    <comment ref="B25" authorId="33" shapeId="0" xr:uid="{D1815610-93D3-469C-8CC6-34FF18A30241}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -452,7 +442,7 @@
     Here I am not so sure, 4.7 and 4.8 could also be added earlier - potentially after 4.5, i.e., before the more detailed analysis of activity occurrence and transactions (my argument is that I would probably first want to fine-tune my final set of activity types before asssessing how often they occur per case in if there are patterns. </t>
       </text>
     </comment>
-    <comment ref="C26" authorId="35" shapeId="0" xr:uid="{64C6940B-C2D9-4159-A95B-053607C0EE94}">
+    <comment ref="C25" authorId="34" shapeId="0" xr:uid="{64C6940B-C2D9-4159-A95B-053607C0EE94}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -464,7 +454,7 @@
     Lisa and I have a new proposal</t>
       </text>
     </comment>
-    <comment ref="E26" authorId="36" shapeId="0" xr:uid="{AD30F376-7AE7-483C-B1ED-037A0A5DD418}">
+    <comment ref="E25" authorId="35" shapeId="0" xr:uid="{AD30F376-7AE7-483C-B1ED-037A0A5DD418}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -494,7 +484,7 @@
 However, to not inflate the patterns, to me it would also be intuitive to have one pattern for consolidation of events with an optional extension of attribute information. </t>
       </text>
     </comment>
-    <comment ref="I26" authorId="37" shapeId="0" xr:uid="{0830C006-494A-43E2-AD84-155DF24F9F6F}">
+    <comment ref="I25" authorId="36" shapeId="0" xr:uid="{0830C006-494A-43E2-AD84-155DF24F9F6F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -504,7 +494,7 @@
     Makes sense - I added to the preconditions a discussion of the folding rule with a reference the timestamp - this way the approach is kept more conceptual</t>
       </text>
     </comment>
-    <comment ref="L26" authorId="38" shapeId="0" xr:uid="{FA0E7DA0-A4B7-4284-8801-47245B01F42A}">
+    <comment ref="L25" authorId="37" shapeId="0" xr:uid="{FA0E7DA0-A4B7-4284-8801-47245B01F42A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -512,7 +502,7 @@
     Why? It makes sense for row 22, but here this association is only created with the potential new attribute, right?</t>
       </text>
     </comment>
-    <comment ref="E27" authorId="39" shapeId="0" xr:uid="{35C3E6DD-AF62-4359-BEC0-5AAD8B53F596}">
+    <comment ref="E26" authorId="38" shapeId="0" xr:uid="{35C3E6DD-AF62-4359-BEC0-5AAD8B53F596}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -522,7 +512,7 @@
     Additionally, if we want to add the format, I think this should be the first analysis, then the granularity, then the constant values. ☺️ </t>
       </text>
     </comment>
-    <comment ref="F27" authorId="40" shapeId="0" xr:uid="{9C382232-11FD-4AD9-B906-B9BBCB23099A}">
+    <comment ref="F26" authorId="39" shapeId="0" xr:uid="{9C382232-11FD-4AD9-B906-B9BBCB23099A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -534,7 +524,7 @@
 P.S.: I did not yet check if also motivation/approach requires updates)</t>
       </text>
     </comment>
-    <comment ref="G27" authorId="41" shapeId="0" xr:uid="{E9D777BE-4CE3-483D-B443-5BDB34925F01}">
+    <comment ref="G26" authorId="40" shapeId="0" xr:uid="{E9D777BE-4CE3-483D-B443-5BDB34925F01}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -542,7 +532,7 @@
     I think based on this, information the case-wise ordering check would be the next logical pattern. </t>
       </text>
     </comment>
-    <comment ref="H27" authorId="42" shapeId="0" xr:uid="{EEE1BCF1-19DF-499D-81EA-09A2F79D620B}">
+    <comment ref="H26" authorId="41" shapeId="0" xr:uid="{EEE1BCF1-19DF-499D-81EA-09A2F79D620B}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -552,7 +542,7 @@
     In jupyter we could ponetially convert to a valid datetime format</t>
       </text>
     </comment>
-    <comment ref="K27" authorId="43" shapeId="0" xr:uid="{7612A1A2-1311-432D-846D-55391B9B80FF}">
+    <comment ref="K26" authorId="42" shapeId="0" xr:uid="{7612A1A2-1311-432D-846D-55391B9B80FF}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -560,7 +550,7 @@
     Re-introduce the summary in marimo</t>
       </text>
     </comment>
-    <comment ref="O27" authorId="44" shapeId="0" xr:uid="{5FDD14F3-7C62-5948-9029-841D8FA4676E}">
+    <comment ref="O26" authorId="43" shapeId="0" xr:uid="{5FDD14F3-7C62-5948-9029-841D8FA4676E}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -572,7 +562,7 @@
 However, I don‘t think this will stay in as evidence, as I understood that we are not using the ProMiSE Log as an example. </t>
       </text>
     </comment>
-    <comment ref="E28" authorId="45" shapeId="0" xr:uid="{2E267686-14D6-4169-8DB8-16462DBC5A3F}">
+    <comment ref="E27" authorId="44" shapeId="0" xr:uid="{2E267686-14D6-4169-8DB8-16462DBC5A3F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -580,7 +570,7 @@
     This and the above one remedy to the Suriadi „Unanchored event“ pattern</t>
       </text>
     </comment>
-    <comment ref="C30" authorId="46" shapeId="0" xr:uid="{3877D097-A754-44CB-8262-A4154106C5B9}">
+    <comment ref="C29" authorId="45" shapeId="0" xr:uid="{3877D097-A754-44CB-8262-A4154106C5B9}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -588,7 +578,7 @@
     This name is not good as this is not necessarily reducing complexity - its more a refinement</t>
       </text>
     </comment>
-    <comment ref="E30" authorId="47" shapeId="0" xr:uid="{9021A5E7-7672-4A9D-B2D2-889DA37C26B1}">
+    <comment ref="E29" authorId="46" shapeId="0" xr:uid="{9021A5E7-7672-4A9D-B2D2-889DA37C26B1}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -596,7 +586,7 @@
     Detection of the Suriadi „Form-based event capture“ pattern + other such cases of events being recorded with the same timestamp --&gt; “Form-based Event Capture Candidates”</t>
       </text>
     </comment>
-    <comment ref="F30" authorId="48" shapeId="0" xr:uid="{D8030C57-2AFB-4D02-8960-7584EA109DCB}">
+    <comment ref="F29" authorId="47" shapeId="0" xr:uid="{D8030C57-2AFB-4D02-8960-7584EA109DCB}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -744,7 +734,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="389">
   <si>
     <t>RTFM</t>
   </si>
@@ -765,21 +755,6 @@
   </si>
   <si>
     <t>BPIC2018</t>
-  </si>
-  <si>
-    <t>7 candidate case attributes</t>
-  </si>
-  <si>
-    <t>118 case attributes</t>
-  </si>
-  <si>
-    <t>2 case attributes</t>
-  </si>
-  <si>
-    <t>15 case attributes, 1 candidate</t>
-  </si>
-  <si>
-    <t>3 case attributes</t>
   </si>
   <si>
     <t>N/A</t>
@@ -916,9 +891,6 @@
   </si>
   <si>
     <t>Remove a selected uninformative attribute while retaining, in the case of redundant attributes, the attribute that provides its equivalent information.</t>
-  </si>
-  <si>
-    <t>Event logs may not explicitly or reliably distinguish log-level and case-level from event-level attributes. Identifying attributes that remain constant within the log and cases helps analysts understand the log structure and determine which attributes characterize the entire log or entire process instances and therefore must not be analyzed on the event level.</t>
   </si>
   <si>
     <t>Log and Case Attribute Candidates</t>
@@ -1126,9 +1098,6 @@
     <t>Concurrent Events Detection</t>
   </si>
   <si>
-    <t>The set of attributes identified as candidate log and case attributes, respectively.</t>
-  </si>
-  <si>
     <t>The distribution of the attribute's filling characteristics across cases, including the percentage of cases in which the attribute is missing, populated once, populated multiple times with the same value, or populated multiple times with different values.</t>
   </si>
   <si>
@@ -1139,59 +1108,6 @@
   </si>
   <si>
     <t>An event log in which the selected uninformative attribute has been removed.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Sepsis: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Age, which is an attribute loosely (i.e., not strictly) associated with several activity types in the event log is unique per case, which makes it a case attribute candidate.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>DomesticDeclarations:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Attribute case:BudgetNumber has a unique non-null value across the log, which makes it a log attribute candidate.</t>
-    </r>
-  </si>
-  <si>
-    <t>Identify attributes that are likely to represent  log-level or case-level properties.</t>
-  </si>
-  <si>
-    <t>Identify evidence that an attribute might represent log-level or case-level information, considering explicit log- and case-level designation, and whether its value remains constant within the log or within each case.</t>
   </si>
   <si>
     <t>Attribute information may differ not only in its availability across activity types but also across cases. An attribute may be available exactly once per case (i.e., case attribute candidate), multiple times with the same or different values, or only for a subset of cases. Understanding these filling characteristics helps analysts assess the attribute's availability.</t>
@@ -2079,11 +1995,6 @@
     <t>By default, the log is already ordered case-wise, but not totally (log-level).</t>
   </si>
   <si>
-    <t xml:space="preserve">Identified 3 case level attributes: impact, organization country &amp; product. 
-All three are quite reasonable. 
-No log level attributes. </t>
-  </si>
-  <si>
     <t>Created a case table with the case level attributes</t>
   </si>
   <si>
@@ -2170,9 +2081,6 @@
 All attributes are either mandatory or global.</t>
   </si>
   <si>
-    <t>24 candidate case attributes, e.g., age, which is an attribute loosely (i.e., not strictly) associated with several activity types in the event log is unique per case, which makes it a case attribute candidate..</t>
-  </si>
-  <si>
     <t xml:space="preserve">A majority (all but "user"/org:resource) of attributes are case level attributes that blow up the event log  and are more relevant to analyse for cases instead of each event. </t>
   </si>
   <si>
@@ -2939,10 +2847,6 @@
     <t>With a set size of 2, 5,094 candidates for super events are identified. However, case support is limited, with the top candiate ("administratief tarief- eerste pol", "vervolgconsult poliklinisch") being support by 48% of cases, and other candidates with support 30% or lower. No batch candidates are found.</t>
   </si>
   <si>
-    <t xml:space="preserve">2 attributes (case:Purch. Doc. Category name,  case:Source) are unique for the complete log. 
-15 other attributes are case level attributes. </t>
-  </si>
-  <si>
     <t>Attribute "case:Age" appears to follow a normal distribution.</t>
   </si>
   <si>
@@ -3005,10 +2909,6 @@
   </si>
   <si>
     <t>With a set size of 2, 1,010 super event candidates are identified, however with limited case support (max is 0.37). No batch candidates are identified.</t>
-  </si>
-  <si>
-    <t>4 case attributes and 
-Attribute "case:BudgetNumber" has a unique non-null value across the log, which makes it a log attribute candidate.</t>
   </si>
   <si>
     <t>No duplicate events.</t>
@@ -3183,9 +3083,6 @@
 The schemas of many activities overlap. </t>
   </si>
   <si>
-    <t xml:space="preserve">62 candidates case attributes identified and 4 candidate log attributes. </t>
-  </si>
-  <si>
     <t>Event log can be enriched with the addition of a new attribute "AmountDifference", whose value is computed as the difference between the value of "RequestedAmount"and the value of "OfferedAmount".</t>
   </si>
   <si>
@@ -3257,6 +3154,9 @@
   </si>
   <si>
     <t>There are 42 distinct actity types of which many show are rather low case coverage: 25 activities below 1%, another 9 below 10%. Only "Create Purchase Order Item" is covered by all cases.</t>
+  </si>
+  <si>
+    <t>C1 | Create Order | 2024-01-01 08:10 C1 | Check Stock | 2024-01-01 08:12 C1 | Reserve Items | 2024-01-01 08:13 C1 | Confirm Order | 2024-01-01 08:15 C1 | Ship Order | 2024-01-02 10:00 C1 | Send Invoice | 2024-01-02 10:05 C2 | Create Order | 2024-01-03 09:00 C2 | Check Stock | 2024-01-03 09:02 C2 | Reserve Items | 2024-01-03 09:03 C2 | Confirm Order | 2024-01-03 09:04 C2 | Ship Order | 2024-01-04 11:20 C2 | Send Invoice | 2024-01-04 11:25 C3 | Create Order | 2024-01-05 14:10 C3 | Check Stock | 2024-01-05 14:12 C3 | Reserve Items | 2024-01-05 14:13 C3 | Confirm Order | 2024-01-05 14:15 C3 | Send Invoice | 2024-01-05 16:20</t>
   </si>
 </sst>
 </file>
@@ -3614,7 +3514,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3699,9 +3599,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4617,10 +4514,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C219EE16-BD6D-4A1C-A20C-7BB47EB72A85}" name="Table1" displayName="Table1" ref="B9:P34" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31" tableBorderDxfId="30">
-  <autoFilter ref="B9:P34" xr:uid="{C219EE16-BD6D-4A1C-A20C-7BB47EB72A85}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B10:P34">
-    <sortCondition ref="B9:B34"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C219EE16-BD6D-4A1C-A20C-7BB47EB72A85}" name="Table1" displayName="Table1" ref="B9:P33" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31" tableBorderDxfId="30">
+  <autoFilter ref="B9:P33" xr:uid="{C219EE16-BD6D-4A1C-A20C-7BB47EB72A85}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B10:P33">
+    <sortCondition ref="B9:B33"/>
   </sortState>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{073C678C-BCE0-4EA8-BDCB-E8064D9744D7}" name="No." dataDxfId="29"/>
@@ -4644,10 +4541,10 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3EDC892B-CCCC-4F0E-8345-38847C019291}" name="Table2" displayName="Table2" ref="A1:M38" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
-  <autoFilter ref="A1:M38" xr:uid="{3EDC892B-CCCC-4F0E-8345-38847C019291}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M38">
-    <sortCondition ref="A1:A38"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3EDC892B-CCCC-4F0E-8345-38847C019291}" name="Table2" displayName="Table2" ref="A1:M37" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+  <autoFilter ref="A1:M37" xr:uid="{3EDC892B-CCCC-4F0E-8345-38847C019291}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M37">
+    <sortCondition ref="A1:A37"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{033F8C96-7095-49A2-B40C-2D8DBAEB4D12}" name="No." dataDxfId="13"/>
@@ -4931,10 +4828,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C11" dT="2026-09-02T15:03:01.58" personId="{67619BF6-90B0-4F5A-9CB2-1D00BC01A3E8}" id="{C3AB106E-67B6-47D3-89A2-BB8CB97FB91E}">
+  <threadedComment ref="C11" dT="2026-09-02T15:03:01.58" personId="{67619BF6-90B0-4F5A-9CB2-1D00BC01A3E8}" id="{C3AB106E-67B6-47D3-89A2-BB8CB97FB91E}" done="1">
     <text>Could structure and population also be different categories; they do not seem so similar to me.</text>
   </threadedComment>
-  <threadedComment ref="N11" dT="2026-08-28T07:28:06.63" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{E7877EEB-2D85-2341-994E-2C28A5849E9A}">
+  <threadedComment ref="N11" dT="2026-08-28T07:28:06.63" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{E7877EEB-2D85-2341-994E-2C28A5849E9A}" done="1">
     <text>@Franceschetti, Marco: paper is related but broader than a single patterns. Discovers data-flow of attributes and how they are manipulated.</text>
     <mentions>
       <mention mentionpersonId="{347771E1-58EF-44A4-B677-C217AD80543B}" mentionId="{B59D35A6-152D-4245-AE94-833BAE14A5B6}" startIndex="0" length="21"/>
@@ -4943,59 +4840,50 @@
   <threadedComment ref="N11" dT="2026-08-28T07:31:31.76" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{272D643D-E0DF-9043-9A10-82EFF1E2126B}" parentId="{E7877EEB-2D85-2341-994E-2C28A5849E9A}">
     <text>Interesting is Attribute-change matrix creation</text>
   </threadedComment>
-  <threadedComment ref="E12" dT="2026-08-31T13:45:30.12" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{51C16D9B-76D6-4433-8632-5524C850DF46}" done="1">
-    <text xml:space="preserve">@Franceschetti, Marco, somehow I don‘t manage to find this pattern in the merimo notebook. I can see that log attributes are „silently“ dropped, but what about the case level candidates? </text>
-    <mentions>
-      <mention mentionpersonId="{347771E1-58EF-44A4-B677-C217AD80543B}" mentionId="{B72C90DE-E6F0-4AD6-872D-4EC3EB1BD15D}" startIndex="0" length="21"/>
-    </mentions>
-  </threadedComment>
-  <threadedComment ref="E12" dT="2026-08-31T13:51:47.17" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{37481457-CA15-4096-9E27-D80DC219EDD3}" parentId="{51C16D9B-76D6-4433-8632-5524C850DF46}">
-    <text>Yes, log attributes are dropped, but the case level are listed - it‘s the last output before the log view</text>
-  </threadedComment>
-  <threadedComment ref="E13" dT="2026-08-18T14:03:00.32" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{AAFD993C-A04A-4B76-B167-304144E7A171}" done="1">
+  <threadedComment ref="E12" dT="2026-08-18T14:03:00.32" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{AAFD993C-A04A-4B76-B167-304144E7A171}" done="1">
     <text>@Zimmermann, Lisa from the description of the motivation it looks like this concerns not only case attributes, as the name suggests - what about Attribute filling within case - or something like that?</text>
     <mentions>
       <mention mentionpersonId="{5251FA7F-7AD4-42C8-A99C-4E1EBADEC8E3}" mentionId="{50AD6EED-E735-4D28-B714-47800D4442BC}" startIndex="0" length="17"/>
     </mentions>
   </threadedComment>
-  <threadedComment ref="E13" dT="2026-08-18T14:09:44.85" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{37D81DC9-2B01-4931-B53A-41F22E8AB540}" parentId="{AAFD993C-A04A-4B76-B167-304144E7A171}">
+  <threadedComment ref="E12" dT="2026-08-18T14:09:44.85" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{37D81DC9-2B01-4931-B53A-41F22E8AB540}" parentId="{AAFD993C-A04A-4B76-B167-304144E7A171}">
     <text>Or case-wise attribute filling</text>
   </threadedComment>
-  <threadedComment ref="E13" dT="2026-08-19T06:48:40.57" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{5656CBAD-21CD-4D39-81AD-10F85C2D4932}" parentId="{AAFD993C-A04A-4B76-B167-304144E7A171}">
+  <threadedComment ref="E12" dT="2026-08-19T06:48:40.57" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{5656CBAD-21CD-4D39-81AD-10F85C2D4932}" parentId="{AAFD993C-A04A-4B76-B167-304144E7A171}">
     <text>A saw the similiarity to the „Activity-Attribute Filling“ pattern and therefore suggested the name, but I see the confusion with case-level attributes. So case-wise is also fine for me! (I am just wondering, if we should then also rename the one above into activity-wise attribute filling, just for consistency?)</text>
   </threadedComment>
-  <threadedComment ref="E13" dT="2026-08-19T07:44:11.61" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{1FEAB77D-9D94-4E6E-A2AE-35FA8D5DFAEF}" parentId="{AAFD993C-A04A-4B76-B167-304144E7A171}">
+  <threadedComment ref="E12" dT="2026-08-19T07:44:11.61" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{1FEAB77D-9D94-4E6E-A2AE-35FA8D5DFAEF}" parentId="{AAFD993C-A04A-4B76-B167-304144E7A171}">
     <text>I would then also rename the above one for consistency, yes</text>
   </threadedComment>
-  <threadedComment ref="K13" dT="2026-08-31T14:32:20.31" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{AB77BB8E-CA5C-42B0-A57D-8714CA3C2751}" done="1">
+  <threadedComment ref="K12" dT="2026-08-31T14:32:20.31" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{AB77BB8E-CA5C-42B0-A57D-8714CA3C2751}" done="1">
     <text>The second part of the Sepsis example is not about relevant evidence, but some additional hypothesis to evaluate as this patterns can be indicative e.g., for missing values</text>
   </threadedComment>
-  <threadedComment ref="K13" dT="2026-09-01T14:26:05.23" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{EA7EB35B-BE5C-4C9F-91C5-7F4BA3D58BB4}" parentId="{AB77BB8E-CA5C-42B0-A57D-8714CA3C2751}">
+  <threadedComment ref="K12" dT="2026-09-01T14:26:05.23" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{EA7EB35B-BE5C-4C9F-91C5-7F4BA3D58BB4}" parentId="{AB77BB8E-CA5C-42B0-A57D-8714CA3C2751}">
     <text xml:space="preserve">I removed this part. </text>
   </threadedComment>
-  <threadedComment ref="H14" dT="2026-08-31T14:09:14.37" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{21D50800-A3E3-4ADA-A6A0-28A745989724}" done="1">
+  <threadedComment ref="H13" dT="2026-08-31T14:09:14.37" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{21D50800-A3E3-4ADA-A6A0-28A745989724}" done="1">
     <text xml:space="preserve">Added this precondition - do you think it is ok?
 </text>
   </threadedComment>
-  <threadedComment ref="K14" dT="2026-08-31T14:42:04.59" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{691C73A0-D1D8-4D1C-9516-40DEC9F03857}">
+  <threadedComment ref="K13" dT="2026-08-31T14:42:04.59" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{691C73A0-D1D8-4D1C-9516-40DEC9F03857}" done="1">
     <text>The examples are nice but the BPIC 2019 description is not ideal. I like the RTFM version where you mention the case log as a way to reduce complexity</text>
   </threadedComment>
-  <threadedComment ref="E15" dT="2026-08-19T13:29:58.32" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{C0E32D3B-8652-4173-9E35-41CCF37B4A96}" done="1">
+  <threadedComment ref="E14" dT="2026-08-19T13:29:58.32" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{C0E32D3B-8652-4173-9E35-41CCF37B4A96}" done="1">
     <text>Add modification to clean duplicate events?</text>
   </threadedComment>
-  <threadedComment ref="C16" dT="2026-08-31T14:47:40.60" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{55AAB93E-8EC8-422F-AD91-C085FDF4DFDE}" done="1">
+  <threadedComment ref="C15" dT="2026-08-31T14:47:40.60" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{55AAB93E-8EC8-422F-AD91-C085FDF4DFDE}" done="1">
     <text>For me the first and the second one are a different catagorie than the third and the fourth - 3 and 4 are about granularity</text>
   </threadedComment>
-  <threadedComment ref="C16" dT="2026-09-01T11:36:54.54" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{25B417E9-AD62-4F51-883E-F8F1A2834617}" parentId="{55AAB93E-8EC8-422F-AD91-C085FDF4DFDE}">
+  <threadedComment ref="C15" dT="2026-09-01T11:36:54.54" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{25B417E9-AD62-4F51-883E-F8F1A2834617}" parentId="{55AAB93E-8EC8-422F-AD91-C085FDF4DFDE}">
     <text xml:space="preserve">Could these two also fit into category „derived information“? </text>
   </threadedComment>
-  <threadedComment ref="E16" dT="2026-08-20T07:53:42.14" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{0EB0EBAB-D5EC-4BC0-B6C7-9206BBE5A796}" done="1">
+  <threadedComment ref="E15" dT="2026-08-20T07:53:42.14" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{0EB0EBAB-D5EC-4BC0-B6C7-9206BBE5A796}" done="1">
     <text>For consistency, we should either use attribute or column. Lisa and I would go for attribute</text>
   </threadedComment>
-  <threadedComment ref="E16" dT="2026-09-01T07:45:01.21" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{BFE3E78C-DC05-E047-883F-1805423AB536}" parentId="{0EB0EBAB-D5EC-4BC0-B6C7-9206BBE5A796}">
+  <threadedComment ref="E15" dT="2026-09-01T07:45:01.21" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{BFE3E78C-DC05-E047-883F-1805423AB536}" parentId="{0EB0EBAB-D5EC-4BC0-B6C7-9206BBE5A796}">
     <text>I agree - column comes from the case log I think</text>
   </threadedComment>
-  <threadedComment ref="F16" dT="2026-08-31T13:33:52.76" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{A000C18D-3B8A-4F63-9C6D-0C0CA7A4AF57}" done="1">
+  <threadedComment ref="F15" dT="2026-08-31T13:33:52.76" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{A000C18D-3B8A-4F63-9C6D-0C0CA7A4AF57}" done="1">
     <text xml:space="preserve">@Franceschetti, Marco : Suggestion: 
 Understand the distribution of of values for a given activity and attribute combination. 
 In additional, also the motivation needs to be updated accordingly from my understanding. What do you think?
@@ -5004,197 +4892,197 @@
       <mention mentionpersonId="{347771E1-58EF-44A4-B677-C217AD80543B}" mentionId="{9F81E7FC-8740-434D-BA8E-CF91C8F9BAE9}" startIndex="0" length="21"/>
     </mentions>
   </threadedComment>
-  <threadedComment ref="F16" dT="2026-08-31T13:56:12.66" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{E1D04637-D75F-4525-A567-7F59BE273E66}" parentId="{A000C18D-3B8A-4F63-9C6D-0C0CA7A4AF57}">
+  <threadedComment ref="F15" dT="2026-08-31T13:56:12.66" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{E1D04637-D75F-4525-A567-7F59BE273E66}" parentId="{A000C18D-3B8A-4F63-9C6D-0C0CA7A4AF57}">
     <text>I like this formulation and updated the motivation - see if you like it</text>
   </threadedComment>
-  <threadedComment ref="F16" dT="2026-09-01T07:21:05.39" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{E6A042FA-AE52-4C23-8D8A-F0B3C0682A25}" parentId="{A000C18D-3B8A-4F63-9C6D-0C0CA7A4AF57}">
+  <threadedComment ref="F15" dT="2026-09-01T07:21:05.39" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{E6A042FA-AE52-4C23-8D8A-F0B3C0682A25}" parentId="{A000C18D-3B8A-4F63-9C6D-0C0CA7A4AF57}">
     <text xml:space="preserve">Sounds good to me now ☺️ </text>
   </threadedComment>
-  <threadedComment ref="G16" dT="2026-09-07T09:55:13.84" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{61996517-5406-467F-B19F-0EC4060EB4D1}">
+  <threadedComment ref="G15" dT="2026-09-07T09:55:13.84" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{61996517-5406-467F-B19F-0EC4060EB4D1}" done="1">
     <text>New proposal for information need based on the output: Understand how consistently a given attribute is populated for a selected activity and how its available values are distributed. 
 Also the output might need adaption?</text>
   </threadedComment>
-  <threadedComment ref="I16" dT="2026-08-31T13:32:03.08" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{3B0E8F38-2BB9-44DB-9C56-20D49FF9C5DC}" done="1">
+  <threadedComment ref="I15" dT="2026-08-31T13:32:03.08" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{3B0E8F38-2BB9-44DB-9C56-20D49FF9C5DC}" done="1">
     <text>@Franceschetti, Marco : Suggestion (to be confirmed by you): 
 Based on an Activity and Attribute combination, derive the distribution of its values and visualize as a histogram with variable number of bins?</text>
     <mentions>
       <mention mentionpersonId="{347771E1-58EF-44A4-B677-C217AD80543B}" mentionId="{D4956C9B-AE14-40E0-9591-160D49BEBE1D}" startIndex="0" length="21"/>
     </mentions>
   </threadedComment>
-  <threadedComment ref="I16" dT="2026-08-31T14:00:53.25" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{E0D81E72-7CCD-4C9A-8616-5E5ACF42B4CC}" parentId="{3B0E8F38-2BB9-44DB-9C56-20D49FF9C5DC}">
+  <threadedComment ref="I15" dT="2026-08-31T14:00:53.25" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{E0D81E72-7CCD-4C9A-8616-5E5ACF42B4CC}" parentId="{3B0E8F38-2BB9-44DB-9C56-20D49FF9C5DC}">
     <text>I would not state how the results are presented to the user, since this is implementation-dependent.</text>
   </threadedComment>
-  <threadedComment ref="I16" dT="2026-09-01T14:30:00.84" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{DE2D151F-36EA-4553-801D-409CEFDBFD10}" parentId="{3B0E8F38-2BB9-44DB-9C56-20D49FF9C5DC}">
+  <threadedComment ref="I15" dT="2026-09-01T14:30:00.84" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{DE2D151F-36EA-4553-801D-409CEFDBFD10}" parentId="{3B0E8F38-2BB9-44DB-9C56-20D49FF9C5DC}">
     <text xml:space="preserve">Made a new proposal without the visualization part. </text>
   </threadedComment>
-  <threadedComment ref="J16" dT="2026-08-24T14:14:05.96" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{F06D0834-1DA6-4DF8-AC23-58B5855D9707}" done="1">
+  <threadedComment ref="J15" dT="2026-08-24T14:14:05.96" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{F06D0834-1DA6-4DF8-AC23-58B5855D9707}" done="1">
     <text xml:space="preserve">I think this is currently not the output of the implementation ...
 </text>
   </threadedComment>
-  <threadedComment ref="J16" dT="2026-08-24T14:26:05.48" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{E9A0B25B-D136-4DEC-94E5-1DC112DB6D8B}" parentId="{F06D0834-1DA6-4DF8-AC23-58B5855D9707}">
+  <threadedComment ref="J15" dT="2026-08-24T14:26:05.48" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{E9A0B25B-D136-4DEC-94E5-1DC112DB6D8B}" parentId="{F06D0834-1DA6-4DF8-AC23-58B5855D9707}">
     <text>The visualization of the distribution is in a separate notebook - to be merged</text>
   </threadedComment>
-  <threadedComment ref="J16" dT="2026-08-25T08:00:53.00" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{ECCF9417-E308-4C68-8563-6EC98A3636B6}" parentId="{F06D0834-1DA6-4DF8-AC23-58B5855D9707}">
+  <threadedComment ref="J15" dT="2026-08-25T08:00:53.00" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{ECCF9417-E308-4C68-8563-6EC98A3636B6}" parentId="{F06D0834-1DA6-4DF8-AC23-58B5855D9707}">
     <text xml:space="preserve">As soon as it is merged, we might be able to find some nicer examples. I think for the distributions, amount for add penalty vs. Create fine could be more interesting than the age for the sepsis log. </text>
   </threadedComment>
-  <threadedComment ref="J16" dT="2026-08-25T14:22:36.79" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{29548D33-1724-4A47-BCA1-B6691750E3EB}" parentId="{F06D0834-1DA6-4DF8-AC23-58B5855D9707}">
+  <threadedComment ref="J15" dT="2026-08-25T14:22:36.79" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{29548D33-1724-4A47-BCA1-B6691750E3EB}" parentId="{F06D0834-1DA6-4DF8-AC23-58B5855D9707}">
     <text>This is now merged</text>
   </threadedComment>
-  <threadedComment ref="K16" dT="2026-08-24T13:57:45.14" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{3666C166-7054-4EB3-9256-735FC5E46074}">
+  <threadedComment ref="K15" dT="2026-08-24T13:57:45.14" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{3666C166-7054-4EB3-9256-735FC5E46074}" done="1">
     <text xml:space="preserve">„The identified unique values are different for both activity types.„
 -&gt; I suggest to remove this last part here, as for me, it raises more questions than it reveals anything about the pattern. Or rephrase it to something like: 
 the attributes value distribution slightly differs for both  activities types, indicating that a wieder variety of ages is captures for the ER Registration activity is captured (or something like that? Because I don‘t think in this case, the value distribution is related to an underlying difference. Maybe I can find a better example.
 </text>
   </threadedComment>
-  <threadedComment ref="K16" dT="2026-08-28T07:40:41.54" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{CCD89A6A-26AB-5B49-A1FF-58D72A44F831}" parentId="{3666C166-7054-4EB3-9256-735FC5E46074}">
+  <threadedComment ref="K15" dT="2026-08-28T07:40:41.54" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{CCD89A6A-26AB-5B49-A1FF-58D72A44F831}" parentId="{3666C166-7054-4EB3-9256-735FC5E46074}">
     <text xml:space="preserve">.. suggesting that the expense is not related to penalties - does not relate to the pattern description; </text>
   </threadedComment>
-  <threadedComment ref="K16" dT="2026-08-28T07:41:18.85" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{7EA46871-8109-5247-A370-96EC6D5F7C22}" parentId="{3666C166-7054-4EB3-9256-735FC5E46074}">
+  <threadedComment ref="K15" dT="2026-08-28T07:41:18.85" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{7EA46871-8109-5247-A370-96EC6D5F7C22}" parentId="{3666C166-7054-4EB3-9256-735FC5E46074}">
     <text xml:space="preserve">Same with the second example: indicating …. </text>
   </threadedComment>
-  <threadedComment ref="K16" dT="2026-08-28T07:42:02.26" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{C5F20196-26AC-314B-B888-8F411C22916B}" parentId="{3666C166-7054-4EB3-9256-735FC5E46074}">
+  <threadedComment ref="K15" dT="2026-08-28T07:42:02.26" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{C5F20196-26AC-314B-B888-8F411C22916B}" parentId="{3666C166-7054-4EB3-9256-735FC5E46074}">
     <text>I would expect to find that in the information need when it is mentioned here - the information need is about consistency of population and not about activity-attribute associations</text>
   </threadedComment>
-  <threadedComment ref="K16" dT="2026-08-31T13:38:46.97" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{507A9A44-484D-4D06-B701-33D4762CC2BD}" parentId="{3666C166-7054-4EB3-9256-735FC5E46074}">
+  <threadedComment ref="K15" dT="2026-08-31T13:38:46.97" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{507A9A44-484D-4D06-B701-33D4762CC2BD}" parentId="{3666C166-7054-4EB3-9256-735FC5E46074}">
     <text xml:space="preserve">Outdated evidence. But I think it would be nice to add the precentages to the activity schema pattern.
 The list of negative missing absolute values that is currently there, is not so intuitive to me, but maybe I am reading it wrong? </text>
   </threadedComment>
-  <threadedComment ref="K16" dT="2026-09-07T11:16:52.14" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{565E6D21-A2B1-46DF-8E7E-766DD666FD96}" parentId="{3666C166-7054-4EB3-9256-735FC5E46074}">
+  <threadedComment ref="K15" dT="2026-09-07T11:16:52.14" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{565E6D21-A2B1-46DF-8E7E-766DD666FD96}" parentId="{3666C166-7054-4EB3-9256-735FC5E46074}">
     <text xml:space="preserve">@Marco - updated the relevant evidence. Can you check if this makes sense?
 </text>
   </threadedComment>
-  <threadedComment ref="E17" dT="2026-09-02T11:20:41.45" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{57EA069E-1ECD-4C4F-9FF9-1F90B9ACDD9A}" done="1">
+  <threadedComment ref="E16" dT="2026-09-02T11:20:41.45" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{57EA069E-1ECD-4C4F-9FF9-1F90B9ACDD9A}" done="1">
     <text>We mention in the paper / excel sheet that this is realized manually</text>
   </threadedComment>
-  <threadedComment ref="D18" dT="2026-09-02T15:43:39.23" personId="{67619BF6-90B0-4F5A-9CB2-1D00BC01A3E8}" id="{89338788-C0B7-457D-AA08-57875DE8D18A}" done="1">
+  <threadedComment ref="D17" dT="2026-09-02T15:43:39.23" personId="{67619BF6-90B0-4F5A-9CB2-1D00BC01A3E8}" id="{89338788-C0B7-457D-AA08-57875DE8D18A}" done="1">
     <text>One-to-one is a special case of that an attribute is already a derivate (enrichment) of the remainder (which is hard to detect but this is linked to consistency - for example totalPaymentAmount is computed from paymentAmount) - on the other hand 1:1 also generalizes to 1:0 n:m etc. which is easy to compute and what would make sense as a general pattern IMO</text>
   </threadedComment>
-  <threadedComment ref="E18" dT="2026-08-31T11:17:56.66" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{0AEA5C55-82A5-4211-BF25-3CF0E2A3C6B2}" done="1">
+  <threadedComment ref="E17" dT="2026-08-31T11:17:56.66" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{0AEA5C55-82A5-4211-BF25-3CF0E2A3C6B2}" done="1">
     <text>Weakened the name “Redundant Attribute Candidates” as there may be no redundancy but all needed information</text>
   </threadedComment>
-  <threadedComment ref="E18" dT="2026-09-01T08:16:44.90" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{7E9A4499-3F55-465F-9F95-7C757951F8FE}" parentId="{0AEA5C55-82A5-4211-BF25-3CF0E2A3C6B2}">
+  <threadedComment ref="E17" dT="2026-09-01T08:16:44.90" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{7E9A4499-3F55-465F-9F95-7C757951F8FE}" parentId="{0AEA5C55-82A5-4211-BF25-3CF0E2A3C6B2}">
     <text>To be aligned in the notebook</text>
   </threadedComment>
-  <threadedComment ref="D19" dT="2026-09-02T15:48:25.61" personId="{67619BF6-90B0-4F5A-9CB2-1D00BC01A3E8}" id="{EDEE3FC7-D0FA-45B3-B479-7A1207682CB9}">
+  <threadedComment ref="D18" dT="2026-09-02T15:48:25.61" personId="{67619BF6-90B0-4F5A-9CB2-1D00BC01A3E8}" id="{EDEE3FC7-D0FA-45B3-B479-7A1207682CB9}" done="1">
     <text>Constant and 1:1 columns are to instances/sub-patterns of redundant (uninformative).</text>
   </threadedComment>
-  <threadedComment ref="E19" dT="2026-08-19T14:12:32.65" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{5D37468B-09E9-4FFE-8546-6A2341A391B3}" done="1">
+  <threadedComment ref="E18" dT="2026-08-19T14:12:32.65" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{5D37468B-09E9-4FFE-8546-6A2341A391B3}" done="1">
     <text>Made attribute removal more general</text>
   </threadedComment>
-  <threadedComment ref="G19" dT="2026-08-31T15:20:44.03" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{774CE146-74B0-4753-BFE6-B91819DA1C44}" done="1">
+  <threadedComment ref="G18" dT="2026-08-31T15:20:44.03" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{774CE146-74B0-4753-BFE6-B91819DA1C44}" done="1">
     <text xml:space="preserve">I would avoid saying “preserving the information they encode” for constant attributes. If you actually delete a constant attribute such as country = CH, that information is technically no longer encoded in the resulting log. What you're preserving is the relevant/distinguishing information. </text>
   </threadedComment>
-  <threadedComment ref="G19" dT="2026-09-01T07:14:50.26" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{CDE29664-5FF2-4674-B8AE-1DF46C7FC967}" parentId="{774CE146-74B0-4753-BFE6-B91819DA1C44}">
+  <threadedComment ref="G18" dT="2026-09-01T07:14:50.26" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{CDE29664-5FF2-4674-B8AE-1DF46C7FC967}" parentId="{774CE146-74B0-4753-BFE6-B91819DA1C44}">
     <text>Agree - removed that part</text>
   </threadedComment>
-  <threadedComment ref="I20" dT="2026-08-12T10:12:39.79" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{1E16C301-C9B2-44D6-841D-1D2B584940B2}" done="1">
+  <threadedComment ref="I19" dT="2026-08-12T10:12:39.79" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{1E16C301-C9B2-44D6-841D-1D2B584940B2}" done="1">
     <text>Requires validation/update</text>
   </threadedComment>
-  <threadedComment ref="I20" dT="2026-08-19T13:18:42.35" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{79510315-CE2A-43C0-A29F-E88964BA694F}" parentId="{1E16C301-C9B2-44D6-841D-1D2B584940B2}">
+  <threadedComment ref="I19" dT="2026-08-19T13:18:42.35" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{79510315-CE2A-43C0-A29F-E88964BA694F}" parentId="{1E16C301-C9B2-44D6-841D-1D2B584940B2}">
     <text>I just noticed: data type is already part of pattern 1.1 - could this pattern be potentially included in the event log column classification one or similar?</text>
   </threadedComment>
-  <threadedComment ref="I20" dT="2026-08-19T13:18:59.20" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{F0169A40-B730-4440-8541-FE84A2439C2E}" parentId="{1E16C301-C9B2-44D6-841D-1D2B584940B2}">
+  <threadedComment ref="I19" dT="2026-08-19T13:18:59.20" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{F0169A40-B730-4440-8541-FE84A2439C2E}" parentId="{1E16C301-C9B2-44D6-841D-1D2B584940B2}">
     <text>Just feels a bit obsolete at the moment.</text>
   </threadedComment>
-  <threadedComment ref="J20" dT="2026-08-19T14:37:01.76" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{69312987-A4DF-458B-A66C-282A91B5A63F}" done="1">
+  <threadedComment ref="J19" dT="2026-08-19T14:37:01.76" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{69312987-A4DF-458B-A66C-282A91B5A63F}" done="1">
     <text xml:space="preserve">Need update with timestamp 
 </text>
   </threadedComment>
-  <threadedComment ref="K20" dT="2026-08-31T15:22:11.63" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{106DA730-0355-41A1-8F55-3D4B7287BE45}">
+  <threadedComment ref="K19" dT="2026-08-31T15:22:11.63" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{106DA730-0355-41A1-8F55-3D4B7287BE45}" done="1">
     <text>Woudnt I want to get the different dismissal codes listed that can appear?</text>
   </threadedComment>
-  <threadedComment ref="E21" dT="2026-08-31T15:24:34.04" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{0B51E013-4F9D-430D-841B-19FC9B143976}" done="1">
+  <threadedComment ref="E20" dT="2026-08-31T15:24:34.04" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{0B51E013-4F9D-430D-841B-19FC9B143976}" done="1">
     <text xml:space="preserve">Maybe Case-Level Attribute Consistency Validation. </text>
   </threadedComment>
-  <threadedComment ref="F21" dT="2026-08-31T15:27:32.07" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{B7FEC47E-54DE-4364-812D-DBAF5731EB4E}" done="1">
+  <threadedComment ref="F20" dT="2026-08-31T15:27:32.07" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{B7FEC47E-54DE-4364-812D-DBAF5731EB4E}" done="1">
     <text xml:space="preserve">Its a bit unclear what consistent means:
 If you mean identical within a case, I'd avoid consistent and write “has the same value across all events of a case” or “is constant within each case.” 
 If you mean complies with some domain rule, then consistent is appropriate, but the rule needs to define what consistency means.
 Domain rule: The paymentAmount must remain between 0 and 100 throughout the entire case. </text>
   </threadedComment>
-  <threadedComment ref="F21" dT="2026-09-02T14:52:54.80" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{23078CE1-CD96-49A0-BC07-A593D60AE8E9}" parentId="{B7FEC47E-54DE-4364-812D-DBAF5731EB4E}">
+  <threadedComment ref="F20" dT="2026-09-02T14:52:54.80" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{23078CE1-CD96-49A0-BC07-A593D60AE8E9}" parentId="{B7FEC47E-54DE-4364-812D-DBAF5731EB4E}">
     <text>Reformulated for clarity</text>
   </threadedComment>
-  <threadedComment ref="K21" dT="2026-08-25T12:17:45.42" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{83EE44CD-8856-416F-8B24-6F1BE24AEF2E}" done="1">
+  <threadedComment ref="K20" dT="2026-08-25T12:17:45.42" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{83EE44CD-8856-416F-8B24-6F1BE24AEF2E}" done="1">
     <text>I think we need a better example here, including a more sophisticated rule than uniqueness (which we already check in the case attribute candidates pattern)</text>
   </threadedComment>
-  <threadedComment ref="K21" dT="2026-09-08T11:12:56.15" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{F588617E-7250-4644-B54C-AF810D27358C}" parentId="{83EE44CD-8856-416F-8B24-6F1BE24AEF2E}">
+  <threadedComment ref="K20" dT="2026-09-08T11:12:56.15" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{F588617E-7250-4644-B54C-AF810D27358C}" parentId="{83EE44CD-8856-416F-8B24-6F1BE24AEF2E}">
     <text>After restructuring, I think these two examples are better</text>
   </threadedComment>
-  <threadedComment ref="E22" dT="2026-09-02T15:45:48.11" personId="{67619BF6-90B0-4F5A-9CB2-1D00BC01A3E8}" id="{A8AB18DA-CD05-4130-B2CA-B3872BDEA80A}" done="1">
+  <threadedComment ref="E21" dT="2026-09-02T15:45:48.11" personId="{67619BF6-90B0-4F5A-9CB2-1D00BC01A3E8}" id="{A8AB18DA-CD05-4130-B2CA-B3872BDEA80A}" done="1">
     <text>This is nice, but not entirely clear how you compute this. This is tightly related to scatter plots, which should be mentioned here as well.</text>
   </threadedComment>
-  <threadedComment ref="F22" dT="2026-08-31T15:32:29.81" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{402584D8-B375-4D51-8684-F15FA5F4BBF5}" done="1">
+  <threadedComment ref="F21" dT="2026-08-31T15:32:29.81" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{402584D8-B375-4D51-8684-F15FA5F4BBF5}" done="1">
     <text xml:space="preserve">Do you mean correlation ? Association here? </text>
   </threadedComment>
-  <threadedComment ref="F22" dT="2026-08-31T15:33:47.73" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{0E875967-F7B1-48C0-8923-FF1A4EC56883}" parentId="{402584D8-B375-4D51-8684-F15FA5F4BBF5}">
+  <threadedComment ref="F21" dT="2026-08-31T15:33:47.73" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{0E875967-F7B1-48C0-8923-FF1A4EC56883}" parentId="{402584D8-B375-4D51-8684-F15FA5F4BBF5}">
     <text xml:space="preserve">Or do you mean: Statistical dependence: A relationship between two attributes where the distribution of one attribute varies depending on the value of the other. </text>
   </threadedComment>
-  <threadedComment ref="F22" dT="2026-08-31T15:34:01.15" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{9089B5B6-155E-4B18-B77E-1339336D5DDA}" parentId="{402584D8-B375-4D51-8684-F15FA5F4BBF5}">
+  <threadedComment ref="F21" dT="2026-08-31T15:34:01.15" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{9089B5B6-155E-4B18-B77E-1339336D5DDA}" parentId="{402584D8-B375-4D51-8684-F15FA5F4BBF5}">
     <text>I find the description here a bit too fuzzy</text>
   </threadedComment>
-  <threadedComment ref="F22" dT="2026-09-01T08:55:26.27" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{4CA4FD07-7D7F-4A84-9021-19222D303D93}" parentId="{402584D8-B375-4D51-8684-F15FA5F4BBF5}">
+  <threadedComment ref="F21" dT="2026-09-01T08:55:26.27" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{4CA4FD07-7D7F-4A84-9021-19222D303D93}" parentId="{402584D8-B375-4D51-8684-F15FA5F4BBF5}">
     <text>Statistical dependence. I checked for consistent terminology and I think that now it should be clear. Please let me know if this is still not sufficiently clear</text>
   </threadedComment>
-  <threadedComment ref="C24" dT="2026-08-31T14:47:40.60" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{01DF6923-E607-4C1B-BF78-59F3BAA10DA4}" done="1">
+  <threadedComment ref="C23" dT="2026-08-31T14:47:40.60" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{01DF6923-E607-4C1B-BF78-59F3BAA10DA4}" done="1">
     <text>For me the first and the second one are a different catagorie than the third and the fourth - 3 and 4 are about granularity</text>
   </threadedComment>
-  <threadedComment ref="C24" dT="2026-09-01T11:36:54.54" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{7E4047C6-6134-46CC-8157-B03010D0B762}" parentId="{01DF6923-E607-4C1B-BF78-59F3BAA10DA4}">
+  <threadedComment ref="C23" dT="2026-09-01T11:36:54.54" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{7E4047C6-6134-46CC-8157-B03010D0B762}" parentId="{01DF6923-E607-4C1B-BF78-59F3BAA10DA4}">
     <text xml:space="preserve">Could these two also fit into category „derived information“? </text>
   </threadedComment>
-  <threadedComment ref="E24" dT="2026-08-18T14:25:25.40" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{915AD55F-BFE8-403C-822B-591C77261636}" done="1">
+  <threadedComment ref="E23" dT="2026-08-18T14:25:25.40" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{915AD55F-BFE8-403C-822B-591C77261636}" done="1">
     <text>Maybe Case-wise activity occurrence?</text>
   </threadedComment>
-  <threadedComment ref="E24" dT="2026-08-19T06:49:08.44" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{4FA466AE-C11A-40E4-BEE0-53859EE51EE5}" parentId="{915AD55F-BFE8-403C-822B-591C77261636}">
+  <threadedComment ref="E23" dT="2026-08-19T06:49:08.44" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{4FA466AE-C11A-40E4-BEE0-53859EE51EE5}" parentId="{915AD55F-BFE8-403C-822B-591C77261636}">
     <text xml:space="preserve">Sounds good to me! </text>
   </threadedComment>
-  <threadedComment ref="C25" dT="2026-08-31T14:47:40.60" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{F581D420-4F66-47B0-93C4-676F91999735}" done="1">
+  <threadedComment ref="C24" dT="2026-08-31T14:47:40.60" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{F581D420-4F66-47B0-93C4-676F91999735}" done="1">
     <text>For me the first and the second one are a different catagorie than the third and the fourth - 3 and 4 are about granularity</text>
   </threadedComment>
-  <threadedComment ref="C25" dT="2026-09-01T11:36:54.54" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{AD7B26C8-B475-47D8-9A93-2838265ABAD5}" parentId="{F581D420-4F66-47B0-93C4-676F91999735}">
+  <threadedComment ref="C24" dT="2026-09-01T11:36:54.54" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{AD7B26C8-B475-47D8-9A93-2838265ABAD5}" parentId="{F581D420-4F66-47B0-93C4-676F91999735}">
     <text xml:space="preserve">Could these two also fit into category „derived information“? </text>
   </threadedComment>
-  <threadedComment ref="E25" dT="2026-09-01T08:05:25.38" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{3976CB8A-A166-4144-8235-28E0ECAF53B4}">
+  <threadedComment ref="E24" dT="2026-09-01T08:05:25.38" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{3976CB8A-A166-4144-8235-28E0ECAF53B4}" done="1">
     <text>Detection of the Suriadi „Collateral events“ pattern - but more in general as we drop the assumption on the event timestamps they have (they are close in time in the imperfection pattern, here we assume only coexistence) --&gt; “Collateral Events Candidates”</text>
   </threadedComment>
-  <threadedComment ref="H25" dT="2026-09-04T13:27:40.37" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{6D97DA2C-FCDE-4741-9559-009793170C1B}">
+  <threadedComment ref="H24" dT="2026-09-04T13:27:40.37" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{6D97DA2C-FCDE-4741-9559-009793170C1B}" done="1">
     <text>@Abbad-Andaloussi, Amine Is the weighted Jaccard similarity the only way to achieve this or an implementation choice? Also relevant for the next cell no the approach. If possible, we should give more conceptual descriptions here that abstract from the specific instantiation of the patterns that we provide in the notebooks</text>
     <mentions>
       <mention mentionpersonId="{77CAF1B6-12F5-4365-B867-6AB78306C125}" mentionId="{537E67E6-DC21-436D-8418-AFB63FA6BB86}" startIndex="0" length="24"/>
     </mentions>
   </threadedComment>
-  <threadedComment ref="H25" dT="2026-09-04T13:33:54.99" personId="{1D3666FE-8297-4003-80FC-8C5CAF30F225}" id="{69DE3EB2-9C02-B649-B27F-F89186F57872}" parentId="{6D97DA2C-FCDE-4741-9559-009793170C1B}">
+  <threadedComment ref="H24" dT="2026-09-04T13:33:54.99" personId="{1D3666FE-8297-4003-80FC-8C5CAF30F225}" id="{69DE3EB2-9C02-B649-B27F-F89186F57872}" parentId="{6D97DA2C-FCDE-4741-9559-009793170C1B}">
     <text>Abstracted to "similarity score/threshold" in both to avoid bringing technical details in</text>
   </threadedComment>
-  <threadedComment ref="B26" dT="2026-09-01T14:16:01.20" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{D1815610-93D3-469C-8CC6-34FF18A30241}">
+  <threadedComment ref="B25" dT="2026-09-01T14:16:01.20" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{D1815610-93D3-469C-8CC6-34FF18A30241}" done="1">
     <text xml:space="preserve">Here I am not so sure, 4.7 and 4.8 could also be added earlier - potentially after 4.5, i.e., before the more detailed analysis of activity occurrence and transactions (my argument is that I would probably first want to fine-tune my final set of activity types before asssessing how often they occur per case in if there are patterns. </text>
   </threadedComment>
-  <threadedComment ref="C26" dT="2026-08-31T14:47:40.60" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{64C6940B-C2D9-4159-A95B-053607C0EE94}" done="1">
+  <threadedComment ref="C25" dT="2026-08-31T14:47:40.60" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{64C6940B-C2D9-4159-A95B-053607C0EE94}" done="1">
     <text>For me the first and the second one are a different catagorie than the third and the fourth - 3 and 4 are about granularity</text>
   </threadedComment>
-  <threadedComment ref="C26" dT="2026-09-01T11:36:54.54" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{5F95771A-7906-468C-8E74-F1A2EF3ED296}" parentId="{64C6940B-C2D9-4159-A95B-053607C0EE94}">
+  <threadedComment ref="C25" dT="2026-09-01T11:36:54.54" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{5F95771A-7906-468C-8E74-F1A2EF3ED296}" parentId="{64C6940B-C2D9-4159-A95B-053607C0EE94}">
     <text xml:space="preserve">Could these two also fit into category „derived information“? </text>
   </threadedComment>
-  <threadedComment ref="C26" dT="2026-09-01T14:26:13.86" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{7675EEF4-FB4A-46A6-84A3-C8ACE635E147}" parentId="{64C6940B-C2D9-4159-A95B-053607C0EE94}">
+  <threadedComment ref="C25" dT="2026-09-01T14:26:13.86" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{7675EEF4-FB4A-46A6-84A3-C8ACE635E147}" parentId="{64C6940B-C2D9-4159-A95B-053607C0EE94}">
     <text>Lisa and I have a new proposal</text>
   </threadedComment>
-  <threadedComment ref="E26" dT="2026-08-26T13:56:36.76" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{AD30F376-7AE7-483C-B1ED-037A0A5DD418}" done="1">
+  <threadedComment ref="E25" dT="2026-08-26T13:56:36.76" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{AD30F376-7AE7-483C-B1ED-037A0A5DD418}" done="1">
     <text>These need renaming as discussed</text>
   </threadedComment>
-  <threadedComment ref="E26" dT="2026-08-26T13:56:55.18" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{7C3DAC54-C23B-4702-B666-7EAE5D12DD3D}" parentId="{AD30F376-7AE7-483C-B1ED-037A0A5DD418}">
+  <threadedComment ref="E25" dT="2026-08-26T13:56:55.18" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{7C3DAC54-C23B-4702-B666-7EAE5D12DD3D}" parentId="{AD30F376-7AE7-483C-B1ED-037A0A5DD418}">
     <text>Activity types &lt;-&gt; attributes</text>
   </threadedComment>
-  <threadedComment ref="E26" dT="2026-08-31T14:14:35.76" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{77AFD6CE-B8CC-4569-8FB9-1D329D64F383}" parentId="{AD30F376-7AE7-483C-B1ED-037A0A5DD418}">
+  <threadedComment ref="E25" dT="2026-08-31T14:14:35.76" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{77AFD6CE-B8CC-4569-8FB9-1D329D64F383}" parentId="{AD30F376-7AE7-483C-B1ED-037A0A5DD418}">
     <text>Is it a requirement, that some information always goes into an attribute, or could it also simply be dropped? 
 In that case, maybe „Activity Type Consolidation“ is a better name for the pattern?</text>
   </threadedComment>
-  <threadedComment ref="E26" dT="2026-08-31T14:34:20.35" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{E4DD134F-BB37-44B1-8167-8CD0C1DFF407}" parentId="{AD30F376-7AE7-483C-B1ED-037A0A5DD418}">
+  <threadedComment ref="E25" dT="2026-08-31T14:34:20.35" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{E4DD134F-BB37-44B1-8167-8CD0C1DFF407}" parentId="{AD30F376-7AE7-483C-B1ED-037A0A5DD418}">
     <text>Do you have any use case in mind where you would completely (ie with information loss) drop the distinction between activities?</text>
   </threadedComment>
-  <threadedComment ref="E26" dT="2026-08-31T14:46:18.78" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{683315A6-FE97-4722-ADB2-103E19C06AA5}" parentId="{AD30F376-7AE7-483C-B1ED-037A0A5DD418}">
+  <threadedComment ref="E25" dT="2026-08-31T14:46:18.78" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{683315A6-FE97-4722-ADB2-103E19C06AA5}" parentId="{AD30F376-7AE7-483C-B1ED-037A0A5DD418}">
     <text>This sounds pretty much like event abstraction - this could also be checked as related literature</text>
   </threadedComment>
-  <threadedComment ref="E26" dT="2026-08-31T14:50:29.87" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{F3D1FAA0-8C9C-47A9-BD9E-8BC4221E42AA}" parentId="{AD30F376-7AE7-483C-B1ED-037A0A5DD418}">
+  <threadedComment ref="E25" dT="2026-08-31T14:50:29.87" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{F3D1FAA0-8C9C-47A9-BD9E-8BC4221E42AA}" parentId="{AD30F376-7AE7-483C-B1ED-037A0A5DD418}">
     <text xml:space="preserve">And there is a redesign pattern by hajo which is called task composition whihc is related: 270043 193..213 </text>
     <extLst>
       <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
@@ -5203,36 +5091,36 @@
       </x:ext>
     </extLst>
   </threadedComment>
-  <threadedComment ref="E26" dT="2026-08-31T15:05:53.75" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{FE517293-4FE7-4525-AB16-C2761A9D1F40}" parentId="{AD30F376-7AE7-483C-B1ED-037A0A5DD418}">
+  <threadedComment ref="E25" dT="2026-08-31T15:05:53.75" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{FE517293-4FE7-4525-AB16-C2761A9D1F40}" parentId="{AD30F376-7AE7-483C-B1ED-037A0A5DD418}">
     <text>Suggestions for names: 
 Activity Type Consolidation: Multiple activity types → one generalized activity type
 Type-to-Attribute Encoding: Their former type distinction → attribute values
 Generalization: Good when the original types are semantic specializations of the resulting type 
 Depending on which name is chosen the resulting description should align</text>
   </threadedComment>
-  <threadedComment ref="E26" dT="2026-09-01T08:07:14.13" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{08EF5510-B711-41CB-B53B-75C7A4CFB3DB}" parentId="{AD30F376-7AE7-483C-B1ED-037A0A5DD418}">
+  <threadedComment ref="E25" dT="2026-09-01T08:07:14.13" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{08EF5510-B711-41CB-B53B-75C7A4CFB3DB}" parentId="{AD30F376-7AE7-483C-B1ED-037A0A5DD418}">
     <text>Remedy to the Suriadi „Polluted label“ pattern --&gt; “Polluted Label Remedy”</text>
   </threadedComment>
-  <threadedComment ref="E26" dT="2026-09-01T10:24:03.21" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{0495B732-E4F8-4AAA-B140-78ED18EC3EFE}" parentId="{AD30F376-7AE7-483C-B1ED-037A0A5DD418}">
+  <threadedComment ref="E25" dT="2026-09-01T10:24:03.21" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{0495B732-E4F8-4AAA-B140-78ED18EC3EFE}" parentId="{AD30F376-7AE7-483C-B1ED-037A0A5DD418}">
     <text xml:space="preserve">Barbaras suggestion for another pattern: „activity type consolidation“ would also be a remedy to the „Form-based Event capture“ imperfection pattern IMO. 
 However, to not inflate the patterns, to me it would also be intuitive to have one pattern for consolidation of events with an optional extension of attribute information. </text>
   </threadedComment>
-  <threadedComment ref="I26" dT="2026-08-24T08:24:10.96" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{0830C006-494A-43E2-AD84-155DF24F9F6F}" done="1">
+  <threadedComment ref="I25" dT="2026-08-24T08:24:10.96" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{0830C006-494A-43E2-AD84-155DF24F9F6F}" done="1">
     <text>I think event timestamp &amp; name handling is missing here. Requires a sentence of explanation IMO.</text>
   </threadedComment>
-  <threadedComment ref="I26" dT="2026-08-24T09:30:43.36" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{F84CC4B3-B32C-4F99-A9B5-D0CBDBB6B7C6}" parentId="{0830C006-494A-43E2-AD84-155DF24F9F6F}">
+  <threadedComment ref="I25" dT="2026-08-24T09:30:43.36" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{F84CC4B3-B32C-4F99-A9B5-D0CBDBB6B7C6}" parentId="{0830C006-494A-43E2-AD84-155DF24F9F6F}">
     <text>Makes sense - I added to the preconditions a discussion of the folding rule with a reference the timestamp - this way the approach is kept more conceptual</text>
   </threadedComment>
-  <threadedComment ref="L26" dT="2026-08-31T14:16:15.27" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{FA0E7DA0-A4B7-4284-8801-47245B01F42A}" done="1">
+  <threadedComment ref="L25" dT="2026-08-31T14:16:15.27" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{FA0E7DA0-A4B7-4284-8801-47245B01F42A}" done="1">
     <text>Why? It makes sense for row 22, but here this association is only created with the potential new attribute, right?</text>
   </threadedComment>
-  <threadedComment ref="E27" dT="2026-08-25T12:56:34.38" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{35C3E6DD-AF62-4359-BEC0-5AAD8B53F596}" done="1">
+  <threadedComment ref="E26" dT="2026-08-25T12:56:34.38" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{35C3E6DD-AF62-4359-BEC0-5AAD8B53F596}" done="1">
     <text>I think the printed text at the end of the constant timestamp elements part might be a bit misleading (not sure if you plan to use that also in the merimo notebook. For the RTFM log for example, I can identify a timestamp format of:  %Y-%m-%d %H:%M:%S%z , but also know that the lowest level of granularity is hour. So actually, minutes, seconds and timezone are constant.</text>
   </threadedComment>
-  <threadedComment ref="E27" dT="2026-08-25T13:05:52.77" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{46DA4EE9-1FF4-4A84-B0C4-27EC638D69DB}" parentId="{35C3E6DD-AF62-4359-BEC0-5AAD8B53F596}">
+  <threadedComment ref="E26" dT="2026-08-25T13:05:52.77" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{46DA4EE9-1FF4-4A84-B0C4-27EC638D69DB}" parentId="{35C3E6DD-AF62-4359-BEC0-5AAD8B53F596}">
     <text xml:space="preserve">Additionally, if we want to add the format, I think this should be the first analysis, then the granularity, then the constant values. ☺️ </text>
   </threadedComment>
-  <threadedComment ref="F27" dT="2026-09-07T13:36:24.40" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{9C382232-11FD-4AD9-B906-B9BBCB23099A}">
+  <threadedComment ref="F26" dT="2026-09-07T13:36:24.40" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{9C382232-11FD-4AD9-B906-B9BBCB23099A}" done="1">
     <text>@Franceschetti, Marco 
 Timezone is currently not identified in the jupyter notebook and timestamp format is missing from this list. 
 Proposal: 
@@ -5242,68 +5130,68 @@
       <mention mentionpersonId="{347771E1-58EF-44A4-B677-C217AD80543B}" mentionId="{F11974EF-B197-45EC-B484-36DFBC30BE72}" startIndex="0" length="21"/>
     </mentions>
   </threadedComment>
-  <threadedComment ref="G27" dT="2026-08-12T10:06:35.67" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{E9D777BE-4CE3-483D-B443-5BDB34925F01}" done="1">
+  <threadedComment ref="G26" dT="2026-08-12T10:06:35.67" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{E9D777BE-4CE3-483D-B443-5BDB34925F01}" done="1">
     <text xml:space="preserve">I think based on this, information the case-wise ordering check would be the next logical pattern. </text>
   </threadedComment>
-  <threadedComment ref="H27" dT="2026-09-07T12:59:26.75" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{EEE1BCF1-19DF-499D-81EA-09A2F79D620B}" done="1">
+  <threadedComment ref="H26" dT="2026-09-07T12:59:26.75" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{EEE1BCF1-19DF-499D-81EA-09A2F79D620B}" done="1">
     <text>@Franceschetti, Marco  - lets double check, but if I recall correctly, that is the precondition for the Merimo notebook, right? Should it be added in the jupyter implementation? Or dropped here in the excel?</text>
     <mentions>
       <mention mentionpersonId="{347771E1-58EF-44A4-B677-C217AD80543B}" mentionId="{85FF85AC-9763-4A9A-ABC4-0CC02E5B5AA8}" startIndex="0" length="21"/>
     </mentions>
   </threadedComment>
-  <threadedComment ref="H27" dT="2026-09-07T12:59:49.91" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{38687B02-7D6F-4A15-8A7C-BD663F33C1A2}" parentId="{EEE1BCF1-19DF-499D-81EA-09A2F79D620B}">
+  <threadedComment ref="H26" dT="2026-09-07T12:59:49.91" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{38687B02-7D6F-4A15-8A7C-BD663F33C1A2}" parentId="{EEE1BCF1-19DF-499D-81EA-09A2F79D620B}">
     <text>In jupyter we could ponetially convert to a valid datetime format</text>
   </threadedComment>
-  <threadedComment ref="K27" dT="2026-09-02T12:09:12.82" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{7612A1A2-1311-432D-846D-55391B9B80FF}">
+  <threadedComment ref="K26" dT="2026-09-02T12:09:12.82" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{7612A1A2-1311-432D-846D-55391B9B80FF}" done="1">
     <text>Re-introduce the summary in marimo</text>
   </threadedComment>
-  <threadedComment ref="O27" dT="2026-08-31T17:32:55.06" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{5FDD14F3-7C62-5948-9029-841D8FA4676E}">
+  <threadedComment ref="O26" dT="2026-08-31T17:32:55.06" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{5FDD14F3-7C62-5948-9029-841D8FA4676E}" done="1">
     <text>The sessions in promise happened at different days and times - I therefore guess that this comes from aligning the sequences - to make them comparable they are given the same artificial starting date and time</text>
   </threadedComment>
-  <threadedComment ref="O27" dT="2026-09-01T14:22:01.68" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{DFF5623A-6F1E-445B-826F-2C9B5CD44E41}" parentId="{5FDD14F3-7C62-5948-9029-841D8FA4676E}">
+  <threadedComment ref="O26" dT="2026-09-01T14:22:01.68" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{DFF5623A-6F1E-445B-826F-2C9B5CD44E41}" parentId="{5FDD14F3-7C62-5948-9029-841D8FA4676E}">
     <text xml:space="preserve">This exact information about the video recordings is not available in the log anymore.
 The events are derived from the coding in maxqda, which only carries information about the time passed from the beginning of the video. To transform that into a proper timestamp, an artifical start date was set that is common for all cases (e.g., 01.01.2022 00:00:00). 
 However, I don‘t think this will stay in as evidence, as I understood that we are not using the ProMiSE Log as an example. </text>
   </threadedComment>
-  <threadedComment ref="E28" dT="2026-09-01T08:08:10.83" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{2E267686-14D6-4169-8DB8-16462DBC5A3F}">
+  <threadedComment ref="E27" dT="2026-09-01T08:08:10.83" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{2E267686-14D6-4169-8DB8-16462DBC5A3F}" done="1">
     <text>This and the above one remedy to the Suriadi „Unanchored event“ pattern</text>
   </threadedComment>
-  <threadedComment ref="C30" dT="2026-08-31T15:07:46.22" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{3877D097-A754-44CB-8262-A4154106C5B9}" done="1">
+  <threadedComment ref="C29" dT="2026-08-31T15:07:46.22" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{3877D097-A754-44CB-8262-A4154106C5B9}" done="1">
     <text>This name is not good as this is not necessarily reducing complexity - its more a refinement</text>
   </threadedComment>
-  <threadedComment ref="E30" dT="2026-09-01T08:06:33.14" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{9021A5E7-7672-4A9D-B2D2-889DA37C26B1}" done="1">
+  <threadedComment ref="E29" dT="2026-09-01T08:06:33.14" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{9021A5E7-7672-4A9D-B2D2-889DA37C26B1}" done="1">
     <text>Detection of the Suriadi „Form-based event capture“ pattern + other such cases of events being recorded with the same timestamp --&gt; “Form-based Event Capture Candidates”</text>
   </threadedComment>
-  <threadedComment ref="F30" dT="2026-08-31T14:43:05.37" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{D8030C57-2AFB-4D02-8960-7584EA109DCB}" done="1">
+  <threadedComment ref="F29" dT="2026-08-31T14:43:05.37" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{D8030C57-2AFB-4D02-8960-7584EA109DCB}" done="1">
     <text>Are these potentially batch activities</text>
   </threadedComment>
-  <threadedComment ref="F30" dT="2026-08-31T14:51:47.41" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{8902A913-155E-4899-A706-D3D8CA4722C6}" parentId="{D8030C57-2AFB-4D02-8960-7584EA109DCB}">
+  <threadedComment ref="F29" dT="2026-08-31T14:51:47.41" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{8902A913-155E-4899-A706-D3D8CA4722C6}" parentId="{D8030C57-2AFB-4D02-8960-7584EA109DCB}">
     <text>If I recall correctly, this was only considered within one case, not across cases</text>
   </threadedComment>
-  <threadedComment ref="F30" dT="2026-08-31T14:55:47.32" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{E067FA9D-CDEF-486B-98BD-73887843CD66}" parentId="{D8030C57-2AFB-4D02-8960-7584EA109DCB}">
+  <threadedComment ref="F29" dT="2026-08-31T14:55:47.32" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{E067FA9D-CDEF-486B-98BD-73887843CD66}" parentId="{D8030C57-2AFB-4D02-8960-7584EA109DCB}">
     <text>The pattern says event logs may contain .. The formulation hints towards that this is accross cases</text>
   </threadedComment>
-  <threadedComment ref="F30" dT="2026-08-31T15:12:00.98" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{075F9F80-6693-488A-A9E9-CBCBCDB70601}" parentId="{D8030C57-2AFB-4D02-8960-7584EA109DCB}">
+  <threadedComment ref="F29" dT="2026-08-31T15:12:00.98" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{075F9F80-6693-488A-A9E9-CBCBCDB70601}" parentId="{D8030C57-2AFB-4D02-8960-7584EA109DCB}">
     <text>I think the name is the problem here: 
 Concurrent Events Detection: Detect events occurring concurrently
 Batch DetectionDetect groups of events/activities executed as a batch =&gt; both can have the same timestamps but it means different things</text>
   </threadedComment>
-  <threadedComment ref="F30" dT="2026-08-31T15:13:19.04" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{57BAEA9C-2DAC-478C-BA44-AF4BD4D0C9AE}" parentId="{D8030C57-2AFB-4D02-8960-7584EA109DCB}">
+  <threadedComment ref="F29" dT="2026-08-31T15:13:19.04" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{57BAEA9C-2DAC-478C-BA44-AF4BD4D0C9AE}" parentId="{D8030C57-2AFB-4D02-8960-7584EA109DCB}">
     <text>Concurrent events have often the same timestamps; Events overlap or occur simultaneously, but are otherwise independent
 Batch events; have often the same timestamp: events are processed together as a group because they share some batching mechanism</text>
   </threadedComment>
-  <threadedComment ref="F30" dT="2026-08-31T15:13:56.78" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{82FFC416-FC16-4BD0-910C-C35B0CD59EF7}" parentId="{D8030C57-2AFB-4D02-8960-7584EA109DCB}">
+  <threadedComment ref="F29" dT="2026-08-31T15:13:56.78" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{82FFC416-FC16-4BD0-910C-C35B0CD59EF7}" parentId="{D8030C57-2AFB-4D02-8960-7584EA109DCB}">
     <text xml:space="preserve">Concurrent Events Detection: Identify events that potentially occur concurrently, e.g., based on identical or overlapping timestamps.
 Batch Detection: Identify groups of events that potentially represent joint or grouped execution, e.g., based on temporal proximity, identical timestamps, shared resources, or other batching characteristics.
 </text>
   </threadedComment>
-  <threadedComment ref="F30" dT="2026-08-31T15:40:15.96" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{8CAA59E9-395D-49E5-AE7F-CC30193BED31}" parentId="{D8030C57-2AFB-4D02-8960-7584EA109DCB}">
+  <threadedComment ref="F29" dT="2026-08-31T15:40:15.96" personId="{DD18090C-DE55-4CC1-A323-C6C9AA91D8E7}" id="{8CAA59E9-395D-49E5-AE7F-CC30193BED31}" parentId="{D8030C57-2AFB-4D02-8960-7584EA109DCB}">
     <text>This pattern should look for events occurring at the exact same time, within cases and across cases, and report on both as part of the result.</text>
   </threadedComment>
-  <threadedComment ref="F30" dT="2026-09-04T11:34:59.25" personId="{1D3666FE-8297-4003-80FC-8C5CAF30F225}" id="{F875DA62-6A02-AE44-9691-F551C047F0EC}" parentId="{D8030C57-2AFB-4D02-8960-7584EA109DCB}">
+  <threadedComment ref="F29" dT="2026-09-04T11:34:59.25" personId="{1D3666FE-8297-4003-80FC-8C5CAF30F225}" id="{F875DA62-6A02-AE44-9691-F551C047F0EC}" parentId="{D8030C57-2AFB-4D02-8960-7584EA109DCB}">
     <text>we have now both super event detection and batching</text>
   </threadedComment>
-  <threadedComment ref="F30" dT="2026-09-04T11:35:27.29" personId="{1D3666FE-8297-4003-80FC-8C5CAF30F225}" id="{6F292316-3598-214A-8102-8A449EABDA39}" parentId="{D8030C57-2AFB-4D02-8960-7584EA109DCB}">
+  <threadedComment ref="F29" dT="2026-09-04T11:35:27.29" personId="{1D3666FE-8297-4003-80FC-8C5CAF30F225}" id="{6F292316-3598-214A-8102-8A449EABDA39}" parentId="{D8030C57-2AFB-4D02-8960-7584EA109DCB}">
     <text>jupyter and marimo notebooks pushed</text>
   </threadedComment>
 </ThreadedComments>
@@ -5317,7 +5205,7 @@
   <threadedComment ref="H1" dT="2026-09-01T07:00:51.38" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{149490DA-E31D-4980-9896-F3DA2D37FB19}" parentId="{E60B19B2-08FC-0445-872E-6556AFFB0445}">
     <text>Changed ☺️ thank you for the suggestion!</text>
   </threadedComment>
-  <threadedComment ref="L1" dT="2026-09-01T07:09:15.88" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{4E012B53-F45E-43E8-807A-39F16792913A}">
+  <threadedComment ref="L1" dT="2026-09-01T07:09:15.88" personId="{BEBE2C5C-502A-41A0-A958-8C4E9BB0A6B3}" id="{4E012B53-F45E-43E8-807A-39F16792913A}" done="1">
     <text xml:space="preserve">@Franceschetti, Marco , in the approach, it says it is either added in the event log or the case table. Can you double check the output here and for the following enrichments? </text>
     <mentions>
       <mention mentionpersonId="{347771E1-58EF-44A4-B677-C217AD80543B}" mentionId="{D7DFF802-6930-44ED-B6DE-4DD3A1998A8D}" startIndex="0" length="21"/>
@@ -5355,7 +5243,7 @@
   <threadedComment ref="H3" dT="2026-08-31T17:44:20.44" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{93A69BA3-1C2B-2B46-9AC3-A3700393FC6D}" done="1">
     <text>Derive an event-level attribute solely from information contained in that event.</text>
   </threadedComment>
-  <threadedComment ref="E4" dT="2026-09-02T16:04:06.71" personId="{67619BF6-90B0-4F5A-9CB2-1D00BC01A3E8}" id="{2E258791-85CF-4C0E-B270-0FD808B902C2}">
+  <threadedComment ref="E4" dT="2026-09-02T16:04:06.71" personId="{67619BF6-90B0-4F5A-9CB2-1D00BC01A3E8}" id="{2E258791-85CF-4C0E-B270-0FD808B902C2}" done="1">
     <text>With some of the later patterns, we should be careful that we do not come across as a restaurant that offers 32 dishes but only uses the same 5 ingredients. There are some technical distinctions, which give differences in the operationalization but not in the meaning of the pattern.</text>
   </threadedComment>
   <threadedComment ref="G4" dT="2026-08-31T17:39:58.52" personId="{FAFAE72D-B38B-41E4-BD77-8993546BBD22}" id="{EC379C8F-F997-BA43-8F2D-77FA1069998C}" done="1">
@@ -5382,7 +5270,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE0A0EEE-D5C1-4957-AF8D-A06D4053E578}">
-  <dimension ref="B1:Q396"/>
+  <dimension ref="B1:Q395"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2" style="2" customWidth="1"/>
@@ -5418,45 +5306,45 @@
     </row>
     <row r="3" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F3" s="8" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G3" s="8"/>
-      <c r="H3" s="79" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" s="79"/>
-      <c r="J3" s="79"/>
+      <c r="H3" s="78" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
     <row r="4" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="E4" s="16" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G4" s="8"/>
-      <c r="H4" s="80" t="s">
-        <v>36</v>
-      </c>
-      <c r="I4" s="80"/>
-      <c r="J4" s="80"/>
+      <c r="H4" s="79" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="79"/>
+      <c r="J4" s="79"/>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
     </row>
     <row r="5" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E5" s="43" t="s">
-        <v>112</v>
+      <c r="E5" s="42" t="s">
+        <v>102</v>
       </c>
       <c r="F5" s="3"/>
-      <c r="H5" s="81" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5" s="81"/>
-      <c r="J5" s="81"/>
+      <c r="H5" s="80" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="80"/>
+      <c r="J5" s="80"/>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
@@ -5484,916 +5372,881 @@
     </row>
     <row r="9" spans="2:17" ht="53.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="4" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="Q9" s="2"/>
     </row>
-    <row r="10" spans="2:17" s="37" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:17" s="36" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="7">
         <v>0</v>
       </c>
-      <c r="C10" s="35" t="s">
-        <v>71</v>
+      <c r="C10" s="34" t="s">
+        <v>65</v>
       </c>
       <c r="D10" s="7"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="35" t="s">
-        <v>68</v>
-      </c>
-      <c r="I10" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="J10" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="K10" s="35"/>
-      <c r="L10" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="O10" s="36"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="I10" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="K10" s="34"/>
+      <c r="L10" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="M10" s="35"/>
+      <c r="N10" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="O10" s="35"/>
     </row>
     <row r="11" spans="2:17" ht="350.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="38">
+      <c r="B11" s="37">
         <v>1.1000000000000001</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="33" t="s">
-        <v>273</v>
+        <v>20</v>
+      </c>
+      <c r="E11" s="32" t="s">
+        <v>261</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="M11" s="99" t="s">
-        <v>390</v>
-      </c>
-      <c r="N11" s="42" t="s">
-        <v>88</v>
+        <v>52</v>
+      </c>
+      <c r="M11" s="98" t="s">
+        <v>375</v>
+      </c>
+      <c r="N11" s="41" t="s">
+        <v>82</v>
       </c>
       <c r="O11" s="13"/>
       <c r="P11" s="20"/>
       <c r="Q11" s="2"/>
     </row>
-    <row r="12" spans="2:17" ht="193.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="38">
+    <row r="12" spans="2:17" ht="221.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="37">
         <v>1.2</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="33" t="s">
-        <v>58</v>
+        <v>20</v>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>211</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="L12" s="59" t="s">
-        <v>158</v>
-      </c>
-      <c r="M12" s="15"/>
+        <v>119</v>
+      </c>
+      <c r="L12" s="58" t="s">
+        <v>148</v>
+      </c>
+      <c r="M12" s="98" t="s">
+        <v>370</v>
+      </c>
       <c r="N12" s="15"/>
-      <c r="O12" s="31"/>
-      <c r="P12" s="26"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="14"/>
       <c r="Q12" s="2"/>
     </row>
-    <row r="13" spans="2:17" ht="221.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="38">
+    <row r="13" spans="2:17" ht="237" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="37">
         <v>1.3</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="33" t="s">
-        <v>223</v>
+        <v>22</v>
+      </c>
+      <c r="E13" s="32" t="s">
+        <v>39</v>
       </c>
       <c r="F13" s="13" t="s">
         <v>92</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="H13" s="18" t="s">
-        <v>12</v>
+        <v>41</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>153</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>93</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="L13" s="59" t="s">
-        <v>158</v>
-      </c>
-      <c r="M13" s="99" t="s">
-        <v>385</v>
-      </c>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="14"/>
+        <v>94</v>
+      </c>
+      <c r="L13" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="P13" s="20"/>
       <c r="Q13" s="2"/>
     </row>
-    <row r="14" spans="2:17" ht="237" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:17" ht="262" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="38">
         <v>1.4</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="33" t="s">
-        <v>44</v>
+        <v>204</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="E14" s="32" t="s">
+        <v>205</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>102</v>
+        <v>207</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>46</v>
+        <v>208</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>163</v>
+        <v>7</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="J14" s="13" t="s">
-        <v>47</v>
+        <v>209</v>
+      </c>
+      <c r="J14" s="25" t="s">
+        <v>210</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="L14" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="28" t="s">
-        <v>151</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="L14" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
       <c r="P14" s="20"/>
       <c r="Q14" s="2"/>
     </row>
-    <row r="15" spans="2:17" ht="262" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="39">
-        <v>1.5</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="E15" s="33" t="s">
-        <v>217</v>
+    <row r="15" spans="2:17" ht="313" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="37">
+        <v>2.1</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>236</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="32" t="s">
+        <v>227</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>12</v>
+        <v>90</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="J15" s="25" t="s">
-        <v>222</v>
+        <v>120</v>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>36</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="20"/>
+        <v>151</v>
+      </c>
+      <c r="L15" s="18" t="s">
+        <v>261</v>
+      </c>
+      <c r="M15" s="18"/>
+      <c r="N15" s="18"/>
+      <c r="O15" s="18"/>
+      <c r="P15" s="22" t="s">
+        <v>21</v>
+      </c>
       <c r="Q15" s="2"/>
     </row>
-    <row r="16" spans="2:17" ht="313" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="38">
-        <v>2.1</v>
-      </c>
-      <c r="C16" s="34" t="s">
-        <v>248</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="33" t="s">
-        <v>239</v>
+    <row r="16" spans="2:17" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="37">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="E16" s="32" t="s">
+        <v>66</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>247</v>
+        <v>64</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="H16" s="18" t="s">
-        <v>12</v>
+        <v>244</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>63</v>
       </c>
       <c r="I16" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="J16" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="K16" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="L16" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="M16" s="98" t="s">
+        <v>370</v>
+      </c>
+      <c r="N16" s="23"/>
+      <c r="O16" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="2"/>
+    </row>
+    <row r="17" spans="2:17" ht="207.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="37">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="I17" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="J16" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="K16" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="L16" s="18" t="s">
-        <v>273</v>
-      </c>
-      <c r="M16" s="18"/>
-      <c r="N16" s="18"/>
-      <c r="O16" s="18"/>
-      <c r="P16" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q16" s="2"/>
-    </row>
-    <row r="17" spans="2:17" ht="150" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="38">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="E17" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>257</v>
-      </c>
       <c r="J17" s="13" t="s">
-        <v>258</v>
+        <v>131</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="L17" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="M17" s="99" t="s">
-        <v>385</v>
-      </c>
-      <c r="N17" s="23"/>
-      <c r="O17" s="24" t="s">
-        <v>174</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="L17" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="27"/>
       <c r="P17" s="20"/>
       <c r="Q17" s="2"/>
     </row>
-    <row r="18" spans="2:17" ht="207.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:17" ht="227" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="38">
-        <v>2.2999999999999998</v>
+        <v>2.4</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="41" t="s">
-        <v>137</v>
+        <v>236</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="32" t="s">
+        <v>240</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>138</v>
+        <v>49</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>139</v>
+        <v>241</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>140</v>
+        <v>51</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>141</v>
+        <v>87</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>250</v>
+        <v>166</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="M18" s="13"/>
       <c r="N18" s="13"/>
-      <c r="O18" s="27"/>
+      <c r="O18" s="19"/>
       <c r="P18" s="20"/>
       <c r="Q18" s="2"/>
     </row>
-    <row r="19" spans="2:17" ht="227" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="39">
-        <v>2.4</v>
+    <row r="19" spans="2:17" ht="203.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="37">
+        <v>2.5</v>
       </c>
       <c r="C19" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="40" t="s">
+        <v>237</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="I19" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="D19" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>252</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>56</v>
-      </c>
       <c r="J19" s="13" t="s">
-        <v>94</v>
+        <v>249</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="L19" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="M19" s="13"/>
-      <c r="N19" s="13"/>
-      <c r="O19" s="19"/>
+        <v>280</v>
+      </c>
+      <c r="L19" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="M19" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="N19" s="23"/>
+      <c r="O19" s="27"/>
       <c r="P19" s="20"/>
       <c r="Q19" s="2"/>
     </row>
-    <row r="20" spans="2:17" ht="203.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="38">
-        <v>2.5</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>248</v>
+    <row r="20" spans="2:17" ht="242.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="37">
+        <v>2.6</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>236</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="41" t="s">
-        <v>249</v>
+        <v>20</v>
+      </c>
+      <c r="E20" s="32" t="s">
+        <v>243</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>259</v>
+        <v>155</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>262</v>
+        <v>158</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>12</v>
+        <v>157</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>260</v>
+        <v>156</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="K20" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="L20" s="23" t="s">
-        <v>158</v>
-      </c>
-      <c r="M20" s="13" t="s">
-        <v>388</v>
-      </c>
-      <c r="N20" s="23"/>
-      <c r="O20" s="27"/>
+        <v>165</v>
+      </c>
+      <c r="K20" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="L20" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="M20" s="98" t="s">
+        <v>370</v>
+      </c>
+      <c r="N20" s="39"/>
+      <c r="O20" s="19"/>
       <c r="P20" s="20"/>
       <c r="Q20" s="2"/>
     </row>
-    <row r="21" spans="2:17" ht="242.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="38">
-        <v>2.6</v>
-      </c>
-      <c r="C21" s="34" t="s">
-        <v>248</v>
+    <row r="21" spans="2:17" ht="217" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="37">
+        <v>2.7</v>
+      </c>
+      <c r="C21" s="33" t="s">
+        <v>236</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="33" t="s">
-        <v>255</v>
+        <v>20</v>
+      </c>
+      <c r="E21" s="40" t="s">
+        <v>239</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>165</v>
+        <v>107</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>168</v>
+        <v>108</v>
       </c>
       <c r="H21" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="I21" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="I21" s="13" t="s">
-        <v>166</v>
-      </c>
       <c r="J21" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="K21" s="33" t="s">
-        <v>254</v>
-      </c>
-      <c r="L21" s="25" t="s">
-        <v>280</v>
-      </c>
-      <c r="M21" s="99" t="s">
-        <v>385</v>
-      </c>
-      <c r="N21" s="40"/>
-      <c r="O21" s="19"/>
+        <v>144</v>
+      </c>
+      <c r="K21" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="L21" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="M21" s="29"/>
+      <c r="N21" s="29"/>
+      <c r="O21" s="29"/>
       <c r="P21" s="20"/>
       <c r="Q21" s="2"/>
     </row>
-    <row r="22" spans="2:17" ht="217" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:17" ht="223.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="38">
-        <v>2.7</v>
-      </c>
-      <c r="C22" s="34" t="s">
-        <v>248</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="41" t="s">
-        <v>251</v>
+        <v>2.8</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="32" t="s">
+        <v>122</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>118</v>
+        <v>256</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>12</v>
+        <v>123</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="J22" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="J22" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="K22" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="L22" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="K22" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="L22" s="30" t="s">
-        <v>158</v>
-      </c>
-      <c r="M22" s="29"/>
-      <c r="N22" s="29"/>
-      <c r="O22" s="29"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13"/>
       <c r="P22" s="20"/>
       <c r="Q22" s="2"/>
     </row>
-    <row r="23" spans="2:17" ht="223.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="39">
-        <v>2.8</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" s="33" t="s">
-        <v>132</v>
+    <row r="23" spans="2:17" ht="229" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="37">
+        <v>3.1</v>
+      </c>
+      <c r="C23" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="32" t="s">
+        <v>228</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>268</v>
-      </c>
-      <c r="H23" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="H23" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="J23" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="K23" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="L23" s="58" t="s">
+        <v>148</v>
+      </c>
+      <c r="M23" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="N23" s="15"/>
+      <c r="O23" s="15"/>
+      <c r="P23" s="14"/>
+      <c r="Q23" s="2"/>
+    </row>
+    <row r="24" spans="2:17" ht="270" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="37">
+        <v>3.2</v>
+      </c>
+      <c r="C24" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="57" t="s">
+        <v>54</v>
+      </c>
+      <c r="F24" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="I23" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="J23" s="25" t="s">
+      <c r="G24" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="K23" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="L23" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="M23" s="13"/>
-      <c r="N23" s="13"/>
-      <c r="O23" s="13"/>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="2"/>
-    </row>
-    <row r="24" spans="2:17" ht="229" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="38">
-        <v>3.1</v>
-      </c>
-      <c r="C24" s="34" t="s">
-        <v>238</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E24" s="33" t="s">
-        <v>240</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="H24" s="18" t="s">
-        <v>12</v>
+      <c r="H24" s="13" t="s">
+        <v>159</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="J24" s="13" t="s">
-        <v>157</v>
+        <v>142</v>
+      </c>
+      <c r="J24" s="25" t="s">
+        <v>143</v>
       </c>
       <c r="K24" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="L24" s="59" t="s">
-        <v>158</v>
+        <v>152</v>
+      </c>
+      <c r="L24" s="13" t="s">
+        <v>267</v>
       </c>
       <c r="M24" s="13" t="s">
-        <v>391</v>
-      </c>
-      <c r="N24" s="15"/>
-      <c r="O24" s="15"/>
-      <c r="P24" s="14"/>
+        <v>372</v>
+      </c>
+      <c r="N24" s="23"/>
+      <c r="O24" s="23"/>
+      <c r="P24" s="20"/>
       <c r="Q24" s="2"/>
     </row>
-    <row r="25" spans="2:17" ht="270" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:17" ht="271" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="38">
-        <v>3.2</v>
-      </c>
-      <c r="C25" s="34" t="s">
-        <v>238</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E25" s="58" t="s">
-        <v>60</v>
+        <v>3.3</v>
+      </c>
+      <c r="C25" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="40" t="s">
+        <v>262</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>143</v>
+        <v>229</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>144</v>
+        <v>230</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="I25" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="J25" s="25" t="s">
-        <v>153</v>
+        <v>232</v>
+      </c>
+      <c r="I25" s="81" t="s">
+        <v>233</v>
+      </c>
+      <c r="J25" s="13" t="s">
+        <v>234</v>
       </c>
       <c r="K25" s="13" t="s">
-        <v>162</v>
+        <v>231</v>
       </c>
       <c r="L25" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="M25" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="N25" s="23"/>
-      <c r="O25" s="23"/>
+        <v>266</v>
+      </c>
+      <c r="M25" s="98" t="s">
+        <v>374</v>
+      </c>
+      <c r="N25" s="13"/>
+      <c r="O25" s="27"/>
       <c r="P25" s="20"/>
       <c r="Q25" s="2"/>
     </row>
-    <row r="26" spans="2:17" ht="271" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="39">
-        <v>3.3</v>
-      </c>
-      <c r="C26" s="34" t="s">
-        <v>238</v>
+    <row r="26" spans="2:17" ht="259.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="37">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>59</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E26" s="41" t="s">
-        <v>274</v>
+        <v>206</v>
+      </c>
+      <c r="E26" s="32" t="s">
+        <v>34</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>241</v>
+        <v>216</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="H26" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="I26" s="82" t="s">
-        <v>245</v>
+        <v>217</v>
+      </c>
+      <c r="H26" s="25" t="s">
+        <v>218</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>219</v>
       </c>
       <c r="J26" s="13" t="s">
-        <v>246</v>
+        <v>220</v>
       </c>
       <c r="K26" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="L26" s="13" t="s">
-        <v>278</v>
-      </c>
-      <c r="M26" s="99" t="s">
-        <v>389</v>
-      </c>
-      <c r="N26" s="13"/>
-      <c r="O26" s="27"/>
-      <c r="P26" s="20"/>
+        <v>96</v>
+      </c>
+      <c r="L26" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="M26" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="P26" s="26" t="s">
+        <v>121</v>
+      </c>
       <c r="Q26" s="2"/>
     </row>
-    <row r="27" spans="2:17" ht="259.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:17" ht="268.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="38">
-        <v>4.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="E27" s="33" t="s">
-        <v>39</v>
+        <v>59</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="32" t="s">
+        <v>160</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>228</v>
+        <v>161</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="H27" s="25" t="s">
-        <v>230</v>
-      </c>
-      <c r="I27" s="13" t="s">
-        <v>231</v>
+        <v>162</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="I27" s="59" t="s">
+        <v>163</v>
       </c>
       <c r="J27" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="K27" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="L27" s="25" t="s">
-        <v>158</v>
+        <v>70</v>
+      </c>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="M27" s="25" t="s">
-        <v>384</v>
-      </c>
-      <c r="N27" s="19"/>
-      <c r="O27" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="P27" s="26" t="s">
-        <v>131</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13"/>
+      <c r="P27" s="20"/>
       <c r="Q27" s="2"/>
     </row>
-    <row r="28" spans="2:17" ht="268.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="39">
-        <v>4.2</v>
+    <row r="28" spans="2:17" ht="251" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="37">
+        <v>4.3</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E28" s="33" t="s">
-        <v>170</v>
+        <v>59</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="E28" s="40" t="s">
+        <v>53</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>171</v>
+        <v>221</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>172</v>
+        <v>222</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="I28" s="60" t="s">
-        <v>173</v>
+        <v>223</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>224</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="K28" s="13"/>
-      <c r="L28" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="M28" s="25" t="s">
-        <v>383</v>
-      </c>
-      <c r="N28" s="13"/>
-      <c r="O28" s="13"/>
+        <v>225</v>
+      </c>
+      <c r="K28" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L28" s="25" t="s">
+        <v>264</v>
+      </c>
+      <c r="M28" s="30"/>
+      <c r="N28" s="30"/>
+      <c r="O28" s="29"/>
       <c r="P28" s="20"/>
       <c r="Q28" s="2"/>
     </row>
-    <row r="29" spans="2:17" ht="251" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:17" ht="209.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="38">
-        <v>4.3</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="E29" s="41" t="s">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C29" s="33" t="s">
         <v>59</v>
       </c>
+      <c r="D29" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="32" t="s">
+        <v>265</v>
+      </c>
       <c r="F29" s="13" t="s">
-        <v>233</v>
+        <v>135</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>234</v>
+        <v>136</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>235</v>
+        <v>137</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="J29" s="13" t="s">
-        <v>237</v>
+        <v>138</v>
+      </c>
+      <c r="J29" s="25" t="s">
+        <v>139</v>
       </c>
       <c r="K29" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="L29" s="25" t="s">
-        <v>276</v>
-      </c>
-      <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
-      <c r="O29" s="29"/>
+        <v>140</v>
+      </c>
+      <c r="L29" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="M29" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13"/>
       <c r="P29" s="20"/>
       <c r="Q29" s="2"/>
     </row>
-    <row r="30" spans="2:17" ht="209.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="39">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C30" s="34" t="s">
-        <v>65</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E30" s="33" t="s">
-        <v>277</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="G30" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="I30" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="J30" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="L30" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="M30" s="13" t="s">
-        <v>382</v>
-      </c>
-      <c r="N30" s="13"/>
-      <c r="O30" s="13"/>
-      <c r="P30" s="20"/>
+    <row r="30" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="O30" s="3"/>
+      <c r="P30"/>
       <c r="Q30" s="2"/>
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.35">
@@ -6412,26 +6265,26 @@
       <c r="Q33" s="2"/>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="O34" s="3"/>
-      <c r="P34"/>
+      <c r="B34" s="77"/>
+      <c r="C34" s="77"/>
+      <c r="D34" s="77"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="K34" s="11"/>
       <c r="Q34" s="2"/>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B35" s="78"/>
-      <c r="C35" s="78"/>
-      <c r="D35" s="78"/>
-      <c r="E35" s="2"/>
       <c r="F35" s="2"/>
-      <c r="K35" s="11"/>
       <c r="Q35" s="2"/>
     </row>
     <row r="36" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="F36" s="2"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="21"/>
       <c r="Q36" s="2"/>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.35">
       <c r="E37" s="14"/>
-      <c r="F37" s="21"/>
+      <c r="F37" s="14"/>
       <c r="Q37" s="2"/>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.35">
@@ -6440,29 +6293,28 @@
       <c r="Q38" s="2"/>
     </row>
     <row r="39" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="E39" s="14"/>
+      <c r="E39" s="31"/>
       <c r="F39" s="14"/>
       <c r="Q39" s="2"/>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="E40" s="32"/>
+      <c r="E40" s="31"/>
       <c r="F40" s="14"/>
       <c r="Q40" s="2"/>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="E41" s="32"/>
-      <c r="F41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="26"/>
+      <c r="H41" s="12"/>
       <c r="Q41" s="2"/>
     </row>
     <row r="42" spans="2:17" x14ac:dyDescent="0.35">
       <c r="E42" s="14"/>
-      <c r="F42" s="26"/>
-      <c r="H42" s="12"/>
+      <c r="F42" s="14"/>
       <c r="Q42" s="2"/>
     </row>
     <row r="43" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
+      <c r="F43" s="2"/>
       <c r="Q43" s="2"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.35">
@@ -7873,13 +7725,9 @@
       <c r="F395" s="2"/>
       <c r="Q395" s="2"/>
     </row>
-    <row r="396" spans="6:17" x14ac:dyDescent="0.35">
-      <c r="F396" s="2"/>
-      <c r="Q396" s="2"/>
-    </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="H4:J4"/>
     <mergeCell ref="H5:J5"/>
@@ -7898,1145 +7746,1119 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF527B26-9CE4-479E-898E-665E6D4731AE}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.7265625" customWidth="1"/>
     <col min="2" max="2" width="25.81640625" customWidth="1"/>
     <col min="3" max="3" width="39.81640625" customWidth="1"/>
-    <col min="4" max="4" width="28.453125" style="56" customWidth="1"/>
+    <col min="4" max="4" width="28.453125" style="55" customWidth="1"/>
     <col min="5" max="13" width="28.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="61" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="62" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="62" t="s">
-        <v>142</v>
-      </c>
-      <c r="C1" s="62" t="s">
+    <row r="1" spans="1:13" s="60" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="61" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" s="61" t="s">
+        <v>174</v>
+      </c>
+      <c r="D1" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="61" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="61" t="s">
+        <v>175</v>
+      </c>
+      <c r="I1" s="61" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="61" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="61" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="61" t="s">
+        <v>178</v>
+      </c>
+      <c r="M1" s="61" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="64" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="66">
+        <v>1</v>
+      </c>
+      <c r="B2" s="65" t="s">
+        <v>204</v>
+      </c>
+      <c r="C2" s="67"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+    </row>
+    <row r="3" spans="1:13" ht="233" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="63">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B3" s="63" t="s">
+        <v>204</v>
+      </c>
+      <c r="C3" s="63" t="s">
+        <v>261</v>
+      </c>
+      <c r="D3" s="74" t="s">
+        <v>269</v>
+      </c>
+      <c r="E3" s="62" t="s">
+        <v>286</v>
+      </c>
+      <c r="F3" s="62" t="s">
+        <v>287</v>
+      </c>
+      <c r="G3" s="62" t="s">
+        <v>329</v>
+      </c>
+      <c r="H3" s="62" t="s">
+        <v>303</v>
+      </c>
+      <c r="I3" s="62" t="s">
+        <v>302</v>
+      </c>
+      <c r="J3" s="62" t="s">
+        <v>328</v>
+      </c>
+      <c r="K3" s="62" t="s">
+        <v>364</v>
+      </c>
+      <c r="L3" s="62" t="s">
+        <v>194</v>
+      </c>
+      <c r="M3" s="62" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="210" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="63">
+        <v>1.2</v>
+      </c>
+      <c r="B4" s="63" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4" s="63" t="s">
+        <v>211</v>
+      </c>
+      <c r="D4" s="74" t="s">
+        <v>348</v>
+      </c>
+      <c r="E4" s="62" t="s">
+        <v>349</v>
+      </c>
+      <c r="F4" s="62" t="s">
+        <v>350</v>
+      </c>
+      <c r="G4" s="62" t="s">
+        <v>331</v>
+      </c>
+      <c r="H4" s="62" t="s">
+        <v>181</v>
+      </c>
+      <c r="I4" s="62" t="s">
+        <v>351</v>
+      </c>
+      <c r="J4" s="62" t="s">
+        <v>352</v>
+      </c>
+      <c r="K4" s="62" t="s">
+        <v>353</v>
+      </c>
+      <c r="L4" s="62" t="s">
+        <v>385</v>
+      </c>
+      <c r="M4" s="62" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" s="69" customFormat="1" ht="183" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="63">
+        <v>1.3</v>
+      </c>
+      <c r="B5" s="63" t="s">
+        <v>204</v>
+      </c>
+      <c r="C5" s="63" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="74" t="s">
+        <v>196</v>
+      </c>
+      <c r="E5" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="62" t="s">
+        <v>299</v>
+      </c>
+      <c r="G5" s="62" t="s">
+        <v>332</v>
+      </c>
+      <c r="H5" s="62" t="s">
+        <v>169</v>
+      </c>
+      <c r="I5" s="62" t="s">
+        <v>346</v>
+      </c>
+      <c r="J5" s="62" t="s">
+        <v>345</v>
+      </c>
+      <c r="K5" s="62" t="s">
+        <v>366</v>
+      </c>
+      <c r="L5" s="62" t="s">
+        <v>195</v>
+      </c>
+      <c r="M5" s="62" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="111.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="63">
+        <v>1.4</v>
+      </c>
+      <c r="B6" s="63" t="s">
+        <v>204</v>
+      </c>
+      <c r="C6" s="63" t="s">
+        <v>205</v>
+      </c>
+      <c r="D6" s="74" t="s">
+        <v>312</v>
+      </c>
+      <c r="E6" s="62" t="s">
+        <v>193</v>
+      </c>
+      <c r="F6" s="62" t="s">
+        <v>192</v>
+      </c>
+      <c r="G6" s="62" t="s">
+        <v>312</v>
+      </c>
+      <c r="H6" s="62" t="s">
+        <v>312</v>
+      </c>
+      <c r="I6" s="62" t="s">
+        <v>312</v>
+      </c>
+      <c r="J6" s="62" t="s">
+        <v>312</v>
+      </c>
+      <c r="K6" s="97" t="s">
+        <v>173</v>
+      </c>
+      <c r="L6" s="62" t="s">
+        <v>386</v>
+      </c>
+      <c r="M6" s="62" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="66">
+        <v>2</v>
+      </c>
+      <c r="B7" s="65" t="s">
+        <v>236</v>
+      </c>
+      <c r="C7" s="67"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="68"/>
+      <c r="J7" s="68"/>
+      <c r="K7" s="68"/>
+      <c r="L7" s="68"/>
+      <c r="M7" s="68"/>
+    </row>
+    <row r="8" spans="1:13" ht="163.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="63">
+        <v>2.1</v>
+      </c>
+      <c r="B8" s="63" t="s">
+        <v>236</v>
+      </c>
+      <c r="C8" s="63" t="s">
+        <v>227</v>
+      </c>
+      <c r="D8" s="74" t="s">
+        <v>277</v>
+      </c>
+      <c r="E8" s="74" t="s">
+        <v>183</v>
+      </c>
+      <c r="F8" s="62" t="s">
+        <v>291</v>
+      </c>
+      <c r="G8" s="62" t="s">
+        <v>339</v>
+      </c>
+      <c r="H8" s="62" t="s">
+        <v>176</v>
+      </c>
+      <c r="I8" s="62" t="s">
+        <v>182</v>
+      </c>
+      <c r="J8" s="62" t="s">
+        <v>182</v>
+      </c>
+      <c r="K8" s="62" t="s">
+        <v>377</v>
+      </c>
+      <c r="L8" s="62" t="s">
+        <v>294</v>
+      </c>
+      <c r="M8" s="62" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="146" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="63">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9" s="63" t="s">
+        <v>236</v>
+      </c>
+      <c r="C9" s="63" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="74" t="s">
+        <v>190</v>
+      </c>
+      <c r="E9" s="62" t="s">
+        <v>298</v>
+      </c>
+      <c r="F9" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="62" t="s">
+        <v>340</v>
+      </c>
+      <c r="H9" s="62" t="s">
+        <v>176</v>
+      </c>
+      <c r="I9" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="J9" s="62" t="s">
+        <v>333</v>
+      </c>
+      <c r="K9" s="62" t="s">
+        <v>378</v>
+      </c>
+      <c r="L9" s="82" t="s">
+        <v>251</v>
+      </c>
+      <c r="M9" s="62" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="253.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="63">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="B10" s="63" t="s">
+        <v>236</v>
+      </c>
+      <c r="C10" s="63" t="s">
+        <v>127</v>
+      </c>
+      <c r="D10" s="74" t="s">
+        <v>273</v>
+      </c>
+      <c r="E10" s="62" t="s">
+        <v>306</v>
+      </c>
+      <c r="F10" s="62" t="s">
+        <v>295</v>
+      </c>
+      <c r="G10" s="62" t="s">
+        <v>357</v>
+      </c>
+      <c r="H10" s="62" t="s">
+        <v>384</v>
+      </c>
+      <c r="I10" s="62" t="s">
+        <v>305</v>
+      </c>
+      <c r="J10" s="62" t="s">
+        <v>341</v>
+      </c>
+      <c r="K10" s="62" t="s">
+        <v>382</v>
+      </c>
+      <c r="L10" s="62" t="s">
+        <v>317</v>
+      </c>
+      <c r="M10" s="62" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="113" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="63">
+        <v>2.4</v>
+      </c>
+      <c r="B11" s="63" t="s">
+        <v>236</v>
+      </c>
+      <c r="C11" s="63" t="s">
+        <v>240</v>
+      </c>
+      <c r="D11" s="74" t="s">
+        <v>284</v>
+      </c>
+      <c r="E11" s="96" t="s">
+        <v>284</v>
+      </c>
+      <c r="F11" s="62" t="s">
+        <v>300</v>
+      </c>
+      <c r="G11" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="H11" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="I11" s="62" t="s">
+        <v>301</v>
+      </c>
+      <c r="J11" s="62" t="s">
+        <v>335</v>
+      </c>
+      <c r="K11" s="62" t="s">
+        <v>361</v>
+      </c>
+      <c r="L11" s="62" t="s">
+        <v>315</v>
+      </c>
+      <c r="M11" s="62" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="149.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="63">
+        <v>2.5</v>
+      </c>
+      <c r="B12" s="63" t="s">
+        <v>236</v>
+      </c>
+      <c r="C12" s="63" t="s">
+        <v>237</v>
+      </c>
+      <c r="D12" s="74" t="s">
+        <v>270</v>
+      </c>
+      <c r="E12" s="62" t="s">
+        <v>271</v>
+      </c>
+      <c r="F12" s="62" t="s">
+        <v>292</v>
+      </c>
+      <c r="G12" s="92" t="s">
+        <v>347</v>
+      </c>
+      <c r="H12" s="62" t="s">
+        <v>383</v>
+      </c>
+      <c r="I12" s="62" t="s">
+        <v>304</v>
+      </c>
+      <c r="J12" s="62" t="s">
+        <v>337</v>
+      </c>
+      <c r="K12" s="62" t="s">
+        <v>371</v>
+      </c>
+      <c r="L12" s="62" t="s">
+        <v>316</v>
+      </c>
+      <c r="M12" s="62" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="180" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="63">
+        <v>2.6</v>
+      </c>
+      <c r="B13" s="63" t="s">
+        <v>236</v>
+      </c>
+      <c r="C13" s="63" t="s">
+        <v>243</v>
+      </c>
+      <c r="D13" s="74" t="s">
+        <v>203</v>
+      </c>
+      <c r="E13" s="62" t="s">
+        <v>202</v>
+      </c>
+      <c r="F13" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="G13" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="H13" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="I13" s="62" t="s">
+        <v>191</v>
+      </c>
+      <c r="J13" s="62" t="s">
+        <v>380</v>
+      </c>
+      <c r="K13" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="L13" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="M13" s="62" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" s="69" customFormat="1" ht="187.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="63">
+        <v>2.7</v>
+      </c>
+      <c r="B14" s="63" t="s">
+        <v>236</v>
+      </c>
+      <c r="C14" s="63" t="s">
+        <v>239</v>
+      </c>
+      <c r="D14" s="74" t="s">
+        <v>189</v>
+      </c>
+      <c r="E14" s="62" t="s">
+        <v>330</v>
+      </c>
+      <c r="F14" s="62" t="s">
+        <v>293</v>
+      </c>
+      <c r="G14" s="62" t="s">
+        <v>182</v>
+      </c>
+      <c r="H14" s="62" t="s">
+        <v>182</v>
+      </c>
+      <c r="I14" s="62" t="s">
+        <v>182</v>
+      </c>
+      <c r="J14" s="62" t="s">
+        <v>327</v>
+      </c>
+      <c r="K14" s="62" t="s">
+        <v>182</v>
+      </c>
+      <c r="L14" s="62" t="s">
+        <v>318</v>
+      </c>
+      <c r="M14" s="62" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="129.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="63">
+        <v>2.8</v>
+      </c>
+      <c r="B15" s="63" t="s">
+        <v>236</v>
+      </c>
+      <c r="C15" s="63" t="s">
+        <v>122</v>
+      </c>
+      <c r="D15" s="74" t="s">
+        <v>274</v>
+      </c>
+      <c r="E15" s="62" t="s">
+        <v>283</v>
+      </c>
+      <c r="F15" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="G15" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="H15" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="I15" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="J15" s="62" t="s">
+        <v>365</v>
+      </c>
+      <c r="K15" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="L15" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="M15" s="62" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="64">
+        <v>3</v>
+      </c>
+      <c r="B16" s="65" t="s">
+        <v>226</v>
+      </c>
+      <c r="C16" s="64"/>
+      <c r="D16" s="73"/>
+      <c r="E16" s="64"/>
+      <c r="F16" s="64"/>
+      <c r="G16" s="64"/>
+      <c r="H16" s="64"/>
+      <c r="I16" s="64"/>
+      <c r="J16" s="64"/>
+      <c r="K16" s="64"/>
+      <c r="L16" s="64"/>
+      <c r="M16" s="64"/>
+    </row>
+    <row r="17" spans="1:13" ht="260" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="63">
+        <v>3.1</v>
+      </c>
+      <c r="B17" s="63" t="s">
+        <v>226</v>
+      </c>
+      <c r="C17" s="63" t="s">
+        <v>228</v>
+      </c>
+      <c r="D17" s="74" t="s">
+        <v>281</v>
+      </c>
+      <c r="E17" s="62" t="s">
+        <v>282</v>
+      </c>
+      <c r="F17" s="62" t="s">
+        <v>296</v>
+      </c>
+      <c r="G17" s="62" t="s">
+        <v>336</v>
+      </c>
+      <c r="H17" s="62" t="s">
+        <v>170</v>
+      </c>
+      <c r="I17" s="62" t="s">
+        <v>307</v>
+      </c>
+      <c r="J17" s="62" t="s">
+        <v>184</v>
+      </c>
+      <c r="K17" s="62" t="s">
+        <v>362</v>
+      </c>
+      <c r="L17" s="62" t="s">
+        <v>387</v>
+      </c>
+      <c r="M17" s="62" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="218.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="95">
+        <v>3.2</v>
+      </c>
+      <c r="B18" s="63" t="s">
+        <v>226</v>
+      </c>
+      <c r="C18" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="96" t="s">
+        <v>279</v>
+      </c>
+      <c r="E18" s="62" t="s">
+        <v>278</v>
+      </c>
+      <c r="F18" s="62" t="s">
+        <v>297</v>
+      </c>
+      <c r="G18" s="62" t="s">
+        <v>186</v>
+      </c>
+      <c r="H18" s="62" t="s">
+        <v>171</v>
+      </c>
+      <c r="I18" s="62" t="s">
+        <v>309</v>
+      </c>
+      <c r="J18" s="62" t="s">
         <v>185</v>
       </c>
-      <c r="D1" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="62" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="62" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="62" t="s">
-        <v>186</v>
-      </c>
-      <c r="I1" s="62" t="s">
+      <c r="K18" s="62" t="s">
+        <v>363</v>
+      </c>
+      <c r="L18" s="62" t="s">
+        <v>289</v>
+      </c>
+      <c r="M18" s="62" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="218.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="63">
+        <v>3.3</v>
+      </c>
+      <c r="B19" s="63" t="s">
+        <v>226</v>
+      </c>
+      <c r="C19" s="63" t="s">
+        <v>262</v>
+      </c>
+      <c r="D19" s="74" t="s">
+        <v>188</v>
+      </c>
+      <c r="E19" s="62" t="s">
+        <v>187</v>
+      </c>
+      <c r="F19" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="G19" s="62" t="s">
+        <v>338</v>
+      </c>
+      <c r="H19" s="62" t="s">
+        <v>172</v>
+      </c>
+      <c r="I19" s="62" t="s">
+        <v>308</v>
+      </c>
+      <c r="J19" s="62" t="s">
+        <v>344</v>
+      </c>
+      <c r="K19" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="L19" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="M19" s="62" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" s="71" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="67">
         <v>4</v>
       </c>
-      <c r="J1" s="62" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="62" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" s="62" t="s">
-        <v>189</v>
-      </c>
-      <c r="M1" s="62" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" s="65" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="67">
-        <v>1</v>
-      </c>
-      <c r="B2" s="66" t="s">
-        <v>216</v>
-      </c>
-      <c r="C2" s="68"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-    </row>
-    <row r="3" spans="1:13" ht="233" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="64">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B3" s="64" t="s">
-        <v>216</v>
-      </c>
-      <c r="C3" s="64" t="s">
-        <v>273</v>
-      </c>
-      <c r="D3" s="75" t="s">
-        <v>281</v>
-      </c>
-      <c r="E3" s="63" t="s">
-        <v>298</v>
-      </c>
-      <c r="F3" s="63" t="s">
-        <v>299</v>
-      </c>
-      <c r="G3" s="63" t="s">
+      <c r="B20" s="65" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="67"/>
+      <c r="D20" s="76"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="70"/>
+      <c r="K20" s="70"/>
+      <c r="L20" s="70"/>
+      <c r="M20" s="70"/>
+    </row>
+    <row r="21" spans="1:13" ht="240.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="63">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B21" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="63" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="74" t="s">
+        <v>199</v>
+      </c>
+      <c r="E21" s="62" t="s">
+        <v>355</v>
+      </c>
+      <c r="F21" s="62" t="s">
+        <v>356</v>
+      </c>
+      <c r="G21" s="62" t="s">
+        <v>197</v>
+      </c>
+      <c r="H21" s="62" t="s">
+        <v>179</v>
+      </c>
+      <c r="I21" s="62" t="s">
+        <v>355</v>
+      </c>
+      <c r="J21" s="62" t="s">
+        <v>358</v>
+      </c>
+      <c r="K21" s="62" t="s">
+        <v>198</v>
+      </c>
+      <c r="L21" s="62" t="s">
+        <v>359</v>
+      </c>
+      <c r="M21" s="62" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="74.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="63">
+        <v>4.2</v>
+      </c>
+      <c r="B22" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="63" t="s">
+        <v>160</v>
+      </c>
+      <c r="D22" s="74" t="s">
+        <v>288</v>
+      </c>
+      <c r="E22" s="62" t="s">
+        <v>276</v>
+      </c>
+      <c r="F22" s="62" t="s">
+        <v>276</v>
+      </c>
+      <c r="G22" s="62" t="s">
+        <v>276</v>
+      </c>
+      <c r="H22" s="62" t="s">
+        <v>276</v>
+      </c>
+      <c r="I22" s="62" t="s">
+        <v>276</v>
+      </c>
+      <c r="J22" s="62" t="s">
+        <v>276</v>
+      </c>
+      <c r="K22" s="62" t="s">
+        <v>276</v>
+      </c>
+      <c r="L22" s="62" t="s">
+        <v>276</v>
+      </c>
+      <c r="M22" s="62" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="95">
+        <v>4.3</v>
+      </c>
+      <c r="B23" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="74" t="s">
+        <v>168</v>
+      </c>
+      <c r="E23" s="62" t="s">
+        <v>168</v>
+      </c>
+      <c r="F23" s="62" t="s">
+        <v>168</v>
+      </c>
+      <c r="G23" s="62" t="s">
+        <v>168</v>
+      </c>
+      <c r="H23" s="62" t="s">
+        <v>168</v>
+      </c>
+      <c r="I23" s="62" t="s">
+        <v>168</v>
+      </c>
+      <c r="J23" s="62" t="s">
+        <v>168</v>
+      </c>
+      <c r="K23" s="62" t="s">
+        <v>310</v>
+      </c>
+      <c r="L23" s="62" t="s">
+        <v>168</v>
+      </c>
+      <c r="M23" s="62" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="338" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="63">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="B24" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="63" t="s">
+        <v>265</v>
+      </c>
+      <c r="D24" s="96" t="s">
+        <v>275</v>
+      </c>
+      <c r="E24" s="62" t="s">
+        <v>200</v>
+      </c>
+      <c r="F24" s="62" t="s">
+        <v>290</v>
+      </c>
+      <c r="G24" s="62" t="s">
+        <v>334</v>
+      </c>
+      <c r="H24" s="62" t="s">
+        <v>180</v>
+      </c>
+      <c r="I24" s="62" t="s">
+        <v>311</v>
+      </c>
+      <c r="J24" s="62" t="s">
         <v>343</v>
       </c>
-      <c r="H3" s="63" t="s">
-        <v>316</v>
-      </c>
-      <c r="I3" s="63" t="s">
-        <v>315</v>
-      </c>
-      <c r="J3" s="63" t="s">
-        <v>342</v>
-      </c>
-      <c r="K3" s="63" t="s">
-        <v>378</v>
-      </c>
-      <c r="L3" s="63" t="s">
-        <v>205</v>
-      </c>
-      <c r="M3" s="63" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="137" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="64">
-        <v>1.2</v>
-      </c>
-      <c r="B4" s="64" t="s">
-        <v>216</v>
-      </c>
-      <c r="C4" s="64" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="75" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="63" t="s">
-        <v>206</v>
-      </c>
-      <c r="F4" s="63" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="63" t="s">
-        <v>179</v>
-      </c>
-      <c r="I4" s="63" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="63" t="s">
-        <v>11</v>
-      </c>
-      <c r="K4" s="63" t="s">
+      <c r="K24" s="62" t="s">
         <v>379</v>
       </c>
-      <c r="L4" s="63" t="s">
-        <v>303</v>
-      </c>
-      <c r="M4" s="63" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="210" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="64">
-        <v>1.3</v>
-      </c>
-      <c r="B5" s="64" t="s">
-        <v>216</v>
-      </c>
-      <c r="C5" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="D5" s="75" t="s">
-        <v>362</v>
-      </c>
-      <c r="E5" s="63" t="s">
-        <v>363</v>
-      </c>
-      <c r="F5" s="63" t="s">
-        <v>364</v>
-      </c>
-      <c r="G5" s="63" t="s">
-        <v>345</v>
-      </c>
-      <c r="H5" s="63" t="s">
-        <v>192</v>
-      </c>
-      <c r="I5" s="63" t="s">
-        <v>365</v>
-      </c>
-      <c r="J5" s="63" t="s">
-        <v>366</v>
-      </c>
-      <c r="K5" s="63" t="s">
-        <v>367</v>
-      </c>
-      <c r="L5" s="63" t="s">
-        <v>400</v>
-      </c>
-      <c r="M5" s="63" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" s="70" customFormat="1" ht="183" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="64">
-        <v>1.4</v>
-      </c>
-      <c r="B6" s="64" t="s">
-        <v>216</v>
-      </c>
-      <c r="C6" s="64" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="75" t="s">
-        <v>208</v>
-      </c>
-      <c r="E6" s="63" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="63" t="s">
-        <v>312</v>
-      </c>
-      <c r="G6" s="63" t="s">
-        <v>346</v>
-      </c>
-      <c r="H6" s="63" t="s">
-        <v>180</v>
-      </c>
-      <c r="I6" s="63" t="s">
-        <v>360</v>
-      </c>
-      <c r="J6" s="63" t="s">
-        <v>359</v>
-      </c>
-      <c r="K6" s="63" t="s">
-        <v>381</v>
-      </c>
-      <c r="L6" s="63" t="s">
-        <v>207</v>
-      </c>
-      <c r="M6" s="63" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="111.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="64">
-        <v>1.5</v>
-      </c>
-      <c r="B7" s="64" t="s">
-        <v>216</v>
-      </c>
-      <c r="C7" s="64" t="s">
-        <v>217</v>
-      </c>
-      <c r="D7" s="75" t="s">
-        <v>326</v>
-      </c>
-      <c r="E7" s="63" t="s">
-        <v>204</v>
-      </c>
-      <c r="F7" s="63" t="s">
-        <v>203</v>
-      </c>
-      <c r="G7" s="63" t="s">
-        <v>326</v>
-      </c>
-      <c r="H7" s="63" t="s">
-        <v>326</v>
-      </c>
-      <c r="I7" s="63" t="s">
-        <v>326</v>
-      </c>
-      <c r="J7" s="63" t="s">
-        <v>326</v>
-      </c>
-      <c r="K7" s="98" t="s">
-        <v>184</v>
-      </c>
-      <c r="L7" s="63" t="s">
-        <v>401</v>
-      </c>
-      <c r="M7" s="63" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="67">
-        <v>2</v>
-      </c>
-      <c r="B8" s="66" t="s">
-        <v>248</v>
-      </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="76"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="69"/>
-      <c r="M8" s="69"/>
-    </row>
-    <row r="9" spans="1:13" ht="163.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="64">
-        <v>2.1</v>
-      </c>
-      <c r="B9" s="64" t="s">
-        <v>248</v>
-      </c>
-      <c r="C9" s="64" t="s">
-        <v>239</v>
-      </c>
-      <c r="D9" s="75" t="s">
-        <v>289</v>
-      </c>
-      <c r="E9" s="75" t="s">
-        <v>194</v>
-      </c>
-      <c r="F9" s="63" t="s">
-        <v>304</v>
-      </c>
-      <c r="G9" s="63" t="s">
-        <v>353</v>
-      </c>
-      <c r="H9" s="63" t="s">
-        <v>187</v>
-      </c>
-      <c r="I9" s="63" t="s">
-        <v>193</v>
-      </c>
-      <c r="J9" s="63" t="s">
-        <v>193</v>
-      </c>
-      <c r="K9" s="63" t="s">
-        <v>392</v>
-      </c>
-      <c r="L9" s="63" t="s">
-        <v>307</v>
-      </c>
-      <c r="M9" s="63" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="146" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="64">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="B10" s="64" t="s">
-        <v>248</v>
-      </c>
-      <c r="C10" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" s="75" t="s">
+      <c r="L24" s="62" t="s">
+        <v>285</v>
+      </c>
+      <c r="M24" s="62" t="s">
         <v>201</v>
       </c>
-      <c r="E10" s="63" t="s">
-        <v>311</v>
-      </c>
-      <c r="F10" s="63" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="63" t="s">
-        <v>354</v>
-      </c>
-      <c r="H10" s="63" t="s">
-        <v>187</v>
-      </c>
-      <c r="I10" s="63" t="s">
-        <v>12</v>
-      </c>
-      <c r="J10" s="63" t="s">
-        <v>347</v>
-      </c>
-      <c r="K10" s="63" t="s">
-        <v>393</v>
-      </c>
-      <c r="L10" s="83" t="s">
-        <v>263</v>
-      </c>
-      <c r="M10" s="63" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="253.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="64">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="B11" s="64" t="s">
-        <v>248</v>
-      </c>
-      <c r="C11" s="64" t="s">
-        <v>137</v>
-      </c>
-      <c r="D11" s="75" t="s">
-        <v>285</v>
-      </c>
-      <c r="E11" s="63" t="s">
-        <v>319</v>
-      </c>
-      <c r="F11" s="63" t="s">
-        <v>308</v>
-      </c>
-      <c r="G11" s="63" t="s">
-        <v>371</v>
-      </c>
-      <c r="H11" s="63" t="s">
-        <v>399</v>
-      </c>
-      <c r="I11" s="63" t="s">
-        <v>318</v>
-      </c>
-      <c r="J11" s="63" t="s">
-        <v>355</v>
-      </c>
-      <c r="K11" s="63" t="s">
-        <v>397</v>
-      </c>
-      <c r="L11" s="63" t="s">
-        <v>331</v>
-      </c>
-      <c r="M11" s="63" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="113" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="64">
-        <v>2.4</v>
-      </c>
-      <c r="B12" s="64" t="s">
-        <v>248</v>
-      </c>
-      <c r="C12" s="64" t="s">
-        <v>252</v>
-      </c>
-      <c r="D12" s="75" t="s">
-        <v>296</v>
-      </c>
-      <c r="E12" s="97" t="s">
-        <v>296</v>
-      </c>
-      <c r="F12" s="63" t="s">
-        <v>313</v>
-      </c>
-      <c r="G12" s="63" t="s">
-        <v>12</v>
-      </c>
-      <c r="H12" s="63" t="s">
-        <v>12</v>
-      </c>
-      <c r="I12" s="63" t="s">
-        <v>314</v>
-      </c>
-      <c r="J12" s="63" t="s">
-        <v>349</v>
-      </c>
-      <c r="K12" s="63" t="s">
-        <v>375</v>
-      </c>
-      <c r="L12" s="63" t="s">
-        <v>329</v>
-      </c>
-      <c r="M12" s="63" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="149.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="64">
-        <v>2.5</v>
-      </c>
-      <c r="B13" s="64" t="s">
-        <v>248</v>
-      </c>
-      <c r="C13" s="64" t="s">
-        <v>249</v>
-      </c>
-      <c r="D13" s="75" t="s">
-        <v>282</v>
-      </c>
-      <c r="E13" s="63" t="s">
-        <v>283</v>
-      </c>
-      <c r="F13" s="63" t="s">
-        <v>305</v>
-      </c>
-      <c r="G13" s="93" t="s">
-        <v>361</v>
-      </c>
-      <c r="H13" s="63" t="s">
-        <v>398</v>
-      </c>
-      <c r="I13" s="63" t="s">
-        <v>317</v>
-      </c>
-      <c r="J13" s="63" t="s">
-        <v>351</v>
-      </c>
-      <c r="K13" s="63" t="s">
-        <v>386</v>
-      </c>
-      <c r="L13" s="63" t="s">
-        <v>330</v>
-      </c>
-      <c r="M13" s="63" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="180" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="64">
-        <v>2.6</v>
-      </c>
-      <c r="B14" s="64" t="s">
-        <v>248</v>
-      </c>
-      <c r="C14" s="64" t="s">
-        <v>255</v>
-      </c>
-      <c r="D14" s="75" t="s">
-        <v>215</v>
-      </c>
-      <c r="E14" s="63" t="s">
-        <v>214</v>
-      </c>
-      <c r="F14" s="63" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="63" t="s">
-        <v>12</v>
-      </c>
-      <c r="H14" s="63" t="s">
-        <v>12</v>
-      </c>
-      <c r="I14" s="63" t="s">
-        <v>202</v>
-      </c>
-      <c r="J14" s="63" t="s">
-        <v>395</v>
-      </c>
-      <c r="K14" s="63" t="s">
-        <v>12</v>
-      </c>
-      <c r="L14" s="63" t="s">
-        <v>396</v>
-      </c>
-      <c r="M14" s="63" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" s="70" customFormat="1" ht="187.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="64">
-        <v>2.7</v>
-      </c>
-      <c r="B15" s="64" t="s">
-        <v>248</v>
-      </c>
-      <c r="C15" s="64" t="s">
-        <v>251</v>
-      </c>
-      <c r="D15" s="75" t="s">
-        <v>200</v>
-      </c>
-      <c r="E15" s="63" t="s">
-        <v>344</v>
-      </c>
-      <c r="F15" s="63" t="s">
-        <v>306</v>
-      </c>
-      <c r="G15" s="63" t="s">
-        <v>193</v>
-      </c>
-      <c r="H15" s="63" t="s">
-        <v>193</v>
-      </c>
-      <c r="I15" s="63" t="s">
-        <v>193</v>
-      </c>
-      <c r="J15" s="63" t="s">
-        <v>341</v>
-      </c>
-      <c r="K15" s="63" t="s">
-        <v>193</v>
-      </c>
-      <c r="L15" s="63" t="s">
-        <v>332</v>
-      </c>
-      <c r="M15" s="63" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="129.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="64">
-        <v>2.8</v>
-      </c>
-      <c r="B16" s="64" t="s">
-        <v>248</v>
-      </c>
-      <c r="C16" s="64" t="s">
-        <v>132</v>
-      </c>
-      <c r="D16" s="75" t="s">
-        <v>286</v>
-      </c>
-      <c r="E16" s="63" t="s">
-        <v>295</v>
-      </c>
-      <c r="F16" s="63" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" s="63" t="s">
-        <v>12</v>
-      </c>
-      <c r="H16" s="63" t="s">
-        <v>12</v>
-      </c>
-      <c r="I16" s="63" t="s">
-        <v>12</v>
-      </c>
-      <c r="J16" s="63" t="s">
-        <v>380</v>
-      </c>
-      <c r="K16" s="63" t="s">
-        <v>12</v>
-      </c>
-      <c r="L16" s="63" t="s">
-        <v>12</v>
-      </c>
-      <c r="M16" s="63" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="65">
-        <v>3</v>
-      </c>
-      <c r="B17" s="66" t="s">
-        <v>238</v>
-      </c>
-      <c r="C17" s="65"/>
-      <c r="D17" s="74"/>
-      <c r="E17" s="65"/>
-      <c r="F17" s="65"/>
-      <c r="G17" s="65"/>
-      <c r="H17" s="65"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="65"/>
-      <c r="K17" s="65"/>
-      <c r="L17" s="65"/>
-      <c r="M17" s="65"/>
-    </row>
-    <row r="18" spans="1:13" ht="260" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="64">
-        <v>3.1</v>
-      </c>
-      <c r="B18" s="64" t="s">
-        <v>238</v>
-      </c>
-      <c r="C18" s="64" t="s">
-        <v>240</v>
-      </c>
-      <c r="D18" s="75" t="s">
-        <v>293</v>
-      </c>
-      <c r="E18" s="63" t="s">
-        <v>294</v>
-      </c>
-      <c r="F18" s="63" t="s">
-        <v>309</v>
-      </c>
-      <c r="G18" s="63" t="s">
-        <v>350</v>
-      </c>
-      <c r="H18" s="63" t="s">
-        <v>181</v>
-      </c>
-      <c r="I18" s="63" t="s">
-        <v>320</v>
-      </c>
-      <c r="J18" s="63" t="s">
-        <v>195</v>
-      </c>
-      <c r="K18" s="63" t="s">
-        <v>376</v>
-      </c>
-      <c r="L18" s="63" t="s">
-        <v>402</v>
-      </c>
-      <c r="M18" s="63" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="218.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="96">
-        <v>3.2</v>
-      </c>
-      <c r="B19" s="64" t="s">
-        <v>238</v>
-      </c>
-      <c r="C19" s="64" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" s="97" t="s">
-        <v>291</v>
-      </c>
-      <c r="E19" s="63" t="s">
-        <v>290</v>
-      </c>
-      <c r="F19" s="63" t="s">
-        <v>310</v>
-      </c>
-      <c r="G19" s="63" t="s">
-        <v>197</v>
-      </c>
-      <c r="H19" s="63" t="s">
-        <v>182</v>
-      </c>
-      <c r="I19" s="63" t="s">
-        <v>322</v>
-      </c>
-      <c r="J19" s="63" t="s">
-        <v>196</v>
-      </c>
-      <c r="K19" s="63" t="s">
-        <v>377</v>
-      </c>
-      <c r="L19" s="63" t="s">
-        <v>301</v>
-      </c>
-      <c r="M19" s="63" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="218.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="64">
-        <v>3.3</v>
-      </c>
-      <c r="B20" s="64" t="s">
-        <v>238</v>
-      </c>
-      <c r="C20" s="64" t="s">
-        <v>274</v>
-      </c>
-      <c r="D20" s="75" t="s">
-        <v>199</v>
-      </c>
-      <c r="E20" s="63" t="s">
-        <v>198</v>
-      </c>
-      <c r="F20" s="63" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="63" t="s">
-        <v>352</v>
-      </c>
-      <c r="H20" s="63" t="s">
-        <v>183</v>
-      </c>
-      <c r="I20" s="63" t="s">
-        <v>321</v>
-      </c>
-      <c r="J20" s="63" t="s">
-        <v>358</v>
-      </c>
-      <c r="K20" s="63" t="s">
-        <v>12</v>
-      </c>
-      <c r="L20" s="63" t="s">
-        <v>12</v>
-      </c>
-      <c r="M20" s="63" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" s="72" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="68">
-        <v>4</v>
-      </c>
-      <c r="B21" s="66" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" s="68"/>
-      <c r="D21" s="77"/>
-      <c r="E21" s="71"/>
-      <c r="F21" s="71"/>
-      <c r="G21" s="71"/>
-      <c r="I21" s="71"/>
-      <c r="J21" s="71"/>
-      <c r="K21" s="71"/>
-      <c r="L21" s="71"/>
-      <c r="M21" s="71"/>
-    </row>
-    <row r="22" spans="1:13" ht="240.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="64">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="B22" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" s="64" t="s">
-        <v>39</v>
-      </c>
-      <c r="D22" s="75" t="s">
-        <v>211</v>
-      </c>
-      <c r="E22" s="63" t="s">
-        <v>369</v>
-      </c>
-      <c r="F22" s="63" t="s">
-        <v>370</v>
-      </c>
-      <c r="G22" s="63" t="s">
-        <v>209</v>
-      </c>
-      <c r="H22" s="63" t="s">
-        <v>190</v>
-      </c>
-      <c r="I22" s="63" t="s">
-        <v>369</v>
-      </c>
-      <c r="J22" s="63" t="s">
-        <v>372</v>
-      </c>
-      <c r="K22" s="63" t="s">
-        <v>210</v>
-      </c>
-      <c r="L22" s="63" t="s">
-        <v>373</v>
-      </c>
-      <c r="M22" s="63" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="74.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="64">
-        <v>4.2</v>
-      </c>
-      <c r="B23" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="C23" s="64" t="s">
-        <v>170</v>
-      </c>
-      <c r="D23" s="75" t="s">
-        <v>300</v>
-      </c>
-      <c r="E23" s="63" t="s">
-        <v>288</v>
-      </c>
-      <c r="F23" s="63" t="s">
-        <v>288</v>
-      </c>
-      <c r="G23" s="63" t="s">
-        <v>288</v>
-      </c>
-      <c r="H23" s="63" t="s">
-        <v>288</v>
-      </c>
-      <c r="I23" s="63" t="s">
-        <v>288</v>
-      </c>
-      <c r="J23" s="63" t="s">
-        <v>288</v>
-      </c>
-      <c r="K23" s="63" t="s">
-        <v>288</v>
-      </c>
-      <c r="L23" s="63" t="s">
-        <v>288</v>
-      </c>
-      <c r="M23" s="63" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="96">
-        <v>4.3</v>
-      </c>
-      <c r="B24" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="C24" s="64" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" s="75" t="s">
-        <v>178</v>
-      </c>
-      <c r="E24" s="63" t="s">
-        <v>178</v>
-      </c>
-      <c r="F24" s="63" t="s">
-        <v>178</v>
-      </c>
-      <c r="G24" s="63" t="s">
-        <v>178</v>
-      </c>
-      <c r="H24" s="63" t="s">
-        <v>178</v>
-      </c>
-      <c r="I24" s="63" t="s">
-        <v>178</v>
-      </c>
-      <c r="J24" s="63" t="s">
-        <v>178</v>
-      </c>
-      <c r="K24" s="63" t="s">
-        <v>323</v>
-      </c>
-      <c r="L24" s="63" t="s">
-        <v>178</v>
-      </c>
-      <c r="M24" s="63" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="338" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="64">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="B25" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="C25" s="64" t="s">
-        <v>277</v>
-      </c>
-      <c r="D25" s="97" t="s">
-        <v>287</v>
-      </c>
-      <c r="E25" s="63" t="s">
-        <v>212</v>
-      </c>
-      <c r="F25" s="63" t="s">
-        <v>302</v>
-      </c>
-      <c r="G25" s="63" t="s">
-        <v>348</v>
-      </c>
-      <c r="H25" s="63" t="s">
-        <v>191</v>
-      </c>
-      <c r="I25" s="63" t="s">
-        <v>324</v>
-      </c>
-      <c r="J25" s="63" t="s">
-        <v>357</v>
-      </c>
-      <c r="K25" s="63" t="s">
-        <v>394</v>
-      </c>
-      <c r="L25" s="63" t="s">
-        <v>297</v>
-      </c>
-      <c r="M25" s="63" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" s="88" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="87"/>
-      <c r="D26" s="89"/>
-      <c r="E26" s="90"/>
-      <c r="F26" s="90"/>
-      <c r="G26" s="90"/>
-      <c r="H26" s="90"/>
-      <c r="I26" s="90"/>
-      <c r="J26" s="90"/>
-      <c r="K26" s="90"/>
-      <c r="L26" s="90"/>
-      <c r="M26" s="90"/>
-    </row>
-    <row r="27" spans="1:13" s="94" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="91"/>
-      <c r="B27" s="91"/>
-      <c r="C27" s="91"/>
-      <c r="D27" s="92"/>
-      <c r="E27" s="93"/>
-      <c r="F27" s="93"/>
-      <c r="G27" s="93"/>
-      <c r="H27" s="93"/>
-      <c r="I27" s="93"/>
-      <c r="J27" s="93"/>
-      <c r="K27" s="93"/>
-      <c r="L27" s="93"/>
-      <c r="M27" s="93"/>
-    </row>
-    <row r="28" spans="1:13" s="94" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="91"/>
-      <c r="B28" s="91"/>
-      <c r="C28" s="91"/>
-      <c r="D28" s="92"/>
-      <c r="E28" s="93"/>
-      <c r="F28" s="93"/>
-      <c r="G28" s="93"/>
-      <c r="H28" s="93"/>
-      <c r="I28" s="93"/>
-      <c r="J28" s="93"/>
-      <c r="K28" s="93"/>
-      <c r="L28" s="93"/>
-      <c r="M28" s="93"/>
-    </row>
-    <row r="29" spans="1:13" s="94" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="91"/>
-      <c r="B29" s="91"/>
-      <c r="C29" s="91"/>
-      <c r="D29" s="92"/>
-      <c r="E29" s="93"/>
-      <c r="F29" s="93"/>
-      <c r="G29" s="93"/>
-      <c r="H29" s="93"/>
-      <c r="I29" s="93"/>
-      <c r="J29" s="93"/>
-      <c r="K29" s="93"/>
-      <c r="L29" s="93"/>
-      <c r="M29" s="93"/>
-    </row>
-    <row r="30" spans="1:13" s="94" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="91"/>
-      <c r="B30" s="91"/>
-      <c r="C30" s="91"/>
-      <c r="D30" s="92"/>
-      <c r="E30" s="93"/>
-      <c r="F30" s="93"/>
-      <c r="G30" s="93"/>
-      <c r="H30" s="93"/>
-      <c r="I30" s="93"/>
-      <c r="J30" s="93"/>
-      <c r="K30" s="93"/>
-      <c r="L30" s="93"/>
-      <c r="M30" s="93"/>
-    </row>
-    <row r="31" spans="1:13" s="94" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="95"/>
-      <c r="B31" s="91"/>
-      <c r="C31" s="91"/>
-      <c r="D31" s="92"/>
-      <c r="E31" s="93"/>
-      <c r="F31" s="93"/>
-      <c r="G31" s="93"/>
-      <c r="H31" s="93"/>
-      <c r="I31" s="93"/>
-      <c r="J31" s="93"/>
-      <c r="K31" s="93"/>
-      <c r="L31" s="93"/>
-      <c r="M31" s="93"/>
-    </row>
-    <row r="32" spans="1:13" s="94" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="95"/>
-      <c r="B32" s="91"/>
-      <c r="C32" s="91"/>
-      <c r="D32" s="92"/>
-      <c r="E32" s="93"/>
-      <c r="F32" s="93"/>
-      <c r="G32" s="93"/>
-      <c r="H32" s="93"/>
-      <c r="I32" s="93"/>
-      <c r="J32" s="93"/>
-      <c r="K32" s="93"/>
-      <c r="L32" s="93"/>
-      <c r="M32" s="93"/>
-    </row>
-    <row r="33" spans="1:13" s="94" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="95"/>
-      <c r="B33" s="91"/>
-      <c r="C33" s="91"/>
-      <c r="D33" s="92"/>
-      <c r="E33" s="93"/>
-      <c r="F33" s="93"/>
-      <c r="G33" s="93"/>
-      <c r="H33" s="91"/>
-      <c r="I33" s="93"/>
-      <c r="J33" s="93"/>
-      <c r="K33" s="93"/>
-      <c r="L33" s="93"/>
-      <c r="M33" s="93"/>
-    </row>
-    <row r="34" spans="1:13" s="94" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="91"/>
-      <c r="B34" s="91"/>
-      <c r="C34" s="91"/>
-      <c r="D34" s="92"/>
-      <c r="E34" s="93"/>
-      <c r="F34" s="93"/>
-      <c r="G34" s="93"/>
-      <c r="H34" s="91"/>
-      <c r="I34" s="93"/>
-      <c r="J34" s="93"/>
-      <c r="K34" s="93"/>
-      <c r="L34" s="93"/>
-      <c r="M34" s="93"/>
-    </row>
-    <row r="35" spans="1:13" s="94" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="91"/>
-      <c r="B35" s="91"/>
-      <c r="C35" s="91"/>
-      <c r="D35" s="92"/>
-      <c r="E35" s="93"/>
-      <c r="F35" s="93"/>
-      <c r="G35" s="93"/>
-      <c r="H35" s="93"/>
-      <c r="I35" s="93"/>
-      <c r="J35" s="93"/>
-      <c r="K35" s="93"/>
-      <c r="L35" s="93"/>
-      <c r="M35" s="93"/>
-    </row>
-    <row r="36" spans="1:13" s="94" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="91"/>
-      <c r="B36" s="91"/>
-      <c r="C36" s="91"/>
-      <c r="D36" s="92"/>
-      <c r="E36" s="93"/>
-      <c r="F36" s="93"/>
-      <c r="G36" s="93"/>
-      <c r="H36" s="93"/>
-      <c r="I36" s="93"/>
-      <c r="J36" s="93"/>
-      <c r="K36" s="93"/>
-      <c r="L36" s="93"/>
-      <c r="M36" s="93"/>
-    </row>
-    <row r="37" spans="1:13" s="94" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="91"/>
-      <c r="B37" s="91"/>
-      <c r="C37" s="91"/>
-      <c r="D37" s="92"/>
-      <c r="E37" s="93"/>
-      <c r="F37" s="93"/>
-      <c r="G37" s="93"/>
-      <c r="H37" s="93"/>
-      <c r="I37" s="93"/>
-      <c r="J37" s="93"/>
-      <c r="K37" s="93"/>
-      <c r="L37" s="93"/>
-      <c r="M37" s="93"/>
-    </row>
-    <row r="38" spans="1:13" s="94" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="91"/>
-      <c r="B38" s="91"/>
-      <c r="C38" s="91"/>
-      <c r="D38" s="92"/>
-      <c r="E38" s="93"/>
-      <c r="F38" s="93"/>
-      <c r="G38" s="93"/>
-      <c r="H38" s="93"/>
-      <c r="I38" s="93"/>
-      <c r="J38" s="93"/>
-      <c r="K38" s="93"/>
-      <c r="L38" s="93"/>
-      <c r="M38" s="93"/>
+    </row>
+    <row r="25" spans="1:13" s="87" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="86"/>
+      <c r="D25" s="88"/>
+      <c r="E25" s="89"/>
+      <c r="F25" s="89"/>
+      <c r="G25" s="89"/>
+      <c r="H25" s="89"/>
+      <c r="I25" s="89"/>
+      <c r="J25" s="89"/>
+      <c r="K25" s="89"/>
+      <c r="L25" s="89"/>
+      <c r="M25" s="89"/>
+    </row>
+    <row r="26" spans="1:13" s="93" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="90"/>
+      <c r="B26" s="90"/>
+      <c r="C26" s="90"/>
+      <c r="D26" s="91"/>
+      <c r="E26" s="92"/>
+      <c r="F26" s="92"/>
+      <c r="G26" s="92"/>
+      <c r="H26" s="92"/>
+      <c r="I26" s="92"/>
+      <c r="J26" s="92"/>
+      <c r="K26" s="92"/>
+      <c r="L26" s="92"/>
+      <c r="M26" s="92"/>
+    </row>
+    <row r="27" spans="1:13" s="93" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="90"/>
+      <c r="B27" s="90"/>
+      <c r="C27" s="90"/>
+      <c r="D27" s="91"/>
+      <c r="E27" s="92"/>
+      <c r="F27" s="92"/>
+      <c r="G27" s="92"/>
+      <c r="H27" s="92"/>
+      <c r="I27" s="92"/>
+      <c r="J27" s="92"/>
+      <c r="K27" s="92"/>
+      <c r="L27" s="92"/>
+      <c r="M27" s="92"/>
+    </row>
+    <row r="28" spans="1:13" s="93" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="90"/>
+      <c r="B28" s="90"/>
+      <c r="C28" s="90"/>
+      <c r="D28" s="91"/>
+      <c r="E28" s="92"/>
+      <c r="F28" s="92"/>
+      <c r="G28" s="92"/>
+      <c r="H28" s="92"/>
+      <c r="I28" s="92"/>
+      <c r="J28" s="92"/>
+      <c r="K28" s="92"/>
+      <c r="L28" s="92"/>
+      <c r="M28" s="92"/>
+    </row>
+    <row r="29" spans="1:13" s="93" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="90"/>
+      <c r="B29" s="90"/>
+      <c r="C29" s="90"/>
+      <c r="D29" s="91"/>
+      <c r="E29" s="92"/>
+      <c r="F29" s="92"/>
+      <c r="G29" s="92"/>
+      <c r="H29" s="92"/>
+      <c r="I29" s="92"/>
+      <c r="J29" s="92"/>
+      <c r="K29" s="92"/>
+      <c r="L29" s="92"/>
+      <c r="M29" s="92"/>
+    </row>
+    <row r="30" spans="1:13" s="93" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="94"/>
+      <c r="B30" s="90"/>
+      <c r="C30" s="90"/>
+      <c r="D30" s="91"/>
+      <c r="E30" s="92"/>
+      <c r="F30" s="92"/>
+      <c r="G30" s="92"/>
+      <c r="H30" s="92"/>
+      <c r="I30" s="92"/>
+      <c r="J30" s="92"/>
+      <c r="K30" s="92"/>
+      <c r="L30" s="92"/>
+      <c r="M30" s="92"/>
+    </row>
+    <row r="31" spans="1:13" s="93" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="94"/>
+      <c r="B31" s="90"/>
+      <c r="C31" s="90"/>
+      <c r="D31" s="91"/>
+      <c r="E31" s="92"/>
+      <c r="F31" s="92"/>
+      <c r="G31" s="92"/>
+      <c r="H31" s="92"/>
+      <c r="I31" s="92"/>
+      <c r="J31" s="92"/>
+      <c r="K31" s="92"/>
+      <c r="L31" s="92"/>
+      <c r="M31" s="92"/>
+    </row>
+    <row r="32" spans="1:13" s="93" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="94"/>
+      <c r="B32" s="90"/>
+      <c r="C32" s="90"/>
+      <c r="D32" s="91"/>
+      <c r="E32" s="92"/>
+      <c r="F32" s="92"/>
+      <c r="G32" s="92"/>
+      <c r="H32" s="90"/>
+      <c r="I32" s="92"/>
+      <c r="J32" s="92"/>
+      <c r="K32" s="92"/>
+      <c r="L32" s="92"/>
+      <c r="M32" s="92"/>
+    </row>
+    <row r="33" spans="1:13" s="93" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="90"/>
+      <c r="B33" s="90"/>
+      <c r="C33" s="90"/>
+      <c r="D33" s="91"/>
+      <c r="E33" s="92"/>
+      <c r="F33" s="92"/>
+      <c r="G33" s="92"/>
+      <c r="H33" s="90"/>
+      <c r="I33" s="92"/>
+      <c r="J33" s="92"/>
+      <c r="K33" s="92"/>
+      <c r="L33" s="92"/>
+      <c r="M33" s="92"/>
+    </row>
+    <row r="34" spans="1:13" s="93" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="90"/>
+      <c r="B34" s="90"/>
+      <c r="C34" s="90"/>
+      <c r="D34" s="91"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="92"/>
+      <c r="G34" s="92"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="92"/>
+      <c r="J34" s="92"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="92"/>
+      <c r="M34" s="92"/>
+    </row>
+    <row r="35" spans="1:13" s="93" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="90"/>
+      <c r="B35" s="90"/>
+      <c r="C35" s="90"/>
+      <c r="D35" s="91"/>
+      <c r="E35" s="92"/>
+      <c r="F35" s="92"/>
+      <c r="G35" s="92"/>
+      <c r="H35" s="92"/>
+      <c r="I35" s="92"/>
+      <c r="J35" s="92"/>
+      <c r="K35" s="92"/>
+      <c r="L35" s="92"/>
+      <c r="M35" s="92"/>
+    </row>
+    <row r="36" spans="1:13" s="93" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="90"/>
+      <c r="B36" s="90"/>
+      <c r="C36" s="90"/>
+      <c r="D36" s="91"/>
+      <c r="E36" s="92"/>
+      <c r="F36" s="92"/>
+      <c r="G36" s="92"/>
+      <c r="H36" s="92"/>
+      <c r="I36" s="92"/>
+      <c r="J36" s="92"/>
+      <c r="K36" s="92"/>
+      <c r="L36" s="92"/>
+      <c r="M36" s="92"/>
+    </row>
+    <row r="37" spans="1:13" s="93" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="90"/>
+      <c r="B37" s="90"/>
+      <c r="C37" s="90"/>
+      <c r="D37" s="91"/>
+      <c r="E37" s="92"/>
+      <c r="F37" s="92"/>
+      <c r="G37" s="92"/>
+      <c r="H37" s="92"/>
+      <c r="I37" s="92"/>
+      <c r="J37" s="92"/>
+      <c r="K37" s="92"/>
+      <c r="L37" s="92"/>
+      <c r="M37" s="92"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -9048,7 +8870,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7F786A8-669F-4E18-9021-4E9EFF25F3FF}">
   <dimension ref="B1:R4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -9058,126 +8880,126 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:18" s="2" customFormat="1" ht="161.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="57">
+      <c r="B1" s="56">
         <v>6.1</v>
       </c>
-      <c r="C1" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="57" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="84" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="84" t="s">
-        <v>122</v>
-      </c>
-      <c r="H1" s="84" t="s">
-        <v>107</v>
-      </c>
-      <c r="I1" s="84" t="s">
-        <v>85</v>
-      </c>
-      <c r="J1" s="84" t="s">
-        <v>84</v>
-      </c>
-      <c r="K1" s="84" t="s">
-        <v>123</v>
-      </c>
-      <c r="L1" s="84" t="s">
-        <v>63</v>
-      </c>
-      <c r="M1" s="84" t="s">
-        <v>264</v>
-      </c>
-      <c r="N1" s="84"/>
+      <c r="C1" s="56" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="83" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="83" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1" s="83" t="s">
+        <v>97</v>
+      </c>
+      <c r="I1" s="83" t="s">
+        <v>79</v>
+      </c>
+      <c r="J1" s="83" t="s">
+        <v>78</v>
+      </c>
+      <c r="K1" s="83" t="s">
+        <v>113</v>
+      </c>
+      <c r="L1" s="83" t="s">
+        <v>57</v>
+      </c>
+      <c r="M1" s="83" t="s">
+        <v>252</v>
+      </c>
+      <c r="N1" s="83"/>
       <c r="O1" s="13"/>
       <c r="P1" s="13"/>
       <c r="Q1" s="13"/>
       <c r="R1" s="20"/>
     </row>
     <row r="2" spans="2:18" s="2" customFormat="1" ht="209" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="57">
+      <c r="B2" s="56">
         <v>6.2</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="84" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="84" t="s">
-        <v>121</v>
-      </c>
-      <c r="H2" s="84" t="s">
-        <v>108</v>
-      </c>
-      <c r="I2" s="84" t="s">
-        <v>109</v>
-      </c>
-      <c r="J2" s="84" t="s">
-        <v>82</v>
-      </c>
-      <c r="K2" s="84" t="s">
-        <v>123</v>
-      </c>
-      <c r="L2" s="84" t="s">
-        <v>63</v>
-      </c>
-      <c r="M2" s="84" t="s">
-        <v>265</v>
-      </c>
-      <c r="N2" s="84"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="83" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="83" t="s">
+        <v>111</v>
+      </c>
+      <c r="H2" s="83" t="s">
+        <v>98</v>
+      </c>
+      <c r="I2" s="83" t="s">
+        <v>99</v>
+      </c>
+      <c r="J2" s="83" t="s">
+        <v>76</v>
+      </c>
+      <c r="K2" s="83" t="s">
+        <v>113</v>
+      </c>
+      <c r="L2" s="83" t="s">
+        <v>57</v>
+      </c>
+      <c r="M2" s="83" t="s">
+        <v>253</v>
+      </c>
+      <c r="N2" s="83"/>
       <c r="O2" s="13"/>
       <c r="P2" s="13"/>
       <c r="Q2" s="13"/>
       <c r="R2" s="20"/>
     </row>
     <row r="3" spans="2:18" s="2" customFormat="1" ht="236" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="57">
+      <c r="B3" s="56">
         <v>6.3</v>
       </c>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="84" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="85" t="s">
-        <v>114</v>
-      </c>
-      <c r="H3" s="84" t="s">
-        <v>111</v>
-      </c>
-      <c r="I3" s="84" t="s">
-        <v>87</v>
-      </c>
-      <c r="J3" s="84" t="s">
-        <v>82</v>
-      </c>
-      <c r="K3" s="84" t="s">
-        <v>86</v>
-      </c>
-      <c r="L3" s="84" t="s">
-        <v>62</v>
-      </c>
-      <c r="M3" s="84" t="s">
-        <v>266</v>
-      </c>
-      <c r="N3" s="86" t="s">
-        <v>110</v>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="E3" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="83" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="84" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="83" t="s">
+        <v>101</v>
+      </c>
+      <c r="I3" s="83" t="s">
+        <v>81</v>
+      </c>
+      <c r="J3" s="83" t="s">
+        <v>76</v>
+      </c>
+      <c r="K3" s="83" t="s">
+        <v>80</v>
+      </c>
+      <c r="L3" s="83" t="s">
+        <v>56</v>
+      </c>
+      <c r="M3" s="83" t="s">
+        <v>254</v>
+      </c>
+      <c r="N3" s="85" t="s">
+        <v>100</v>
       </c>
       <c r="O3" s="13"/>
       <c r="P3" s="13"/>
@@ -9185,43 +9007,43 @@
       <c r="R3" s="20"/>
     </row>
     <row r="4" spans="2:18" s="2" customFormat="1" ht="230.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="57">
+      <c r="B4" s="56">
         <v>6.4</v>
       </c>
-      <c r="C4" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="57" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="84" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="84" t="s">
-        <v>115</v>
-      </c>
-      <c r="H4" s="84" t="s">
-        <v>113</v>
-      </c>
-      <c r="I4" s="84" t="s">
-        <v>83</v>
-      </c>
-      <c r="J4" s="84" t="s">
-        <v>82</v>
-      </c>
-      <c r="K4" s="84" t="s">
-        <v>86</v>
-      </c>
-      <c r="L4" s="84" t="s">
-        <v>62</v>
-      </c>
-      <c r="M4" s="84" t="s">
-        <v>267</v>
-      </c>
-      <c r="N4" s="84"/>
+      <c r="C4" s="56" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="83" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="83" t="s">
+        <v>105</v>
+      </c>
+      <c r="H4" s="83" t="s">
+        <v>103</v>
+      </c>
+      <c r="I4" s="83" t="s">
+        <v>77</v>
+      </c>
+      <c r="J4" s="83" t="s">
+        <v>76</v>
+      </c>
+      <c r="K4" s="83" t="s">
+        <v>80</v>
+      </c>
+      <c r="L4" s="83" t="s">
+        <v>56</v>
+      </c>
+      <c r="M4" s="83" t="s">
+        <v>255</v>
+      </c>
+      <c r="N4" s="83"/>
       <c r="O4" s="13"/>
       <c r="P4" s="13"/>
       <c r="Q4" s="13"/>
@@ -9234,7 +9056,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1676ECD-1C62-45E3-A4EC-ECE552C41AE1}">
   <dimension ref="D18:AI21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -9257,266 +9079,266 @@
   </cols>
   <sheetData>
     <row r="18" spans="4:35" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D18" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" s="44" t="s">
+      <c r="D18" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="G18" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="I18" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="J18" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="K18" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="L18" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="M18" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="N18" s="43" t="s">
+        <v>116</v>
+      </c>
+      <c r="O18" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="P18" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q18" s="46" t="s">
+        <v>95</v>
+      </c>
+      <c r="R18" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="F18" s="44" t="s">
-        <v>50</v>
-      </c>
-      <c r="G18" s="45" t="s">
+      <c r="S18" s="46" t="s">
+        <v>47</v>
+      </c>
+      <c r="T18" s="47" t="s">
+        <v>114</v>
+      </c>
+      <c r="U18" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="V18" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="W18" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="X18" s="46" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y18" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z18" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA18" s="45" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB18" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC18" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="H18" s="45" t="s">
-        <v>49</v>
-      </c>
-      <c r="I18" s="44" t="s">
-        <v>51</v>
-      </c>
-      <c r="J18" s="45" t="s">
-        <v>116</v>
-      </c>
-      <c r="K18" s="45" t="s">
-        <v>44</v>
-      </c>
-      <c r="L18" s="44" t="s">
-        <v>60</v>
-      </c>
-      <c r="M18" s="46" t="s">
-        <v>89</v>
-      </c>
-      <c r="N18" s="44" t="s">
-        <v>126</v>
-      </c>
-      <c r="O18" s="44" t="s">
-        <v>127</v>
-      </c>
-      <c r="P18" s="44" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q18" s="47" t="s">
+      <c r="AD18" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE18" s="45" t="s">
+        <v>55</v>
+      </c>
+      <c r="AF18" s="48" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG18" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="AH18" s="48" t="s">
+        <v>104</v>
+      </c>
+      <c r="AI18" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="R18" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="S18" s="47" t="s">
-        <v>52</v>
-      </c>
-      <c r="T18" s="48" t="s">
-        <v>124</v>
-      </c>
-      <c r="U18" s="48" t="s">
-        <v>125</v>
-      </c>
-      <c r="V18" s="47" t="s">
-        <v>45</v>
-      </c>
-      <c r="W18" s="45" t="s">
-        <v>40</v>
-      </c>
-      <c r="X18" s="47" t="s">
-        <v>119</v>
-      </c>
-      <c r="Y18" s="46" t="s">
-        <v>39</v>
-      </c>
-      <c r="Z18" s="46" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA18" s="46" t="s">
-        <v>74</v>
-      </c>
-      <c r="AB18" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="AC18" s="46" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD18" s="46" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE18" s="46" t="s">
-        <v>61</v>
-      </c>
-      <c r="AF18" s="49" t="s">
-        <v>122</v>
-      </c>
-      <c r="AG18" s="49" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH18" s="49" t="s">
-        <v>114</v>
-      </c>
-      <c r="AI18" s="49" t="s">
-        <v>115</v>
-      </c>
     </row>
     <row r="19" spans="4:35" x14ac:dyDescent="0.35">
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="51"/>
-      <c r="K19" s="51"/>
-      <c r="L19" s="50"/>
-      <c r="M19" s="52"/>
-      <c r="N19" s="50"/>
-      <c r="O19" s="50"/>
-      <c r="P19" s="50"/>
-      <c r="Q19" s="53"/>
-      <c r="R19" s="53"/>
-      <c r="S19" s="53"/>
-      <c r="T19" s="54"/>
-      <c r="U19" s="54"/>
-      <c r="V19" s="53"/>
-      <c r="W19" s="51"/>
-      <c r="X19" s="53"/>
-      <c r="Y19" s="52"/>
-      <c r="Z19" s="52"/>
-      <c r="AA19" s="52"/>
-      <c r="AB19" s="52"/>
-      <c r="AC19" s="52"/>
-      <c r="AD19" s="52"/>
-      <c r="AE19" s="52"/>
-      <c r="AF19" s="55"/>
-      <c r="AG19" s="55"/>
-      <c r="AH19" s="55"/>
-      <c r="AI19" s="55"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="49"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="50"/>
+      <c r="L19" s="49"/>
+      <c r="M19" s="51"/>
+      <c r="N19" s="49"/>
+      <c r="O19" s="49"/>
+      <c r="P19" s="49"/>
+      <c r="Q19" s="52"/>
+      <c r="R19" s="52"/>
+      <c r="S19" s="52"/>
+      <c r="T19" s="53"/>
+      <c r="U19" s="53"/>
+      <c r="V19" s="52"/>
+      <c r="W19" s="50"/>
+      <c r="X19" s="52"/>
+      <c r="Y19" s="51"/>
+      <c r="Z19" s="51"/>
+      <c r="AA19" s="51"/>
+      <c r="AB19" s="51"/>
+      <c r="AC19" s="51"/>
+      <c r="AD19" s="51"/>
+      <c r="AE19" s="51"/>
+      <c r="AF19" s="54"/>
+      <c r="AG19" s="54"/>
+      <c r="AH19" s="54"/>
+      <c r="AI19" s="54"/>
     </row>
     <row r="20" spans="4:35" x14ac:dyDescent="0.35">
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="51"/>
-      <c r="K20" s="51"/>
-      <c r="L20" s="50"/>
-      <c r="M20" s="52"/>
-      <c r="N20" s="50"/>
-      <c r="O20" s="50"/>
-      <c r="P20" s="50"/>
-      <c r="Q20" s="53"/>
-      <c r="R20" s="53"/>
-      <c r="S20" s="53"/>
-      <c r="T20" s="54"/>
-      <c r="U20" s="54"/>
-      <c r="V20" s="53"/>
-      <c r="W20" s="51"/>
-      <c r="X20" s="53"/>
-      <c r="Y20" s="52"/>
-      <c r="Z20" s="52"/>
-      <c r="AA20" s="52"/>
-      <c r="AB20" s="52"/>
-      <c r="AC20" s="52"/>
-      <c r="AD20" s="52"/>
-      <c r="AE20" s="52"/>
-      <c r="AF20" s="55"/>
-      <c r="AG20" s="55"/>
-      <c r="AH20" s="55"/>
-      <c r="AI20" s="55"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="50"/>
+      <c r="H20" s="50"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="50"/>
+      <c r="K20" s="50"/>
+      <c r="L20" s="49"/>
+      <c r="M20" s="51"/>
+      <c r="N20" s="49"/>
+      <c r="O20" s="49"/>
+      <c r="P20" s="49"/>
+      <c r="Q20" s="52"/>
+      <c r="R20" s="52"/>
+      <c r="S20" s="52"/>
+      <c r="T20" s="53"/>
+      <c r="U20" s="53"/>
+      <c r="V20" s="52"/>
+      <c r="W20" s="50"/>
+      <c r="X20" s="52"/>
+      <c r="Y20" s="51"/>
+      <c r="Z20" s="51"/>
+      <c r="AA20" s="51"/>
+      <c r="AB20" s="51"/>
+      <c r="AC20" s="51"/>
+      <c r="AD20" s="51"/>
+      <c r="AE20" s="51"/>
+      <c r="AF20" s="54"/>
+      <c r="AG20" s="54"/>
+      <c r="AH20" s="54"/>
+      <c r="AI20" s="54"/>
     </row>
     <row r="21" spans="4:35" x14ac:dyDescent="0.35">
-      <c r="D21" s="50">
+      <c r="D21" s="49">
         <v>4.0999999999999996</v>
       </c>
-      <c r="E21" s="50">
+      <c r="E21" s="49">
         <v>4.2</v>
       </c>
-      <c r="F21" s="50">
+      <c r="F21" s="49">
         <v>4.4000000000000004</v>
       </c>
-      <c r="G21" s="51">
+      <c r="G21" s="50">
         <v>3.2</v>
       </c>
-      <c r="H21" s="51">
+      <c r="H21" s="50">
         <v>3.4</v>
       </c>
-      <c r="I21" s="50">
+      <c r="I21" s="49">
         <v>4.5</v>
       </c>
-      <c r="J21" s="51">
+      <c r="J21" s="50">
         <v>3.1</v>
       </c>
-      <c r="K21" s="51">
+      <c r="K21" s="50">
         <v>3.3</v>
       </c>
-      <c r="L21" s="50">
+      <c r="L21" s="49">
         <v>4.5999999999999996</v>
       </c>
-      <c r="M21" s="52">
+      <c r="M21" s="51">
         <v>1.8</v>
       </c>
-      <c r="N21" s="50">
+      <c r="N21" s="49">
         <v>4.7</v>
       </c>
-      <c r="O21" s="50">
+      <c r="O21" s="49">
         <v>4.8</v>
       </c>
-      <c r="P21" s="50">
+      <c r="P21" s="49">
         <v>4.3</v>
       </c>
-      <c r="Q21" s="53">
+      <c r="Q21" s="52">
         <v>2.4</v>
       </c>
-      <c r="R21" s="53">
+      <c r="R21" s="52">
         <v>2.6</v>
       </c>
-      <c r="S21" s="53">
+      <c r="S21" s="52">
         <v>2.1</v>
       </c>
-      <c r="T21" s="54">
+      <c r="T21" s="53">
         <v>5.0999999999999996</v>
       </c>
-      <c r="U21" s="54">
+      <c r="U21" s="53">
         <v>5.2</v>
       </c>
-      <c r="V21" s="53">
+      <c r="V21" s="52">
         <v>2.2000000000000002</v>
       </c>
-      <c r="W21" s="51">
+      <c r="W21" s="50">
         <v>3.5</v>
       </c>
-      <c r="X21" s="53">
+      <c r="X21" s="52">
         <v>2.5</v>
       </c>
-      <c r="Y21" s="52">
+      <c r="Y21" s="51">
         <v>1.3</v>
       </c>
-      <c r="Z21" s="52">
+      <c r="Z21" s="51">
         <v>1.4</v>
       </c>
-      <c r="AA21" s="52">
+      <c r="AA21" s="51">
         <v>1.5</v>
       </c>
-      <c r="AB21" s="52">
+      <c r="AB21" s="51">
         <v>1.6</v>
       </c>
-      <c r="AC21" s="52">
+      <c r="AC21" s="51">
         <v>1.7</v>
       </c>
-      <c r="AD21" s="52">
+      <c r="AD21" s="51">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AE21" s="52">
+      <c r="AE21" s="51">
         <v>1.2</v>
       </c>
-      <c r="AF21" s="55">
+      <c r="AF21" s="54">
         <v>6.1</v>
       </c>
-      <c r="AG21" s="55">
+      <c r="AG21" s="54">
         <v>6.2</v>
       </c>
-      <c r="AH21" s="55">
+      <c r="AH21" s="54">
         <v>6.3</v>
       </c>
-      <c r="AI21" s="55">
+      <c r="AI21" s="54">
         <v>6.4</v>
       </c>
     </row>

--- a/Patterns_findings.xlsx
+++ b/Patterns_findings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universitaetstgallen-my.sharepoint.com/personal/marco_franceschetti_unisg_ch/Documents/Dokumente/Papers/ICPM2027/online_catalog/patterns_website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="148" documentId="13_ncr:1_{1D00CA42-D2F2-429A-AAD6-12534F9C3AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D6D0ED4-80CD-4342-9EBE-823B5660D349}"/>
+  <xr:revisionPtr revIDLastSave="186" documentId="13_ncr:1_{1D00CA42-D2F2-429A-AAD6-12534F9C3AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85D8EBF6-74D7-41FE-988C-836FB37F8861}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -109,9 +109,6 @@
     <t>Timestamp Granularity</t>
   </si>
   <si>
-    <t>The attribute's value distribution for the selected activity type.</t>
-  </si>
-  <si>
     <t>Case Table</t>
   </si>
   <si>
@@ -139,9 +136,6 @@
     <t>What are the (data) requirements - if any?</t>
   </si>
   <si>
-    <t>The analyst has an understanding of the semantics of the activity types and attributes.</t>
-  </si>
-  <si>
     <t>Assess whether an attribute recorded for an activity is intrinsically associated with that activity.</t>
   </si>
   <si>
@@ -160,9 +154,6 @@
     <t>Derive the population of a selected attribute across cases based on its presence, frequency of occurrence, and consistency of values within each case.</t>
   </si>
   <si>
-    <t>Attribute information may differ not only in its availability across activity types but also across cases. An attribute may be available exactly once per case (i.e., case attribute candidate), multiple times with the same or different values, or only for a subset of cases. Understanding these filling characteristics helps analysts assess the attribute's availability.</t>
-  </si>
-  <si>
     <t>Create a case-level representation of the event log in which each case is represented by a single row containing its unique identifier and case-level attributes.</t>
   </si>
   <si>
@@ -211,32 +202,10 @@
     <t>Identify groups of events that potentially belong to the same short- or long-running transaction within the same case.</t>
   </si>
   <si>
-    <t>Events belonging to the same transaction may be recorded as separate activity types and may occur repeatedly within a case. Identifying activities with similar case-level occurrence helps analysts recognize candidate transaction boundaries, understand which recorded events may represent a common unit of work, and reduce behavioral complexity in subsequent analyses.</t>
-  </si>
-  <si>
-    <t>Identify exact temporal coincidence patterns in an event log, including sets of different activity types occurring simultaneously within the same case (super events) and occurrences of the same activity type occurring simultaneously across multiple cases (batch events).</t>
-  </si>
-  <si>
-    <t>Events sharing an exact timestamp can reveal different structural characteristics of an event log. Within a case, multiple activity types recorded at the same moment may represent components of one jointly recorded occurrence and may therefore be candidates for representation as a super event. Across cases, repeated occurrences of the same activity type at one moment may indicate batch processing, scheduled execution, or a shared system operation.</t>
-  </si>
-  <si>
-    <t>Analyze timestamp coincidence from two perspectives. For super events, group events by case and exact timestamp, derive the set of distinct activity types in each timestamp window, and retain sets meeting the minimum size. Aggregate identical sets and calculate their timestamp-level occurrences, number of cases, case support, conditional set coverage, and average event coverage. For batch events, group events by activity type and exact timestamp across the complete log, count the distinct participating cases, retain groups meeting the minimum case threshold, and record their participating case identifiers. Rank super-event candidates by their support and coverage measures and batch events by the number of participating cases.</t>
-  </si>
-  <si>
     <t>Two complementary results: (1) a ranked collection of candidate super events and (2) a ranked collection of candidate batch events.</t>
   </si>
   <si>
-    <t>Characterize how activity types co-occur within cases and identify sets of activities with sufficiently similar co-occurrence as candidate transactions. Rank the resulting candidate sets according to the strength of their observed association.
-For example, construct a case–activity count table and represent each activity type as a count vector across cases. Compute a similarity score for every pair of activity vectors. Create a graph connecting activity pairs whose similarity meets the specified threshold, then extract maximal cliques in which every activity pair satisfies the threshold. Rank the resulting candidates by set size and mean pairwise similarity.</t>
-  </si>
-  <si>
-    <t>A ranked collection of candidate transaction groups, each containing a set of activity types, together with its set size and  similarity measure.</t>
-  </si>
-  <si>
     <t>An assessment of the presence, strength, and where present form of statistical dependence between the selected attributes, based on the applied dependence measure or graphical exploration.</t>
-  </si>
-  <si>
-    <t>For each activity type, determine its case coverage and distinguish cases with a single versus repeated occurrence.</t>
   </si>
   <si>
     <t>None</t>
@@ -261,9 +230,6 @@
     <t>During initial analysis, analysts may formulate expectations about how recorded attribute values should behave within a case. These expectations can be expressed as domain-specific rules concerning individual attributes or relationships between multiple attributes. For example, an attribute may be expected to satisfy a value constraint, remain constant across events, or depend on the values of other attributes. Checking compliance with such rules allows analysts to validate their expectations and identify inconsistencies in the recorded information.</t>
   </si>
   <si>
-    <t>A similarity threshold, a minimum transaction-set size, and any activity types to exclude are specified.</t>
-  </si>
-  <si>
     <t>An assessment of the compliance of the domain-specific rule within each case, together with the cases and events that violate it.</t>
   </si>
   <si>
@@ -319,24 +285,9 @@
     <t>Identify events within the same case that have identical values across all event attributes. From each identified group of exact duplicate events, retain a single occurrence and remove the remaining occurrences.</t>
   </si>
   <si>
-    <t>The total number of duplicated events in the log, the number of cases where duplicated events occur, and for each case with duplicated events, the case id and the name of the respective activity types. The resulting event log with the identified exact duplicate events removed.</t>
-  </si>
-  <si>
     <t>Schema Population</t>
   </si>
   <si>
-    <t>Understand which attributes are associated with each activity type and which of them are shared across activity types.</t>
-  </si>
-  <si>
-    <t>Event attributes may differ across activity types, so analysts need to know what information is available for an activity before analyzing it. Attributes also differ in structural scope: some are mandatory, some are populated independently of the activity type, and others only for particular activity types. Knowing an attribute's scope tells analysts whether it is globally applicable or activity-dependent, how to interpret absent values, and whether an analysis involving it should consider the entire log or only selected activity types. Schemas may furthermore overlap, because different activity types can record the same information. Identifying overlaps reveals which information supports comparative or cross-activity analyses, and exposes structural relationships between schemas that inspecting each schema in isolation does not.</t>
-  </si>
-  <si>
-    <t>Derive the schema of each activity type from the attributes observed in its events, together with their value types and population. Classify each attribute by structural role: `mandatory` or `non-mandatory`, the latter being `global` if consistently filled for all events and otherwise `local`, and local attributes being local either to a single activity type or to several. Compare attribute membership across schemas to identify shared attributes.</t>
-  </si>
-  <si>
-    <t>Per activity type, a schema listing its observed attributes (those taking a non-null value), their value types, and their population across its events. A classification of all attributes as mandatory, global, or local, local ones further marked as pertaining to one or to several activity types. A list of the attributes shared by multiple activity types, with the number of events in which each activity type populates them.</t>
-  </si>
-  <si>
     <t>Verify if the events within each case and overall in the log are ordered according to the timestamp attribute, and whether the timestamps establish a total or partial ordering of events; where required, reorder events according to their timestamps..</t>
   </si>
   <si>
@@ -361,21 +312,6 @@
     <t>Activity Occurrence Statistics</t>
   </si>
   <si>
-    <t>Combine multiple activity types into a single activity type when their distinction is not required, or separate semantically distinct activities implicitly represented by one existing activity type.</t>
-  </si>
-  <si>
-    <t>Event logs may represent events through separate activity types even though their distinction is unnecessary, or may implicitly represent semantically distinct activities through only one activity type. Folding activity types can provide a simplified list of activity types and reduce distinctions that are not relevant. Conversely, keeping semantically distinct activities implicit can obscure the information represented by the event log. Making them explicit as distinct activity types can provide a representation that better reflects the occurrences evidenced by the recorded data.</t>
-  </si>
-  <si>
-    <t>For folding, the activity types of the events to be folded, the activity type through which they should be represented jointly, and the rule for determining the new representation are specified. For unfolding, semantically distinct activities have been identified as being implicitly represented by one existing activity type, and a distinguishing rule, either at the case-level or event-level, is specified.</t>
-  </si>
-  <si>
-    <t>For folding, combine the selected activity types into a common activity type while optionally preserving the information required to represent the associated events according to the specified rule. For unfolding, change the activity type of implicitly represented activities by assigning them a distinct activity type based on the specified rule.</t>
-  </si>
-  <si>
-    <t>An event log in which the selected distinct activity types are represented through a common activity type rather than as separate activities, with the distinction between them made explicit through attribute values, or in which previously implicit activity types are represented explicitly.</t>
-  </si>
-  <si>
     <t>Understand the distribution of values for a given global, local, or case attribute, where applicable with respect to a given activity.</t>
   </si>
   <si>
@@ -398,12 +334,6 @@
   </si>
   <si>
     <t>Event logs may associate attributes with activities even though their values are determined by other events. Such associations can lead analysts to incorrectly interpret an attribute as describing the activity itself. Identified mismatches may motivate subsequent transformations of the event log, such as adding events to make implicitly represented activities explicit, removing events that do not represent distinct activity occurrences, or relocating information to the activity with which it is semantically associated.</t>
-  </si>
-  <si>
-    <t>Compare where the selected attribute is populated in the event log with where, according to its semantics and the process context, the information represented by the attribute is expected to become available. If required, transform the event log accordingly, for example by adding or removing events or changing the association of information with activity types.</t>
-  </si>
-  <si>
-    <t>An assessment of whether the selected attribute is semantically associated with the activities for which it is recorded, including identified mismatches between its observed and expected association with activity types; if a transformation is performed, an event log in which the identified association is represented accordingly.</t>
   </si>
   <si>
     <t>Characterize a selected attribute according to whether it represents categorical or quantitative information. For quantitative attributes, where relevant, examine the temporal evolution of the attribute within each case and assess whether successive observed values are monotonically increasing or decreasing.</t>
@@ -649,9 +579,6 @@
     <t>A partial population like this is a prompt to investigate the cases. Checking the cases where "lastSent" is missing might show that they never reached the notification step (for example, fines paid earlier) rather than that the value was lost. If that holds, the absence is not a data gap, and its presence can then be used to tell notified from non-notified fines instead of imputing anything.</t>
   </si>
   <si>
-    <t>An attribute may be associated with an activity type but not populated in all of its occurrences, and its populated values may be distributed unevenly. Examining the distribution of attribute values provides a more detailed understanding of the information available for that activity and may reveal missingness or value patterns that warrant further investigation.</t>
-  </si>
-  <si>
     <t>The analysis reveals a value distribution with extreme amounts for "Create Fine", as well as amounts=0, motivating separate inspection of these values before relying on aggregate statistics or using the attribute in downstream analyses.</t>
   </si>
   <si>
@@ -747,12 +674,6 @@
 Domain-specific enrichment: add an attribute "OutstandingBalance" recording the amount still to be paid by the offender to settle the fine.</t>
   </si>
   <si>
-    <t>Understand how activity types occur across cases and in the log, and whether they occur once or repeatedly within a case.</t>
-  </si>
-  <si>
-    <t>An occurrence summary for each activity type.</t>
-  </si>
-  <si>
     <t>"W_Complete application" occurs multiple times in every case, which raises questions about how the workflow system is configured and the granularity at which the activity is captured (e.g. line-item level rather than header level). These repeats should therefore be interpreted as informative of activity lifecycles.</t>
   </si>
   <si>
@@ -775,9 +696,6 @@
   </si>
   <si>
     <t>Determine the effective recording granularity and time zone of timestamps in an event log, assess whether they vary across events, identify temporal components that remain constant throughout the log, and, where required, normalize them to a selected temporal granularity. Convert event timestamps to a selected time zone.</t>
-  </si>
-  <si>
-    <t>Timestamp recording granularity and time zone may be unknown or vary across events or activity types. Insufficient or heterogeneous timestamp granularity/time zone can result in events sharing identical timestamps, making their ordering ambiguous, introducing apparent concurrency, and potentially affecting subsequent temporal analyses. Moreover, temporal components that are constant throughout the log, such as the year or month, reveal the effective temporal scope of the recorded data and may be relevant when interpreting temporal patterns. Normalizing timestamps to a common granularity can provide a consistent temporal representation at the resolution required for subsequent analysis. Converting a timestamp attribute to a selected time zone can establish a common temporal reference across timestamp attributes and support the correct interpretation of time-dependent information.</t>
   </si>
   <si>
     <t>A target granularity is specified if normalization is performed. If timezone conversion is required, a target time zone is specified.</t>
@@ -818,6 +736,88 @@
   </si>
   <si>
     <t>Amount is a running total rather than a per-event figure: the first value is the base fine, the last the total owed after any penalty. It should be read by its last value (the total) or by the increments between events (the penalty), never summed or averaged. This also clarifies how the shared "amount" attributes at "Create Fine" and "Add Penalty" relate.</t>
+  </si>
+  <si>
+    <t>Understand which attributes are associated with each activity and which of them are shared across activities.</t>
+  </si>
+  <si>
+    <t>Attribute information may differ not only in its availability across activities but also across cases. An attribute may be available exactly once per case (i.e., case attribute candidate), multiple times with the same or different values, or only for a subset of cases. Understanding these filling characteristics helps analysts assess the attribute's availability.</t>
+  </si>
+  <si>
+    <t>The total number of duplicated events in the log, the number of cases where duplicated events occur, and for each case with duplicated events, the case id and the name of the respective activities. The resulting event log with the identified exact duplicate events removed.</t>
+  </si>
+  <si>
+    <t>An attribute may be associated with an activity but not populated in all of its occurrences, and its populated values may be distributed unevenly. Examining the distribution of attribute values provides a more detailed understanding of the information available for that activity and may reveal missingness or value patterns that warrant further investigation.</t>
+  </si>
+  <si>
+    <t>The attribute's value distribution for the selected activity.</t>
+  </si>
+  <si>
+    <t>The analyst has an understanding of the semantics of the activities and attributes.</t>
+  </si>
+  <si>
+    <t>Compare where the selected attribute is populated in the event log with where, according to its semantics and the process context, the information represented by the attribute is expected to become available. If required, transform the event log accordingly, for example by adding or removing events or changing the association of information with activities.</t>
+  </si>
+  <si>
+    <t>An assessment of whether the selected attribute is semantically associated with the activities for which it is recorded, including identified mismatches between its observed and expected association with activities; if a transformation is performed, an event log in which the identified association is represented accordingly.</t>
+  </si>
+  <si>
+    <t>Understand how activities occur across cases and in the log, and whether they occur once or repeatedly within a case.</t>
+  </si>
+  <si>
+    <t>For each activity, determine its case coverage and distinguish cases with a single versus repeated occurrence.</t>
+  </si>
+  <si>
+    <t>An occurrence summary for each activity.</t>
+  </si>
+  <si>
+    <t>Events belonging to the same transaction may be recorded as separate activities and may occur repeatedly within a case. Identifying activities with similar case-level occurrence helps analysts recognize candidate transaction boundaries, understand which recorded events may represent a common unit of work, and reduce behavioral complexity in subsequent analyses.</t>
+  </si>
+  <si>
+    <t>A similarity threshold, a minimum transaction-set size, and any activities to exclude are specified.</t>
+  </si>
+  <si>
+    <t>Characterize how activities co-occur within cases and identify sets of activities with sufficiently similar co-occurrence as candidate transactions. Rank the resulting candidate sets according to the strength of their observed association.
+For example, construct a case–activity count table and represent each activity as a count vector across cases. Compute a similarity score for every pair of activity vectors. Create a graph connecting activity pairs whose similarity meets the specified threshold, then extract maximal cliques in which every activity pair satisfies the threshold. Rank the resulting candidates by set size and mean pairwise similarity.</t>
+  </si>
+  <si>
+    <t>A ranked collection of candidate transaction groups, each containing a set of activities, together with its set size and  similarity measure.</t>
+  </si>
+  <si>
+    <t>Timestamp recording granularity and time zone may be unknown or vary across events or activities. Insufficient or heterogeneous timestamp granularity/time zone can result in events sharing identical timestamps, making their ordering ambiguous, introducing apparent concurrency, and potentially affecting subsequent temporal analyses. Moreover, temporal components that are constant throughout the log, such as the year or month, reveal the effective temporal scope of the recorded data and may be relevant when interpreting temporal patterns. Normalizing timestamps to a common granularity can provide a consistent temporal representation at the resolution required for subsequent analysis. Converting a timestamp attribute to a selected time zone can establish a common temporal reference across timestamp attributes and support the correct interpretation of time-dependent information.</t>
+  </si>
+  <si>
+    <t>Identify exact temporal coincidence patterns in an event log, including sets of different activities occurring simultaneously within the same case (super events) and occurrences of the same activity occurring simultaneously across multiple cases (batch events).</t>
+  </si>
+  <si>
+    <t>Analyze timestamp coincidence from two perspectives. For super events, group events by case and exact timestamp, derive the set of distinct activities in each timestamp window, and retain sets meeting the minimum size. Aggregate identical sets and calculate their timestamp-level occurrences, number of cases, case support, conditional set coverage, and average event coverage. For batch events, group events by activity and exact timestamp across the complete log, count the distinct participating cases, retain groups meeting the minimum case threshold, and record their participating case identifiers. Rank super-event candidates by their support and coverage measures and batch events by the number of participating cases.</t>
+  </si>
+  <si>
+    <t>Derive the schema of each activity from the attributes observed in its events, together with their value types and population. Classify each attribute by structural role: `mandatory` or `non-mandatory`, the latter being `global` if consistently filled for all events and otherwise `local`, and local attributes being local either to a single activity or to several. Compare attribute membership across schemas to identify shared attributes.</t>
+  </si>
+  <si>
+    <t>Per activity, a schema listing its observed attributes (those taking a non-null value), their value types, and their population across its events. A classification of all attributes as mandatory, global, or local, local ones further marked as pertaining to one or to several activities. A list of the attributes shared by multiple activities, with the number of events in which each activity populates them.</t>
+  </si>
+  <si>
+    <t>For folding, the activities of the events to be folded, the activity through which they should be represented jointly, and the rule for determining the new representation are specified. For unfolding, semantically distinct activities have been identified as being implicitly represented by one existing activity, and a distinguishing rule, either at the case-level or event-level, is specified.</t>
+  </si>
+  <si>
+    <t>For folding, combine the selected activities into a common activity while optionally preserving the information required to represent the associated events according to the specified rule. For unfolding, change the activity of implicitly represented activities by assigning them a distinct activity based on the specified rule.</t>
+  </si>
+  <si>
+    <t>An event log in which the selected distinct activities are represented through a common activity rather than as separate activities, with the distinction between them made explicit through attribute values, or in which previously implicit activities are represented explicitly.</t>
+  </si>
+  <si>
+    <t>Events sharing an exact timestamp can reveal different structural characteristics of an event log. Within a case, multiple activities recorded at the same moment may represent components of one jointly recorded occurrence and may therefore be candidates for representation as a super event. Across cases, repeated occurrences of the same activity at one moment may indicate batch processing, scheduled execution, or a shared system operation.</t>
+  </si>
+  <si>
+    <t>Combine multiple activities into a single activity when their distinction is not required, or separate semantically distinct activities implicitly represented by one existing activity.</t>
+  </si>
+  <si>
+    <t>Event attributes may differ across activities, so analysts need to know what information is available for an activity before analyzing it. Attributes also differ in structural scope: some are mandatory, some are populated independently of the activity, and others only for particular activities. Knowing an attribute's scope tells analysts whether it is globally applicable or activity-dependent, how to interpret absent values, and whether an analysis involving it should consider the entire log or only selected activities. Schemas may furthermore overlap, because different activities can record the same information. Identifying overlaps reveals which information supports comparative or cross-activity analyses, and exposes structural relationships between schemas that inspecting each schema in isolation does not.</t>
+  </si>
+  <si>
+    <t>Event logs may represent events through separate activities even though their distinction is unnecessary, or may implicitly represent semantically distinct activities through only one activity. Folding activities can provide a simplified list of activities and reduce distinctions that are not relevant. Conversely, keeping semantically distinct activities implicit can obscure the information represented by the event log. Making them explicit as distinct activities can provide a representation that better reflects the occurrences evidenced by the recorded data.</t>
   </si>
 </sst>
 </file>
@@ -1085,7 +1085,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1269,34 +1269,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1522,418 +1513,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -2136,6 +1715,418 @@
       </fill>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2149,53 +2140,49 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C219EE16-BD6D-4A1C-A20C-7BB47EB72A85}" name="Table1" displayName="Table1" ref="A1:K24" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27" tableBorderDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C219EE16-BD6D-4A1C-A20C-7BB47EB72A85}" name="Table1" displayName="Table1" ref="A1:K24" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42" tableBorderDxfId="41">
   <autoFilter ref="A1:K24" xr:uid="{C219EE16-BD6D-4A1C-A20C-7BB47EB72A85}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K24">
     <sortCondition ref="A1:A24"/>
   </sortState>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{073C678C-BCE0-4EA8-BDCB-E8064D9744D7}" name="No." dataDxfId="25"/>
-    <tableColumn id="12" xr3:uid="{5A2716E4-9833-4657-99E1-4ED3033F3A6B}" name="Category" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{28287167-4C2F-4BCC-B9D0-6EC2290B9A82}" name="Tags" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{42059FE6-74BD-43DF-AAF8-A19C90AF0751}" name="Name" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{CA5536BB-3F84-48F8-8C07-1788CAA03ECB}" name="Information Need / Modification Objective" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{016868E1-351A-45A0-A19B-7DEB6CF5C938}" name="Motivation / Context" dataDxfId="20"/>
-    <tableColumn id="14" xr3:uid="{5AC3AAD1-1AEA-46CA-97EA-4EE54081C832}" name="Preconditions" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{9744BB66-6546-4BFA-9D98-0512F242108E}" name="Approach" dataDxfId="18"/>
-    <tableColumn id="13" xr3:uid="{D5AAE128-F0FC-4A06-A848-A5E5D51BC222}" name="Output" dataDxfId="17"/>
-    <tableColumn id="15" xr3:uid="{FFED28F4-5B54-40D1-B5C2-91F48F498075}" name="Dependencies" dataDxfId="16"/>
-    <tableColumn id="16" xr3:uid="{103D6A1F-A037-4D96-A9C3-33234FD81A87}" name="Relation with Imperfection Patterns" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{073C678C-BCE0-4EA8-BDCB-E8064D9744D7}" name="No." dataDxfId="40"/>
+    <tableColumn id="12" xr3:uid="{5A2716E4-9833-4657-99E1-4ED3033F3A6B}" name="Category" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{28287167-4C2F-4BCC-B9D0-6EC2290B9A82}" name="Tags" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{42059FE6-74BD-43DF-AAF8-A19C90AF0751}" name="Name" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{CA5536BB-3F84-48F8-8C07-1788CAA03ECB}" name="Information Need / Modification Objective" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{016868E1-351A-45A0-A19B-7DEB6CF5C938}" name="Motivation / Context" dataDxfId="35"/>
+    <tableColumn id="14" xr3:uid="{5AC3AAD1-1AEA-46CA-97EA-4EE54081C832}" name="Preconditions" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{9744BB66-6546-4BFA-9D98-0512F242108E}" name="Approach" dataDxfId="33"/>
+    <tableColumn id="13" xr3:uid="{D5AAE128-F0FC-4A06-A848-A5E5D51BC222}" name="Output" dataDxfId="32"/>
+    <tableColumn id="15" xr3:uid="{FFED28F4-5B54-40D1-B5C2-91F48F498075}" name="Dependencies" dataDxfId="31"/>
+    <tableColumn id="16" xr3:uid="{103D6A1F-A037-4D96-A9C3-33234FD81A87}" name="Relation with Imperfection Patterns" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3EDC892B-CCCC-4F0E-8345-38847C019291}" name="Table2" displayName="Table2" ref="A1:M36" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3EDC892B-CCCC-4F0E-8345-38847C019291}" name="Table2" displayName="Table2" ref="A1:M36" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
   <autoFilter ref="A1:M36" xr:uid="{3EDC892B-CCCC-4F0E-8345-38847C019291}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M36">
     <sortCondition ref="A1:A36"/>
   </sortState>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{033F8C96-7095-49A2-B40C-2D8DBAEB4D12}" name="No." dataDxfId="41"/>
-    <tableColumn id="2" xr3:uid="{3421A24D-3E4F-484C-8931-798A61CA0B79}" name="Category" dataDxfId="40"/>
-    <tableColumn id="3" xr3:uid="{EC34CFC0-54EE-4B43-965F-D0E72D5F9F97}" name="Pattern name" dataDxfId="39"/>
-    <tableColumn id="5" xr3:uid="{EAE26F60-5A5D-45FE-8467-A4414A482B58}" name="RTFM" dataDxfId="38"/>
-    <tableColumn id="6" xr3:uid="{ADD3A448-8799-4C0C-BE32-57A4C8AC48CB}" name="Sepsis" dataDxfId="37"/>
-    <tableColumn id="8" xr3:uid="{135004A1-B696-44AE-8C44-B40E51D46EC6}" name="BPIC2011" dataDxfId="36"/>
-    <tableColumn id="9" xr3:uid="{F7932278-A552-4254-870D-EBD0ADF1F150}" name="BPIC2012" dataDxfId="35"/>
-    <tableColumn id="10" xr3:uid="{2188B80F-024B-4B97-A371-D8CD4103FA09}" name="BPIC2013" dataDxfId="34"/>
-    <tableColumn id="11" xr3:uid="{22FC0780-C8F6-449F-AF79-23EDA88BBC69}" name="BPIC2015_1" dataDxfId="33"/>
-    <tableColumn id="12" xr3:uid="{2C66C786-B183-4410-826E-E0043DCEF5EE}" name="BPIC2017" dataDxfId="32"/>
-    <tableColumn id="13" xr3:uid="{23FA73C3-045B-4DDD-88AC-11FAAA8E674C}" name="BPIC2018" dataDxfId="31"/>
-    <tableColumn id="14" xr3:uid="{779D4F81-71AB-4721-80EC-5495A1B2679C}" name="BPIC 2019" dataDxfId="30"/>
-    <tableColumn id="15" xr3:uid="{E23C0BD5-86A2-45C3-B9F4-6C00BA51C75C}" name="BPIC 2020" dataDxfId="29"/>
+    <tableColumn id="1" xr3:uid="{033F8C96-7095-49A2-B40C-2D8DBAEB4D12}" name="No." dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{3421A24D-3E4F-484C-8931-798A61CA0B79}" name="Category" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{EC34CFC0-54EE-4B43-965F-D0E72D5F9F97}" name="Pattern name" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{EAE26F60-5A5D-45FE-8467-A4414A482B58}" name="RTFM" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{ADD3A448-8799-4C0C-BE32-57A4C8AC48CB}" name="Sepsis" dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{135004A1-B696-44AE-8C44-B40E51D46EC6}" name="BPIC2011" dataDxfId="22"/>
+    <tableColumn id="9" xr3:uid="{F7932278-A552-4254-870D-EBD0ADF1F150}" name="BPIC2012" dataDxfId="21"/>
+    <tableColumn id="10" xr3:uid="{2188B80F-024B-4B97-A371-D8CD4103FA09}" name="BPIC2013" dataDxfId="20"/>
+    <tableColumn id="11" xr3:uid="{22FC0780-C8F6-449F-AF79-23EDA88BBC69}" name="BPIC2015_1" dataDxfId="19"/>
+    <tableColumn id="12" xr3:uid="{2C66C786-B183-4410-826E-E0043DCEF5EE}" name="BPIC2017" dataDxfId="18"/>
+    <tableColumn id="13" xr3:uid="{23FA73C3-045B-4DDD-88AC-11FAAA8E674C}" name="BPIC2018" dataDxfId="17"/>
+    <tableColumn id="14" xr3:uid="{779D4F81-71AB-4721-80EC-5495A1B2679C}" name="BPIC 2019" dataDxfId="16"/>
+    <tableColumn id="15" xr3:uid="{E23C0BD5-86A2-45C3-B9F4-6C00BA51C75C}" name="BPIC 2020" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2513,13 +2500,13 @@
         <v>8</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>21</v>
@@ -2540,7 +2527,7 @@
         <v>16</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="L1" s="2"/>
     </row>
@@ -2549,7 +2536,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="23"/>
@@ -2560,7 +2547,7 @@
         <v>11</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H2" s="23" t="s">
         <v>12</v>
@@ -2578,34 +2565,34 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>94</v>
+        <v>229</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>95</v>
+        <v>254</v>
       </c>
       <c r="G3" s="13" t="s">
         <v>7</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>96</v>
+        <v>247</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>97</v>
+        <v>248</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K3" s="51" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="L3" s="2"/>
     </row>
@@ -2614,34 +2601,34 @@
         <v>1.2</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>40</v>
+        <v>230</v>
       </c>
       <c r="G4" s="13" t="s">
         <v>7</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J4" s="31" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="K4" s="51" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="L4" s="2"/>
     </row>
@@ -2650,31 +2637,31 @@
         <v>1.3</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>25</v>
-      </c>
       <c r="J5" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K5" s="15"/>
       <c r="L5" s="2"/>
@@ -2684,31 +2671,31 @@
         <v>1.4</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>7</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>92</v>
+        <v>231</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="K6" s="11"/>
       <c r="L6" s="2"/>
@@ -2718,31 +2705,31 @@
         <v>2.1</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="G7" s="13" t="s">
         <v>7</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>23</v>
+        <v>233</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="K7" s="13"/>
       <c r="L7" s="2"/>
@@ -2752,34 +2739,34 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F8" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="K8" s="51" t="s">
         <v>118</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="J8" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="K8" s="51" t="s">
-        <v>141</v>
       </c>
       <c r="L8" s="2"/>
     </row>
@@ -2788,31 +2775,31 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>7</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="K9" s="11"/>
       <c r="L9" s="2"/>
@@ -2822,31 +2809,31 @@
         <v>2.4</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="E10" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>27</v>
-      </c>
       <c r="I10" s="11" t="s">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="K10" s="11"/>
       <c r="L10" s="2"/>
@@ -2856,34 +2843,34 @@
         <v>2.5</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>214</v>
+        <v>190</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="L11" s="2"/>
     </row>
@@ -2892,34 +2879,34 @@
         <v>2.6</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="J12" s="16" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="K12" s="51" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="L12" s="2"/>
     </row>
@@ -2928,31 +2915,31 @@
         <v>2.7</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G13" s="11" t="s">
         <v>7</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="J13" s="19" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="K13" s="18"/>
       <c r="L13" s="2"/>
@@ -2962,31 +2949,31 @@
         <v>2.8</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>14</v>
       </c>
       <c r="D14" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="11" t="s">
-        <v>49</v>
-      </c>
       <c r="F14" s="11" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="2"/>
@@ -2996,34 +2983,34 @@
         <v>3.1</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>7</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>65</v>
+        <v>238</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="J15" s="31" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="L15" s="2"/>
     </row>
@@ -3032,34 +3019,34 @@
         <v>3.2</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>57</v>
+        <v>240</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>73</v>
+        <v>241</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>62</v>
+        <v>242</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>63</v>
+        <v>243</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="L16" s="2"/>
     </row>
@@ -3068,34 +3055,34 @@
         <v>3.3</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>14</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>106</v>
+        <v>253</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>107</v>
+        <v>255</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>108</v>
+        <v>249</v>
       </c>
       <c r="H17" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="J17" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="I17" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="J17" s="11" t="s">
-        <v>132</v>
-      </c>
       <c r="K17" s="51" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="L17" s="2"/>
     </row>
@@ -3104,34 +3091,34 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D18" s="21" t="s">
         <v>22</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>253</v>
+        <v>226</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>244</v>
+        <v>217</v>
       </c>
       <c r="J18" s="16" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="L18" s="2"/>
     </row>
@@ -3140,31 +3127,31 @@
         <v>4.2</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D19" s="28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="J19" s="16" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="K19" s="19"/>
       <c r="L19" s="2"/>
@@ -3174,34 +3161,34 @@
         <v>4.3</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>58</v>
+        <v>245</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>59</v>
+        <v>252</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>60</v>
+        <v>246</v>
       </c>
       <c r="I20" s="16" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="L20" s="2"/>
     </row>
@@ -3209,21 +3196,18 @@
       <c r="L21" s="2"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="E22" s="68"/>
       <c r="L22" s="2"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="E23" s="68"/>
       <c r="L23" s="2"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="E24" s="68"/>
       <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A25" s="65"/>
-      <c r="B25" s="65"/>
-      <c r="C25" s="65"/>
+      <c r="A25" s="74"/>
+      <c r="B25" s="74"/>
+      <c r="C25" s="74"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="L25" s="2"/>
@@ -4703,7 +4687,6 @@
     <col min="3" max="3" width="49.6328125" customWidth="1"/>
     <col min="4" max="4" width="28.453125" style="29" customWidth="1"/>
     <col min="5" max="13" width="28.453125" customWidth="1"/>
-    <col min="14" max="14" width="8.7265625" style="68"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="32" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -4711,10 +4694,10 @@
         <v>8</v>
       </c>
       <c r="B1" s="33" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D1" s="40" t="s">
         <v>0</v>
@@ -4729,7 +4712,7 @@
         <v>3</v>
       </c>
       <c r="H1" s="33" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="I1" s="33" t="s">
         <v>4</v>
@@ -4741,19 +4724,19 @@
         <v>6</v>
       </c>
       <c r="L1" s="33" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="M1" s="33" t="s">
-        <v>79</v>
-      </c>
-      <c r="N1" s="67"/>
+        <v>68</v>
+      </c>
+      <c r="N1" s="66"/>
     </row>
     <row r="2" spans="1:14" s="35" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="36">
         <v>1</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C2" s="38"/>
       <c r="D2" s="43"/>
@@ -4766,50 +4749,50 @@
       <c r="K2" s="36"/>
       <c r="L2" s="36"/>
       <c r="M2" s="36"/>
-      <c r="N2" s="67"/>
+      <c r="N2" s="66"/>
     </row>
     <row r="3" spans="1:14" ht="233.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="66">
+      <c r="A3" s="65">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B3" s="66" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" s="66" t="s">
-        <v>127</v>
+      <c r="B3" s="65" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="65" t="s">
+        <v>104</v>
       </c>
       <c r="D3" s="42" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="F3" s="34"/>
       <c r="G3" s="34"/>
       <c r="H3" s="34"/>
       <c r="I3" s="34"/>
       <c r="J3" s="34" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="K3" s="34"/>
       <c r="L3" s="34"/>
       <c r="M3" s="34"/>
     </row>
     <row r="4" spans="1:14" ht="210" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="66">
+      <c r="A4" s="65">
         <v>1.2</v>
       </c>
-      <c r="B4" s="66" t="s">
-        <v>86</v>
-      </c>
-      <c r="C4" s="66" t="s">
-        <v>93</v>
+      <c r="B4" s="65" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="65" t="s">
+        <v>81</v>
       </c>
       <c r="D4" s="42" t="s">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="E4" s="34" t="s">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="F4" s="34"/>
       <c r="G4" s="34"/>
@@ -4821,20 +4804,20 @@
       <c r="M4" s="34"/>
     </row>
     <row r="5" spans="1:14" s="37" customFormat="1" ht="183" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="66">
+      <c r="A5" s="65">
         <v>1.3</v>
       </c>
-      <c r="B5" s="66" t="s">
-        <v>86</v>
-      </c>
-      <c r="C5" s="66" t="s">
-        <v>24</v>
+      <c r="B5" s="65" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="65" t="s">
+        <v>23</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>254</v>
+        <v>227</v>
       </c>
       <c r="F5" s="34"/>
       <c r="G5" s="34"/>
@@ -4844,22 +4827,22 @@
       <c r="K5" s="34"/>
       <c r="L5" s="34"/>
       <c r="M5" s="34"/>
-      <c r="N5" s="68"/>
+      <c r="N5"/>
     </row>
     <row r="6" spans="1:14" ht="93" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="66">
+      <c r="A6" s="65">
         <v>1.4</v>
       </c>
-      <c r="B6" s="66" t="s">
-        <v>86</v>
-      </c>
-      <c r="C6" s="66" t="s">
-        <v>87</v>
+      <c r="B6" s="65" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="65" t="s">
+        <v>76</v>
       </c>
       <c r="D6" s="42"/>
       <c r="E6" s="34"/>
       <c r="F6" s="34" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="G6" s="34"/>
       <c r="H6" s="34"/>
@@ -4867,7 +4850,7 @@
       <c r="J6" s="34"/>
       <c r="K6" s="34"/>
       <c r="L6" s="34" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="M6" s="34"/>
     </row>
@@ -4876,7 +4859,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C7" s="38"/>
       <c r="D7" s="43"/>
@@ -4891,20 +4874,20 @@
       <c r="M7" s="36"/>
     </row>
     <row r="8" spans="1:14" ht="250.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="66">
+      <c r="A8" s="65">
         <v>2.1</v>
       </c>
-      <c r="B8" s="66" t="s">
-        <v>112</v>
-      </c>
-      <c r="C8" s="66" t="s">
-        <v>104</v>
+      <c r="B8" s="65" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" s="65" t="s">
+        <v>88</v>
       </c>
       <c r="D8" s="42" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="E8" s="42" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34"/>
@@ -4916,20 +4899,20 @@
       <c r="M8" s="34"/>
     </row>
     <row r="9" spans="1:14" ht="146.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="66">
+      <c r="A9" s="65">
         <v>2.2000000000000002</v>
       </c>
-      <c r="B9" s="66" t="s">
-        <v>112</v>
-      </c>
-      <c r="C9" s="66" t="s">
-        <v>36</v>
+      <c r="B9" s="65" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="65" t="s">
+        <v>34</v>
       </c>
       <c r="D9" s="42" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -4941,17 +4924,17 @@
       <c r="M9" s="34"/>
     </row>
     <row r="10" spans="1:14" ht="253.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="66">
+      <c r="A10" s="65">
         <v>2.2999999999999998</v>
       </c>
-      <c r="B10" s="66" t="s">
+      <c r="B10" s="65" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="42" t="s">
         <v>112</v>
-      </c>
-      <c r="C10" s="66" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="42" t="s">
-        <v>135</v>
       </c>
       <c r="E10" s="34"/>
       <c r="F10" s="34"/>
@@ -4959,23 +4942,23 @@
       <c r="H10" s="34"/>
       <c r="I10" s="34"/>
       <c r="J10" s="34" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="K10" s="34"/>
       <c r="L10" s="34" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="M10" s="34"/>
     </row>
     <row r="11" spans="1:14" ht="113.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="66">
+      <c r="A11" s="65">
         <v>2.4</v>
       </c>
-      <c r="B11" s="66" t="s">
-        <v>112</v>
-      </c>
-      <c r="C11" s="66" t="s">
-        <v>115</v>
+      <c r="B11" s="65" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" s="65" t="s">
+        <v>94</v>
       </c>
       <c r="D11" s="42"/>
       <c r="E11" s="34"/>
@@ -4983,38 +4966,38 @@
       <c r="G11" s="34"/>
       <c r="H11" s="34"/>
       <c r="I11" s="34" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="J11" s="34"/>
       <c r="K11" s="34" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="L11" s="34"/>
       <c r="M11" s="34" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="203" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="66">
+      <c r="A12" s="65">
         <v>2.5</v>
       </c>
-      <c r="B12" s="66" t="s">
-        <v>112</v>
-      </c>
-      <c r="C12" s="66" t="s">
-        <v>113</v>
+      <c r="B12" s="65" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" s="65" t="s">
+        <v>92</v>
       </c>
       <c r="D12" s="42" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="E12" s="34"/>
       <c r="F12" s="34"/>
       <c r="G12" s="34" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="H12" s="34"/>
       <c r="I12" s="34" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="J12" s="34"/>
       <c r="K12" s="34"/>
@@ -5022,20 +5005,20 @@
       <c r="M12" s="34"/>
     </row>
     <row r="13" spans="1:14" ht="180" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="66">
+      <c r="A13" s="65">
         <v>2.6</v>
       </c>
-      <c r="B13" s="66" t="s">
-        <v>112</v>
-      </c>
-      <c r="C13" s="66" t="s">
-        <v>117</v>
+      <c r="B13" s="65" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" s="65" t="s">
+        <v>96</v>
       </c>
       <c r="D13" s="42" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
@@ -5044,67 +5027,67 @@
       <c r="J13" s="34"/>
       <c r="K13" s="34"/>
       <c r="L13" s="34" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="M13" s="34"/>
     </row>
     <row r="14" spans="1:14" s="37" customFormat="1" ht="187.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="66">
+      <c r="A14" s="65">
         <v>2.7</v>
       </c>
-      <c r="B14" s="66" t="s">
-        <v>112</v>
-      </c>
-      <c r="C14" s="66" t="s">
-        <v>114</v>
+      <c r="B14" s="65" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" s="65" t="s">
+        <v>93</v>
       </c>
       <c r="D14" s="42" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="F14" s="34" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="G14" s="34"/>
       <c r="H14" s="34"/>
       <c r="I14" s="34"/>
       <c r="J14" s="34" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="K14" s="34"/>
       <c r="L14" s="34"/>
       <c r="M14" s="34"/>
-      <c r="N14" s="68"/>
+      <c r="N14"/>
     </row>
     <row r="15" spans="1:14" ht="129.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="66">
+      <c r="A15" s="65">
         <v>2.8</v>
       </c>
-      <c r="B15" s="66" t="s">
-        <v>112</v>
-      </c>
-      <c r="C15" s="66" t="s">
-        <v>46</v>
+      <c r="B15" s="65" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="65" t="s">
+        <v>43</v>
       </c>
       <c r="D15" s="42" t="s">
-        <v>231</v>
+        <v>207</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34"/>
       <c r="H15" s="34"/>
       <c r="I15" s="34"/>
       <c r="J15" s="34" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="K15" s="34"/>
       <c r="L15" s="50"/>
       <c r="M15" s="34" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -5112,7 +5095,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="35" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C16" s="35"/>
       <c r="D16" s="41"/>
@@ -5127,14 +5110,14 @@
       <c r="M16" s="35"/>
     </row>
     <row r="17" spans="1:14" ht="375.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="66">
+      <c r="A17" s="65">
         <v>3.1</v>
       </c>
-      <c r="B17" s="66" t="s">
-        <v>103</v>
-      </c>
-      <c r="C17" s="66" t="s">
-        <v>105</v>
+      <c r="B17" s="65" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" s="65" t="s">
+        <v>89</v>
       </c>
       <c r="D17" s="42"/>
       <c r="E17" s="34"/>
@@ -5143,72 +5126,72 @@
       <c r="H17" s="34"/>
       <c r="I17" s="34"/>
       <c r="J17" s="34" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="K17" s="34"/>
       <c r="L17" s="34"/>
       <c r="M17" s="34" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="269" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="79">
+      <c r="A18" s="73">
         <v>3.2</v>
       </c>
-      <c r="B18" s="66" t="s">
-        <v>103</v>
-      </c>
-      <c r="C18" s="66" t="s">
-        <v>30</v>
+      <c r="B18" s="65" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" s="65" t="s">
+        <v>29</v>
       </c>
       <c r="D18" s="34" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
       <c r="E18" s="34" t="s">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="F18" s="34"/>
       <c r="G18" s="34" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="H18" s="34" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="I18" s="34"/>
       <c r="J18" s="34"/>
       <c r="K18" s="34"/>
       <c r="L18" s="34" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="M18" s="34"/>
     </row>
     <row r="19" spans="1:14" ht="171.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="66">
+      <c r="A19" s="65">
         <v>3.3</v>
       </c>
-      <c r="B19" s="66" t="s">
-        <v>103</v>
-      </c>
-      <c r="C19" s="66" t="s">
-        <v>128</v>
+      <c r="B19" s="65" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" s="65" t="s">
+        <v>105</v>
       </c>
       <c r="D19" s="42" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="E19" s="34" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F19" s="34"/>
       <c r="G19" s="34"/>
       <c r="H19" s="34"/>
       <c r="I19" s="34" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="J19" s="34"/>
       <c r="K19" s="34"/>
       <c r="L19" s="34"/>
       <c r="M19" s="34" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:14" s="39" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -5216,7 +5199,7 @@
         <v>4</v>
       </c>
       <c r="B20" s="35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C20" s="38"/>
       <c r="D20" s="44"/>
@@ -5229,20 +5212,20 @@
       <c r="K20" s="38"/>
       <c r="L20" s="38"/>
       <c r="M20" s="38"/>
-      <c r="N20" s="69"/>
+      <c r="N20" s="67"/>
     </row>
     <row r="21" spans="1:14" ht="240.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="66">
+      <c r="A21" s="65">
         <v>4.0999999999999996</v>
       </c>
-      <c r="B21" s="66" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" s="66" t="s">
+      <c r="B21" s="65" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="65" t="s">
         <v>22</v>
       </c>
       <c r="D21" s="42" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="E21" s="34"/>
       <c r="F21" s="34"/>
@@ -5251,51 +5234,51 @@
       <c r="I21" s="34"/>
       <c r="J21" s="34"/>
       <c r="K21" s="34" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="L21" s="34"/>
       <c r="M21" s="34"/>
     </row>
     <row r="22" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="79">
+      <c r="A22" s="73">
         <v>4.2</v>
       </c>
-      <c r="B22" s="66" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="66" t="s">
-        <v>29</v>
+      <c r="B22" s="65" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="65" t="s">
+        <v>28</v>
       </c>
       <c r="D22" s="42"/>
       <c r="E22" s="34"/>
       <c r="F22" s="34"/>
       <c r="G22" s="34"/>
       <c r="H22" s="34" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="I22" s="34"/>
       <c r="J22" s="34"/>
       <c r="K22" s="34" t="s">
-        <v>246</v>
+        <v>219</v>
       </c>
       <c r="L22" s="34"/>
       <c r="M22" s="34"/>
     </row>
     <row r="23" spans="1:14" ht="338.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="66">
+      <c r="A23" s="65">
         <v>4.3</v>
       </c>
-      <c r="B23" s="66" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="66" t="s">
-        <v>131</v>
+      <c r="B23" s="65" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="65" t="s">
+        <v>108</v>
       </c>
       <c r="D23" s="34" t="s">
-        <v>248</v>
+        <v>221</v>
       </c>
       <c r="E23" s="34" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="F23" s="34"/>
       <c r="G23" s="34"/>
@@ -5305,204 +5288,201 @@
       <c r="K23" s="34"/>
       <c r="L23" s="34"/>
       <c r="M23" s="34" t="s">
-        <v>250</v>
+        <v>223</v>
       </c>
     </row>
     <row r="24" spans="1:14" s="46" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="71"/>
-      <c r="B24" s="72"/>
-      <c r="C24" s="72"/>
-      <c r="D24" s="73"/>
-      <c r="E24" s="73"/>
-      <c r="F24" s="73"/>
-      <c r="G24" s="73"/>
-      <c r="H24" s="73"/>
-      <c r="I24" s="73"/>
-      <c r="J24" s="73"/>
-      <c r="K24" s="73"/>
-      <c r="L24" s="73"/>
-      <c r="M24" s="73"/>
-      <c r="N24" s="70"/>
+      <c r="A24" s="68"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="48"/>
+      <c r="J24" s="48"/>
+      <c r="K24" s="48"/>
+      <c r="L24" s="48"/>
+      <c r="M24" s="48"/>
     </row>
     <row r="25" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="74"/>
-      <c r="B25" s="74"/>
-      <c r="C25" s="74"/>
-      <c r="D25" s="75"/>
-      <c r="E25" s="75"/>
-      <c r="F25" s="75"/>
-      <c r="G25" s="75"/>
-      <c r="H25" s="75"/>
-      <c r="I25" s="75"/>
-      <c r="J25" s="75"/>
-      <c r="K25" s="75"/>
-      <c r="L25" s="75"/>
-      <c r="M25" s="75"/>
+      <c r="A25" s="69"/>
+      <c r="B25" s="69"/>
+      <c r="C25" s="69"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="50"/>
+      <c r="H25" s="50"/>
+      <c r="I25" s="50"/>
+      <c r="J25" s="50"/>
+      <c r="K25" s="50"/>
+      <c r="L25" s="50"/>
+      <c r="M25" s="50"/>
     </row>
     <row r="26" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="74"/>
-      <c r="B26" s="74"/>
-      <c r="C26" s="74"/>
-      <c r="D26" s="75"/>
-      <c r="E26" s="75"/>
-      <c r="F26" s="75"/>
-      <c r="G26" s="75"/>
-      <c r="H26" s="75"/>
-      <c r="I26" s="75"/>
-      <c r="J26" s="75"/>
-      <c r="K26" s="75"/>
-      <c r="L26" s="75"/>
-      <c r="M26" s="75"/>
+      <c r="A26" s="69"/>
+      <c r="B26" s="69"/>
+      <c r="C26" s="69"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="50"/>
+      <c r="H26" s="50"/>
+      <c r="I26" s="50"/>
+      <c r="J26" s="50"/>
+      <c r="K26" s="50"/>
+      <c r="L26" s="50"/>
+      <c r="M26" s="50"/>
     </row>
     <row r="27" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="74"/>
-      <c r="B27" s="74"/>
-      <c r="C27" s="74"/>
-      <c r="D27" s="75"/>
-      <c r="E27" s="75"/>
-      <c r="F27" s="75"/>
-      <c r="G27" s="75"/>
-      <c r="H27" s="75"/>
-      <c r="I27" s="75"/>
-      <c r="J27" s="75"/>
-      <c r="K27" s="75"/>
-      <c r="L27" s="75"/>
-      <c r="M27" s="75"/>
+      <c r="A27" s="69"/>
+      <c r="B27" s="69"/>
+      <c r="C27" s="69"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="50"/>
+      <c r="G27" s="50"/>
+      <c r="H27" s="50"/>
+      <c r="I27" s="50"/>
+      <c r="J27" s="50"/>
+      <c r="K27" s="50"/>
+      <c r="L27" s="50"/>
+      <c r="M27" s="50"/>
     </row>
     <row r="28" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="74"/>
-      <c r="B28" s="74"/>
-      <c r="C28" s="74"/>
-      <c r="D28" s="75"/>
-      <c r="E28" s="75"/>
-      <c r="F28" s="75"/>
-      <c r="G28" s="75"/>
-      <c r="H28" s="75"/>
-      <c r="I28" s="75"/>
-      <c r="J28" s="75"/>
-      <c r="K28" s="75"/>
-      <c r="L28" s="75"/>
-      <c r="M28" s="75"/>
+      <c r="A28" s="69"/>
+      <c r="B28" s="69"/>
+      <c r="C28" s="69"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="50"/>
+      <c r="G28" s="50"/>
+      <c r="H28" s="50"/>
+      <c r="I28" s="50"/>
+      <c r="J28" s="50"/>
+      <c r="K28" s="50"/>
+      <c r="L28" s="50"/>
+      <c r="M28" s="50"/>
     </row>
     <row r="29" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="76"/>
-      <c r="B29" s="74"/>
-      <c r="C29" s="74"/>
-      <c r="D29" s="75"/>
-      <c r="E29" s="75"/>
-      <c r="F29" s="75"/>
-      <c r="G29" s="75"/>
-      <c r="H29" s="75"/>
-      <c r="I29" s="75"/>
-      <c r="J29" s="75"/>
-      <c r="K29" s="75"/>
-      <c r="L29" s="75"/>
-      <c r="M29" s="75"/>
+      <c r="A29" s="70"/>
+      <c r="B29" s="69"/>
+      <c r="C29" s="69"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="50"/>
+      <c r="H29" s="50"/>
+      <c r="I29" s="50"/>
+      <c r="J29" s="50"/>
+      <c r="K29" s="50"/>
+      <c r="L29" s="50"/>
+      <c r="M29" s="50"/>
     </row>
     <row r="30" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="76"/>
-      <c r="B30" s="74"/>
-      <c r="C30" s="74"/>
-      <c r="D30" s="75"/>
-      <c r="E30" s="75"/>
-      <c r="F30" s="75"/>
-      <c r="G30" s="75"/>
-      <c r="H30" s="75"/>
-      <c r="I30" s="75"/>
-      <c r="J30" s="75"/>
-      <c r="K30" s="75"/>
-      <c r="L30" s="75"/>
-      <c r="M30" s="75"/>
+      <c r="A30" s="70"/>
+      <c r="B30" s="69"/>
+      <c r="C30" s="69"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
+      <c r="F30" s="50"/>
+      <c r="G30" s="50"/>
+      <c r="H30" s="50"/>
+      <c r="I30" s="50"/>
+      <c r="J30" s="50"/>
+      <c r="K30" s="50"/>
+      <c r="L30" s="50"/>
+      <c r="M30" s="50"/>
     </row>
     <row r="31" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="76"/>
-      <c r="B31" s="74"/>
-      <c r="C31" s="74"/>
-      <c r="D31" s="75"/>
-      <c r="E31" s="75"/>
-      <c r="F31" s="75"/>
-      <c r="G31" s="75"/>
-      <c r="H31" s="74"/>
-      <c r="I31" s="75"/>
-      <c r="J31" s="75"/>
-      <c r="K31" s="75"/>
-      <c r="L31" s="75"/>
-      <c r="M31" s="75"/>
+      <c r="A31" s="70"/>
+      <c r="B31" s="69"/>
+      <c r="C31" s="69"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="50"/>
+      <c r="G31" s="50"/>
+      <c r="H31" s="69"/>
+      <c r="I31" s="50"/>
+      <c r="J31" s="50"/>
+      <c r="K31" s="50"/>
+      <c r="L31" s="50"/>
+      <c r="M31" s="50"/>
     </row>
     <row r="32" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="74"/>
-      <c r="B32" s="74"/>
-      <c r="C32" s="74"/>
-      <c r="D32" s="75"/>
-      <c r="E32" s="75"/>
-      <c r="F32" s="75"/>
-      <c r="G32" s="75"/>
-      <c r="H32" s="74"/>
-      <c r="I32" s="75"/>
-      <c r="J32" s="75"/>
-      <c r="K32" s="75"/>
-      <c r="L32" s="75"/>
-      <c r="M32" s="75"/>
+      <c r="A32" s="69"/>
+      <c r="B32" s="69"/>
+      <c r="C32" s="69"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="50"/>
+      <c r="G32" s="50"/>
+      <c r="H32" s="69"/>
+      <c r="I32" s="50"/>
+      <c r="J32" s="50"/>
+      <c r="K32" s="50"/>
+      <c r="L32" s="50"/>
+      <c r="M32" s="50"/>
     </row>
     <row r="33" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="74"/>
-      <c r="B33" s="74"/>
-      <c r="C33" s="74"/>
-      <c r="D33" s="75"/>
-      <c r="E33" s="75"/>
-      <c r="F33" s="75"/>
-      <c r="G33" s="75"/>
-      <c r="H33" s="75"/>
-      <c r="I33" s="75"/>
-      <c r="J33" s="75"/>
-      <c r="K33" s="75"/>
-      <c r="L33" s="75"/>
-      <c r="M33" s="75"/>
+      <c r="A33" s="69"/>
+      <c r="B33" s="69"/>
+      <c r="C33" s="69"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="50"/>
+      <c r="G33" s="50"/>
+      <c r="H33" s="50"/>
+      <c r="I33" s="50"/>
+      <c r="J33" s="50"/>
+      <c r="K33" s="50"/>
+      <c r="L33" s="50"/>
+      <c r="M33" s="50"/>
     </row>
     <row r="34" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="74"/>
-      <c r="B34" s="74"/>
-      <c r="C34" s="74"/>
-      <c r="D34" s="75"/>
-      <c r="E34" s="75"/>
-      <c r="F34" s="75"/>
-      <c r="G34" s="75"/>
-      <c r="H34" s="75"/>
-      <c r="I34" s="75"/>
-      <c r="J34" s="75"/>
-      <c r="K34" s="75"/>
-      <c r="L34" s="75"/>
-      <c r="M34" s="75"/>
+      <c r="A34" s="69"/>
+      <c r="B34" s="69"/>
+      <c r="C34" s="69"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="50"/>
+      <c r="G34" s="50"/>
+      <c r="H34" s="50"/>
+      <c r="I34" s="50"/>
+      <c r="J34" s="50"/>
+      <c r="K34" s="50"/>
+      <c r="L34" s="50"/>
+      <c r="M34" s="50"/>
     </row>
     <row r="35" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="74"/>
-      <c r="B35" s="74"/>
-      <c r="C35" s="74"/>
-      <c r="D35" s="75"/>
-      <c r="E35" s="75"/>
-      <c r="F35" s="75"/>
-      <c r="G35" s="75"/>
-      <c r="H35" s="75"/>
-      <c r="I35" s="75"/>
-      <c r="J35" s="75"/>
-      <c r="K35" s="75"/>
-      <c r="L35" s="75"/>
-      <c r="M35" s="75"/>
+      <c r="A35" s="69"/>
+      <c r="B35" s="69"/>
+      <c r="C35" s="69"/>
+      <c r="D35" s="50"/>
+      <c r="E35" s="50"/>
+      <c r="F35" s="50"/>
+      <c r="G35" s="50"/>
+      <c r="H35" s="50"/>
+      <c r="I35" s="50"/>
+      <c r="J35" s="50"/>
+      <c r="K35" s="50"/>
+      <c r="L35" s="50"/>
+      <c r="M35" s="50"/>
     </row>
     <row r="36" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="77"/>
-      <c r="B36" s="77"/>
-      <c r="C36" s="77"/>
-      <c r="D36" s="78"/>
-      <c r="E36" s="78"/>
-      <c r="F36" s="78"/>
-      <c r="G36" s="78"/>
-      <c r="H36" s="78"/>
-      <c r="I36" s="78"/>
-      <c r="J36" s="78"/>
-      <c r="K36" s="78"/>
-      <c r="L36" s="78"/>
-      <c r="M36" s="78"/>
+      <c r="A36" s="71"/>
+      <c r="B36" s="71"/>
+      <c r="C36" s="71"/>
+      <c r="D36" s="72"/>
+      <c r="E36" s="72"/>
+      <c r="F36" s="72"/>
+      <c r="G36" s="72"/>
+      <c r="H36" s="72"/>
+      <c r="I36" s="72"/>
+      <c r="J36" s="72"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="72"/>
+      <c r="M36" s="72"/>
     </row>
     <row r="37" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
@@ -5534,10 +5514,10 @@
         <v>8</v>
       </c>
       <c r="B1" s="33" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D1" s="40" t="s">
         <v>0</v>
@@ -5552,7 +5532,7 @@
         <v>3</v>
       </c>
       <c r="H1" s="33" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="I1" s="33" t="s">
         <v>4</v>
@@ -5564,10 +5544,10 @@
         <v>6</v>
       </c>
       <c r="L1" s="33" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="M1" s="33" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="35" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -5575,7 +5555,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C2" s="57"/>
       <c r="D2" s="52"/>
@@ -5594,23 +5574,23 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B3" s="58" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C3" s="58" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" s="49" t="s">
         <v>127</v>
       </c>
-      <c r="D3" s="49" t="s">
-        <v>150</v>
-      </c>
       <c r="E3" s="50" t="s">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="F3" s="50"/>
       <c r="G3" s="50"/>
       <c r="H3" s="50"/>
       <c r="I3" s="50"/>
       <c r="J3" s="50" t="s">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="K3" s="50"/>
       <c r="L3" s="50"/>
@@ -5621,16 +5601,16 @@
         <v>1.2</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D4" s="49" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="E4" s="50" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="F4" s="50"/>
       <c r="G4" s="50"/>
@@ -5646,16 +5626,16 @@
         <v>1.3</v>
       </c>
       <c r="B5" s="58" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C5" s="58" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="E5" s="50" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="F5" s="50"/>
       <c r="G5" s="50"/>
@@ -5671,15 +5651,15 @@
         <v>1.4</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="D6" s="49"/>
       <c r="E6" s="50"/>
       <c r="F6" s="50" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="G6" s="50"/>
       <c r="H6" s="50"/>
@@ -5687,7 +5667,7 @@
       <c r="J6" s="50"/>
       <c r="K6" s="54"/>
       <c r="L6" s="50" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="M6" s="50"/>
     </row>
@@ -5696,7 +5676,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C7" s="57"/>
       <c r="D7" s="52"/>
@@ -5715,16 +5695,16 @@
         <v>2.1</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="D8" s="49" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="E8" s="49" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="F8" s="50"/>
       <c r="G8" s="50"/>
@@ -5740,16 +5720,16 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B9" s="58" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C9" s="58" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D9" s="49" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="E9" s="50" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="F9" s="50"/>
       <c r="G9" s="50"/>
@@ -5765,13 +5745,13 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D10" s="49" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="E10" s="50"/>
       <c r="F10" s="50"/>
@@ -5779,11 +5759,11 @@
       <c r="H10" s="50"/>
       <c r="I10" s="50"/>
       <c r="J10" s="50" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="K10" s="50"/>
       <c r="L10" s="50" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="M10" s="50"/>
     </row>
@@ -5792,10 +5772,10 @@
         <v>2.4</v>
       </c>
       <c r="B11" s="58" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C11" s="58" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="D11" s="49"/>
       <c r="E11" s="50"/>
@@ -5803,15 +5783,15 @@
       <c r="G11" s="50"/>
       <c r="H11" s="50"/>
       <c r="I11" s="50" t="s">
-        <v>208</v>
+        <v>184</v>
       </c>
       <c r="J11" s="50"/>
       <c r="K11" s="50" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="L11" s="50"/>
       <c r="M11" s="50" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="222" customHeight="1" x14ac:dyDescent="0.35">
@@ -5819,22 +5799,22 @@
         <v>2.5</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="D12" s="42" t="s">
-        <v>255</v>
+        <v>228</v>
       </c>
       <c r="E12" s="50"/>
       <c r="F12" s="50"/>
       <c r="G12" s="50" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="H12" s="50"/>
       <c r="I12" s="50" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="J12" s="50"/>
       <c r="K12" s="50"/>
@@ -5846,16 +5826,16 @@
         <v>2.6</v>
       </c>
       <c r="B13" s="58" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C13" s="58" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="D13" s="49" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="E13" s="50" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="F13" s="50"/>
       <c r="G13" s="50"/>
@@ -5871,25 +5851,25 @@
         <v>2.7</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="D14" s="49" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="E14" s="50" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="F14" s="50" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="G14" s="50"/>
       <c r="H14" s="50"/>
       <c r="I14" s="50"/>
       <c r="J14" s="50" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="K14" s="50"/>
       <c r="L14" s="50"/>
@@ -5900,28 +5880,28 @@
         <v>2.8</v>
       </c>
       <c r="B15" s="58" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C15" s="58" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D15" s="49" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="E15" s="50" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="F15" s="50"/>
       <c r="G15" s="50"/>
       <c r="H15" s="50"/>
       <c r="I15" s="50"/>
       <c r="J15" s="50" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="K15" s="50"/>
       <c r="L15" s="50"/>
       <c r="M15" s="50" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
@@ -5929,7 +5909,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="35" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C16" s="35"/>
       <c r="D16" s="41"/>
@@ -5948,10 +5928,10 @@
         <v>3.1</v>
       </c>
       <c r="B17" s="58" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C17" s="58" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="D17" s="49"/>
       <c r="E17" s="50"/>
@@ -5960,12 +5940,12 @@
       <c r="H17" s="50"/>
       <c r="I17" s="50"/>
       <c r="J17" s="50" t="s">
-        <v>234</v>
+        <v>208</v>
       </c>
       <c r="K17" s="50"/>
       <c r="L17" s="50"/>
       <c r="M17" s="50" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="256.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5973,29 +5953,29 @@
         <v>3.2</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" s="50" t="s">
-        <v>237</v>
+        <v>211</v>
       </c>
       <c r="E18" s="50" t="s">
-        <v>239</v>
+        <v>213</v>
       </c>
       <c r="F18" s="50"/>
       <c r="G18" s="50" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="H18" s="50" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="I18" s="50"/>
       <c r="J18" s="50"/>
       <c r="K18" s="50"/>
       <c r="L18" s="50" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="M18" s="50"/>
     </row>
@@ -6004,28 +5984,28 @@
         <v>3.3</v>
       </c>
       <c r="B19" s="58" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C19" s="58" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="D19" s="49" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E19" s="50" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="F19" s="50"/>
       <c r="G19" s="50"/>
       <c r="H19" s="50"/>
       <c r="I19" s="50" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="J19" s="50"/>
       <c r="K19" s="50"/>
       <c r="L19" s="50"/>
       <c r="M19" s="50" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:13" s="61" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -6033,7 +6013,7 @@
         <v>4</v>
       </c>
       <c r="B20" s="35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C20" s="57"/>
       <c r="D20" s="56"/>
@@ -6051,13 +6031,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B21" s="58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C21" s="58" t="s">
         <v>22</v>
       </c>
       <c r="D21" s="49" t="s">
-        <v>245</v>
+        <v>218</v>
       </c>
       <c r="E21" s="50"/>
       <c r="F21" s="50"/>
@@ -6066,7 +6046,7 @@
       <c r="I21" s="50"/>
       <c r="J21" s="50"/>
       <c r="K21" s="50" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="L21" s="50"/>
       <c r="M21" s="50"/>
@@ -6076,22 +6056,22 @@
         <v>4.2</v>
       </c>
       <c r="B22" s="58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22" s="58" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D22" s="49"/>
       <c r="E22" s="50"/>
       <c r="F22" s="50"/>
       <c r="G22" s="50"/>
       <c r="H22" s="50" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="I22" s="50"/>
       <c r="J22" s="50"/>
       <c r="K22" s="50" t="s">
-        <v>247</v>
+        <v>220</v>
       </c>
       <c r="L22" s="50"/>
       <c r="M22" s="50"/>
@@ -6101,16 +6081,16 @@
         <v>4.3</v>
       </c>
       <c r="B23" s="58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C23" s="58" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="D23" s="50" t="s">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="E23" s="50" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="F23" s="50"/>
       <c r="G23" s="50"/>
@@ -6120,7 +6100,7 @@
       <c r="K23" s="50"/>
       <c r="L23" s="50"/>
       <c r="M23" s="50" t="s">
-        <v>251</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:13" s="48" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
